--- a/risk/Risk_Analysis_T3_25yrs_Present_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_25yrs_Present_Breaches.xlsx
@@ -25,18 +25,12 @@
     <sheet name="Kashmore_Exp" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Kashmore_Vul" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="Kashmore_Dmg" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Naushahro Feroze_Exp" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Naushahro Feroze_Vul" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Naushahro Feroze_Dmg" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Qambar Shahdadkot_Exp" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Qambar Shahdadkot_Vul" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Qambar Shahdadkot_Dmg" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Shaheed Benazirabad_Exp" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Shaheed Benazirabad_Vul" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Shaheed Benazirabad_Dmg" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Shikarpur_Exp" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Shikarpur_Vul" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Shikarpur_Dmg" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Qambar Shahdadkot_Exp" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Qambar Shahdadkot_Vul" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Qambar Shahdadkot_Dmg" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Shikarpur_Exp" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Shikarpur_Vul" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Shikarpur_Dmg" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9772,7 +9766,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Exp</t>
+          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -9843,37 +9837,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>2527.83</v>
+        <v>33746.4</v>
       </c>
       <c r="C4" t="n">
-        <v>556920</v>
+        <v>5820192</v>
       </c>
       <c r="D4" t="n">
-        <v>437580</v>
+        <v>4573008</v>
       </c>
       <c r="E4" t="n">
-        <v>140400</v>
+        <v>1446300</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>6180</v>
+        <v>96660</v>
       </c>
       <c r="H4" t="n">
-        <v>210</v>
+        <v>10050</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>18840</v>
+        <v>221460</v>
       </c>
     </row>
     <row r="5">
@@ -9881,37 +9875,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3814.74</v>
+        <v>41651.28</v>
       </c>
       <c r="C5" t="n">
-        <v>640584</v>
+        <v>5647824</v>
       </c>
       <c r="D5" t="n">
-        <v>503316</v>
+        <v>4437576</v>
       </c>
       <c r="E5" t="n">
-        <v>105300</v>
+        <v>1126800</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>9090</v>
+        <v>102960</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>13020</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>21240</v>
+        <v>261210</v>
       </c>
     </row>
     <row r="6">
@@ -9919,37 +9913,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>3826.35</v>
+        <v>30218.49</v>
       </c>
       <c r="C6" t="n">
-        <v>394128</v>
+        <v>2431296</v>
       </c>
       <c r="D6" t="n">
-        <v>309672</v>
+        <v>1910304</v>
       </c>
       <c r="E6" t="n">
-        <v>61200</v>
+        <v>242100</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>7710</v>
+        <v>62520</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>5190</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>21180</v>
+        <v>135810</v>
       </c>
     </row>
     <row r="7">
@@ -9957,37 +9951,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2490.3</v>
+        <v>21460.32</v>
       </c>
       <c r="C7" t="n">
-        <v>186480</v>
+        <v>1419264</v>
       </c>
       <c r="D7" t="n">
-        <v>146520</v>
+        <v>1115136</v>
       </c>
       <c r="E7" t="n">
-        <v>31500</v>
+        <v>95400</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>4770</v>
+        <v>39120</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>780</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>8550</v>
+        <v>68400</v>
       </c>
     </row>
     <row r="8">
@@ -9995,37 +9989,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1286.01</v>
+        <v>8587.620000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>54936</v>
+        <v>612360</v>
       </c>
       <c r="D8" t="n">
-        <v>43164</v>
+        <v>481140</v>
       </c>
       <c r="E8" t="n">
-        <v>5400</v>
+        <v>28800</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1530</v>
+        <v>11220</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3540</v>
+        <v>34170</v>
       </c>
     </row>
     <row r="9">
@@ -10033,22 +10027,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>628.38</v>
+        <v>804.6</v>
       </c>
       <c r="C9" t="n">
-        <v>17640</v>
+        <v>82656</v>
       </c>
       <c r="D9" t="n">
-        <v>13860</v>
+        <v>64944</v>
       </c>
       <c r="E9" t="n">
-        <v>7200</v>
+        <v>1800</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>840</v>
+        <v>1920</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -10063,7 +10057,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>840</v>
+        <v>8940</v>
       </c>
     </row>
     <row r="10">
@@ -10071,13 +10065,13 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>385.47</v>
+        <v>226.08</v>
       </c>
       <c r="C10" t="n">
-        <v>2016</v>
+        <v>16632</v>
       </c>
       <c r="D10" t="n">
-        <v>1584</v>
+        <v>13068</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -10086,10 +10080,10 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>390</v>
+        <v>600</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -10101,7 +10095,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>540</v>
+        <v>3930</v>
       </c>
     </row>
     <row r="11">
@@ -10109,13 +10103,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>216.18</v>
+        <v>207.63</v>
       </c>
       <c r="C11" t="n">
-        <v>3024</v>
+        <v>4032</v>
       </c>
       <c r="D11" t="n">
-        <v>2376</v>
+        <v>3168</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -10124,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -10139,7 +10133,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>300</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="12">
@@ -10147,22 +10141,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>156.96</v>
+        <v>43.02</v>
       </c>
       <c r="C12" t="n">
-        <v>1008</v>
+        <v>2520</v>
       </c>
       <c r="D12" t="n">
-        <v>792</v>
+        <v>1980</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>360</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -10177,7 +10171,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="13">
@@ -10185,13 +10179,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>169.2</v>
+        <v>15.48</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -10200,7 +10194,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -10215,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>870</v>
       </c>
     </row>
     <row r="14">
@@ -10223,22 +10217,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>42.93</v>
+        <v>15.21</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>1512</v>
       </c>
       <c r="D14" t="n">
-        <v>396</v>
+        <v>1188</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>450</v>
+        <v>120</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -10253,7 +10247,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>300</v>
       </c>
     </row>
     <row r="15">
@@ -10261,13 +10255,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>4.32</v>
+        <v>7.74</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -10276,7 +10270,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -10291,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
     </row>
     <row r="16">
@@ -10299,13 +10293,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.99</v>
+        <v>4.14</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -10314,7 +10308,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -10329,7 +10323,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>630</v>
       </c>
     </row>
     <row r="17">
@@ -10337,13 +10331,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>0.54</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>2772</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -10352,7 +10346,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>3720</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -10375,13 +10369,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -10413,13 +10407,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -10454,10 +10448,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -10530,10 +10524,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -10568,10 +10562,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -10606,10 +10600,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>2376</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -11636,7 +11630,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Vul</t>
+          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -11745,37 +11739,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>1716.63</v>
+        <v>18743.08</v>
       </c>
       <c r="C5" t="n">
-        <v>352321.2</v>
+        <v>3106303.2</v>
       </c>
       <c r="D5" t="n">
-        <v>166597.6</v>
+        <v>1468837.66</v>
       </c>
       <c r="E5" t="n">
-        <v>11614.59</v>
+        <v>124286.04</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>4687.2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4460.4</v>
+        <v>54854.1</v>
       </c>
     </row>
     <row r="6">
@@ -11783,37 +11777,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>3061.08</v>
+        <v>24174.79</v>
       </c>
       <c r="C6" t="n">
-        <v>354715.2</v>
+        <v>2188166.4</v>
       </c>
       <c r="D6" t="n">
-        <v>157003.7</v>
+        <v>968524.13</v>
       </c>
       <c r="E6" t="n">
-        <v>10342.8</v>
+        <v>40914.9</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="G6" t="n">
-        <v>385.5</v>
+        <v>3126</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2958.3</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>7836.6</v>
+        <v>50249.7</v>
       </c>
     </row>
     <row r="7">
@@ -11821,37 +11815,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2365.78</v>
+        <v>20387.3</v>
       </c>
       <c r="C7" t="n">
-        <v>186480</v>
+        <v>1419264</v>
       </c>
       <c r="D7" t="n">
-        <v>93479.75999999999</v>
+        <v>711456.77</v>
       </c>
       <c r="E7" t="n">
-        <v>6700.05</v>
+        <v>20291.58</v>
       </c>
       <c r="F7" t="n">
         <v>0.6</v>
       </c>
       <c r="G7" t="n">
-        <v>715.5</v>
+        <v>5868</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>569.4</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>5130</v>
+        <v>41040</v>
       </c>
     </row>
     <row r="8">
@@ -11859,37 +11853,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1286.01</v>
+        <v>8587.620000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>54936</v>
+        <v>612360</v>
       </c>
       <c r="D8" t="n">
-        <v>31768.7</v>
+        <v>354119.04</v>
       </c>
       <c r="E8" t="n">
-        <v>1324.62</v>
+        <v>7064.64</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>994.5</v>
+        <v>7293</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2513.4</v>
+        <v>24260.7</v>
       </c>
     </row>
     <row r="9">
@@ -11897,22 +11891,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>628.38</v>
+        <v>804.6</v>
       </c>
       <c r="C9" t="n">
-        <v>17640</v>
+        <v>82656</v>
       </c>
       <c r="D9" t="n">
-        <v>11129.58</v>
+        <v>52150.03</v>
       </c>
       <c r="E9" t="n">
-        <v>1927.44</v>
+        <v>481.86</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>714</v>
+        <v>1632</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -11927,7 +11921,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>680.4</v>
+        <v>7241.4</v>
       </c>
     </row>
     <row r="10">
@@ -11935,13 +11929,13 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>385.47</v>
+        <v>226.08</v>
       </c>
       <c r="C10" t="n">
-        <v>2016</v>
+        <v>16632</v>
       </c>
       <c r="D10" t="n">
-        <v>1378.08</v>
+        <v>11369.16</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -11950,10 +11944,10 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>390</v>
+        <v>600</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -11965,7 +11959,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>480.6</v>
+        <v>3497.7</v>
       </c>
     </row>
     <row r="11">
@@ -11973,13 +11967,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>216.18</v>
+        <v>207.63</v>
       </c>
       <c r="C11" t="n">
-        <v>3024</v>
+        <v>4032</v>
       </c>
       <c r="D11" t="n">
-        <v>2134.84</v>
+        <v>2846.45</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -11988,7 +11982,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -12003,7 +11997,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>300</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="12">
@@ -12011,22 +12005,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>156.96</v>
+        <v>43.02</v>
       </c>
       <c r="C12" t="n">
-        <v>1008</v>
+        <v>2520</v>
       </c>
       <c r="D12" t="n">
-        <v>734.1799999999999</v>
+        <v>1835.46</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>430.2</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>360</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12041,7 +12035,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="13">
@@ -12049,13 +12043,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>169.2</v>
+        <v>15.48</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1128.01</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12064,7 +12058,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -12079,7 +12073,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>870</v>
       </c>
     </row>
     <row r="14">
@@ -12087,22 +12081,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>42.93</v>
+        <v>15.21</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>1512</v>
       </c>
       <c r="D14" t="n">
-        <v>384.91</v>
+        <v>1154.74</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>512.37</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>450</v>
+        <v>120</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -12117,7 +12111,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>300</v>
       </c>
     </row>
     <row r="15">
@@ -12125,13 +12119,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>4.32</v>
+        <v>7.74</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1171.37</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -12140,7 +12134,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -12155,7 +12149,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
     </row>
     <row r="16">
@@ -12163,13 +12157,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.99</v>
+        <v>4.14</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -12178,7 +12172,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -12193,7 +12187,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>630</v>
       </c>
     </row>
     <row r="17">
@@ -12201,13 +12195,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>0.54</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>2772</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -12216,7 +12210,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>3720</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -12239,13 +12233,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -12277,13 +12271,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -12318,10 +12312,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -12394,10 +12388,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -12432,10 +12426,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -12470,10 +12464,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>2376</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -12568,7 +12562,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Dmg</t>
+          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -12677,37 +12671,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3776592.6</v>
+        <v>41234767.2</v>
       </c>
       <c r="C5" t="n">
-        <v>19377666</v>
+        <v>170846676</v>
       </c>
       <c r="D5" t="n">
-        <v>16881334.4</v>
+        <v>148837319.68</v>
       </c>
       <c r="E5" t="n">
-        <v>2139872.06</v>
+        <v>22898460.01</v>
       </c>
       <c r="F5" t="n">
-        <v>4166.7</v>
+        <v>8333.4</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1296713.88</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>122499.3</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>42016.97</v>
+        <v>516725.62</v>
       </c>
     </row>
     <row r="6">
@@ -12715,37 +12709,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>6734376</v>
+        <v>53184542.4</v>
       </c>
       <c r="C6" t="n">
-        <v>19509336</v>
+        <v>120349152</v>
       </c>
       <c r="D6" t="n">
-        <v>15909185.33</v>
+        <v>98140549.89</v>
       </c>
       <c r="E6" t="n">
-        <v>1905557.47</v>
+        <v>7538161.18</v>
       </c>
       <c r="F6" t="n">
-        <v>16666.8</v>
+        <v>4166.7</v>
       </c>
       <c r="G6" t="n">
-        <v>7131.75</v>
+        <v>57831</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>818413.6899999999</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>87499.5</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>73820.77</v>
+        <v>473352.17</v>
       </c>
     </row>
     <row r="7">
@@ -12753,37 +12747,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>5204727</v>
+        <v>44852068.8</v>
       </c>
       <c r="C7" t="n">
-        <v>10256400</v>
+        <v>78059520</v>
       </c>
       <c r="D7" t="n">
-        <v>9472304.08</v>
+        <v>72091914.3</v>
       </c>
       <c r="E7" t="n">
-        <v>1234417.21</v>
+        <v>3738520.7</v>
       </c>
       <c r="F7" t="n">
         <v>25000.2</v>
       </c>
       <c r="G7" t="n">
-        <v>13236.75</v>
+        <v>108558</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>157524.51</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>81666.2</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>48324.6</v>
+        <v>386596.8</v>
       </c>
     </row>
     <row r="8">
@@ -12791,37 +12785,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>2829222</v>
+        <v>18892764</v>
       </c>
       <c r="C8" t="n">
-        <v>3021480</v>
+        <v>33679800</v>
       </c>
       <c r="D8" t="n">
-        <v>3219122.78</v>
+        <v>35882882.32</v>
       </c>
       <c r="E8" t="n">
-        <v>244047.99</v>
+        <v>1301589.27</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>18398.25</v>
+        <v>134920.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>14109.15</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>49583.05</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>23676.23</v>
+        <v>228535.79</v>
       </c>
     </row>
     <row r="9">
@@ -12829,22 +12823,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>1382436</v>
+        <v>1770120</v>
       </c>
       <c r="C9" t="n">
-        <v>970200</v>
+        <v>4546080</v>
       </c>
       <c r="D9" t="n">
-        <v>1127760.34</v>
+        <v>5284362.74</v>
       </c>
       <c r="E9" t="n">
-        <v>355111.55</v>
+        <v>88777.89</v>
       </c>
       <c r="F9" t="n">
-        <v>41667</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>13209</v>
+        <v>30192</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -12859,7 +12853,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>6409.37</v>
+        <v>68213.99000000001</v>
       </c>
     </row>
     <row r="10">
@@ -12867,13 +12861,13 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>848034</v>
+        <v>497376</v>
       </c>
       <c r="C10" t="n">
-        <v>110880</v>
+        <v>914760</v>
       </c>
       <c r="D10" t="n">
-        <v>139640.85</v>
+        <v>1152036.98</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -12882,10 +12876,10 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>7215</v>
+        <v>11100</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>8299.5</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -12897,7 +12891,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>4527.25</v>
+        <v>32948.33</v>
       </c>
     </row>
     <row r="11">
@@ -12905,13 +12899,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>475596</v>
+        <v>456786</v>
       </c>
       <c r="C11" t="n">
-        <v>166320</v>
+        <v>221760</v>
       </c>
       <c r="D11" t="n">
-        <v>216322.93</v>
+        <v>288430.58</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -12920,7 +12914,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2220</v>
+        <v>4440</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -12935,7 +12929,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2826</v>
+        <v>32781.6</v>
       </c>
     </row>
     <row r="12">
@@ -12943,22 +12937,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>345312</v>
+        <v>94644</v>
       </c>
       <c r="C12" t="n">
-        <v>55440</v>
+        <v>138600</v>
       </c>
       <c r="D12" t="n">
-        <v>74394.86</v>
+        <v>185987.16</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>79260.05</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2220</v>
+        <v>6660</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12973,7 +12967,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>847.8</v>
+        <v>18934.2</v>
       </c>
     </row>
     <row r="13">
@@ -12981,13 +12975,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>372240</v>
+        <v>34056</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>83160</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>114300.85</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12996,7 +12990,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2220</v>
+        <v>1665</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13011,7 +13005,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1413</v>
+        <v>8195.4</v>
       </c>
     </row>
     <row r="14">
@@ -13019,22 +13013,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>94446</v>
+        <v>33462</v>
       </c>
       <c r="C14" t="n">
-        <v>27720</v>
+        <v>83160</v>
       </c>
       <c r="D14" t="n">
-        <v>39003.13</v>
+        <v>117009.4</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>94399.05</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>8325</v>
+        <v>2220</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13049,7 +13043,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>5086.8</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="15">
@@ -13057,13 +13051,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>9504</v>
+        <v>17028</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>83160</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>118694.72</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13072,7 +13066,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>3330</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -13087,7 +13081,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>4521.6</v>
       </c>
     </row>
     <row r="16">
@@ -13095,13 +13089,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>2178</v>
+        <v>9108</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13110,7 +13104,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>3330</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -13125,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>5934.6</v>
       </c>
     </row>
     <row r="17">
@@ -13133,13 +13127,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>2772</v>
+        <v>1188</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>194040</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>280886.76</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13148,7 +13142,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>68820</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -13171,13 +13165,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13209,13 +13203,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13250,10 +13244,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13326,10 +13320,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13364,10 +13358,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13402,10 +13396,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>166320</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>240760.08</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13500,7 +13494,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
+          <t>Region: Shikarpur | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -13571,37 +13565,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>33746.4</v>
+        <v>22017.06</v>
       </c>
       <c r="C4" t="n">
-        <v>5820192</v>
+        <v>2242296</v>
       </c>
       <c r="D4" t="n">
-        <v>4573008</v>
+        <v>1761804</v>
       </c>
       <c r="E4" t="n">
-        <v>1446300</v>
+        <v>820800</v>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>96660</v>
+        <v>61770</v>
       </c>
       <c r="H4" t="n">
-        <v>10050</v>
+        <v>4470</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>221460</v>
+        <v>222000</v>
       </c>
     </row>
     <row r="5">
@@ -13609,37 +13603,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>41651.28</v>
+        <v>5543.1</v>
       </c>
       <c r="C5" t="n">
-        <v>5647824</v>
+        <v>433440</v>
       </c>
       <c r="D5" t="n">
-        <v>4437576</v>
+        <v>340560</v>
       </c>
       <c r="E5" t="n">
-        <v>1126800</v>
+        <v>189900</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>102960</v>
+        <v>13050</v>
       </c>
       <c r="H5" t="n">
-        <v>13020</v>
+        <v>1140</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>261210</v>
+        <v>62820</v>
       </c>
     </row>
     <row r="6">
@@ -13647,37 +13641,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>30218.49</v>
+        <v>524.97</v>
       </c>
       <c r="C6" t="n">
-        <v>2431296</v>
+        <v>55944</v>
       </c>
       <c r="D6" t="n">
-        <v>1910304</v>
+        <v>43956</v>
       </c>
       <c r="E6" t="n">
-        <v>242100</v>
+        <v>15300</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>62520</v>
+        <v>1320</v>
       </c>
       <c r="H6" t="n">
-        <v>5190</v>
+        <v>210</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>135810</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="7">
@@ -13685,37 +13679,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>21460.32</v>
+        <v>90.09</v>
       </c>
       <c r="C7" t="n">
-        <v>1419264</v>
+        <v>9072</v>
       </c>
       <c r="D7" t="n">
-        <v>1115136</v>
+        <v>7128</v>
       </c>
       <c r="E7" t="n">
-        <v>95400</v>
+        <v>2700</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>39120</v>
+        <v>30</v>
       </c>
       <c r="H7" t="n">
-        <v>780</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>68400</v>
+        <v>630</v>
       </c>
     </row>
     <row r="8">
@@ -13723,37 +13717,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>8587.620000000001</v>
+        <v>6.3</v>
       </c>
       <c r="C8" t="n">
-        <v>612360</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>481140</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>28800</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>11220</v>
+        <v>60</v>
       </c>
       <c r="H8" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>34170</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9">
@@ -13761,22 +13755,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>804.6</v>
+        <v>0.09</v>
       </c>
       <c r="C9" t="n">
-        <v>82656</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>64944</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1920</v>
+        <v>30</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -13791,7 +13785,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>8940</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
@@ -13799,13 +13793,13 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>226.08</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>16632</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>13068</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -13814,10 +13808,10 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -13829,7 +13823,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3930</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -13837,13 +13831,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>207.63</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>4032</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>3168</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -13852,7 +13846,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -13867,7 +13861,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>3480</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -13875,22 +13869,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>43.02</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -13905,7 +13899,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2010</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -13913,13 +13907,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>15.48</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13928,7 +13922,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13943,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>870</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -13951,22 +13945,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>15.21</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13981,7 +13975,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -13989,13 +13983,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>7.74</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14004,7 +13998,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14019,7 +14013,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14027,13 +14021,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14042,7 +14036,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14057,7 +14051,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>630</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14065,13 +14059,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -14080,7 +14074,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>3720</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -14106,10 +14100,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -14144,10 +14138,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -14182,10 +14176,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14258,10 +14252,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -14296,10 +14290,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -14334,10 +14328,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>3024</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>2376</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -14432,7 +14426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
+          <t>Region: Shikarpur | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -14541,37 +14535,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>18743.08</v>
+        <v>2494.4</v>
       </c>
       <c r="C5" t="n">
-        <v>3106303.2</v>
+        <v>238392</v>
       </c>
       <c r="D5" t="n">
-        <v>1468837.66</v>
+        <v>112725.36</v>
       </c>
       <c r="E5" t="n">
-        <v>124286.04</v>
+        <v>20945.97</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4687.2</v>
+        <v>410.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>54854.1</v>
+        <v>13192.2</v>
       </c>
     </row>
     <row r="6">
@@ -14579,37 +14573,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>24174.79</v>
+        <v>419.98</v>
       </c>
       <c r="C6" t="n">
-        <v>2188166.4</v>
+        <v>50349.6</v>
       </c>
       <c r="D6" t="n">
-        <v>968524.13</v>
+        <v>22285.69</v>
       </c>
       <c r="E6" t="n">
-        <v>40914.9</v>
+        <v>2585.7</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>3126</v>
+        <v>66</v>
       </c>
       <c r="H6" t="n">
-        <v>2958.3</v>
+        <v>119.7</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>50249.7</v>
+        <v>3663</v>
       </c>
     </row>
     <row r="7">
@@ -14617,37 +14611,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>20387.3</v>
+        <v>85.59</v>
       </c>
       <c r="C7" t="n">
-        <v>1419264</v>
+        <v>9072</v>
       </c>
       <c r="D7" t="n">
-        <v>711456.77</v>
+        <v>4547.66</v>
       </c>
       <c r="E7" t="n">
-        <v>20291.58</v>
+        <v>574.29</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>5868</v>
+        <v>4.5</v>
       </c>
       <c r="H7" t="n">
-        <v>569.4</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>41040</v>
+        <v>378</v>
       </c>
     </row>
     <row r="8">
@@ -14655,37 +14649,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>8587.620000000001</v>
+        <v>6.3</v>
       </c>
       <c r="C8" t="n">
-        <v>612360</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>354119.04</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>7064.64</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>7293</v>
+        <v>39</v>
       </c>
       <c r="H8" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>24260.7</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="9">
@@ -14693,22 +14687,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>804.6</v>
+        <v>0.09</v>
       </c>
       <c r="C9" t="n">
-        <v>82656</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>52150.03</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>481.86</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1632</v>
+        <v>25.5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -14723,7 +14717,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>7241.4</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -14731,13 +14725,13 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>226.08</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>16632</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>11369.16</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -14746,10 +14740,10 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -14761,7 +14755,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3497.7</v>
+        <v>160.2</v>
       </c>
     </row>
     <row r="11">
@@ -14769,13 +14763,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>207.63</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>4032</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>2846.45</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -14784,7 +14778,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -14799,7 +14793,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>3480</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -14807,22 +14801,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>43.02</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1835.46</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>430.2</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -14837,7 +14831,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2010</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -14845,13 +14839,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>15.48</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1128.01</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -14860,7 +14854,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -14875,7 +14869,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>870</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -14883,22 +14877,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>15.21</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1154.74</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>512.37</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -14913,7 +14907,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -14921,13 +14915,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>7.74</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1171.37</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14936,7 +14930,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14951,7 +14945,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14959,13 +14953,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14974,7 +14968,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14989,7 +14983,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>630</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14997,13 +14991,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -15012,7 +15006,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>3720</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -15038,10 +15032,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -15076,10 +15070,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -15114,10 +15108,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -15190,10 +15184,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -15228,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -15266,10 +15260,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>3024</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>2376</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -15364,7 +15358,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
+          <t>Region: Shikarpur | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -15473,37 +15467,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>41234767.2</v>
+        <v>5487669</v>
       </c>
       <c r="C5" t="n">
-        <v>170846676</v>
+        <v>13111560</v>
       </c>
       <c r="D5" t="n">
-        <v>148837319.68</v>
+        <v>11422460.73</v>
       </c>
       <c r="E5" t="n">
-        <v>22898460.01</v>
+        <v>3859085.51</v>
       </c>
       <c r="F5" t="n">
-        <v>8333.4</v>
+        <v>5000.04</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1296713.88</v>
+        <v>113537.16</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>122499.3</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>516725.62</v>
+        <v>124270.52</v>
       </c>
     </row>
     <row r="6">
@@ -15511,37 +15505,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>53184542.4</v>
+        <v>923947.2</v>
       </c>
       <c r="C6" t="n">
-        <v>120349152</v>
+        <v>2769228</v>
       </c>
       <c r="D6" t="n">
-        <v>98140549.89</v>
+        <v>2258209.17</v>
       </c>
       <c r="E6" t="n">
-        <v>7538161.18</v>
+        <v>476389.37</v>
       </c>
       <c r="F6" t="n">
-        <v>4166.7</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>57831</v>
+        <v>1221</v>
       </c>
       <c r="H6" t="n">
-        <v>818413.6899999999</v>
+        <v>33115</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>87499.5</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>473352.17</v>
+        <v>34505.46</v>
       </c>
     </row>
     <row r="7">
@@ -15549,37 +15543,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>44852068.8</v>
+        <v>188288.1</v>
       </c>
       <c r="C7" t="n">
-        <v>78059520</v>
+        <v>498960</v>
       </c>
       <c r="D7" t="n">
-        <v>72091914.3</v>
+        <v>460814.79</v>
       </c>
       <c r="E7" t="n">
-        <v>3738520.7</v>
+        <v>105807.19</v>
       </c>
       <c r="F7" t="n">
-        <v>25000.2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>108558</v>
+        <v>83.25</v>
       </c>
       <c r="H7" t="n">
-        <v>157524.51</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>81666.2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>386596.8</v>
+        <v>3560.76</v>
       </c>
     </row>
     <row r="8">
@@ -15587,37 +15581,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>18892764</v>
+        <v>13860</v>
       </c>
       <c r="C8" t="n">
-        <v>33679800</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>35882882.32</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1301589.27</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>134920.5</v>
+        <v>721.5</v>
       </c>
       <c r="H8" t="n">
-        <v>14109.15</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>49583.05</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>228535.79</v>
+        <v>1203.88</v>
       </c>
     </row>
     <row r="9">
@@ -15625,22 +15619,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>1770120</v>
+        <v>198</v>
       </c>
       <c r="C9" t="n">
-        <v>4546080</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>5284362.74</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>88777.89</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>30192</v>
+        <v>471.75</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -15655,7 +15649,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>68213.99000000001</v>
+        <v>686.72</v>
       </c>
     </row>
     <row r="10">
@@ -15663,13 +15657,13 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>497376</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>914760</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1152036.98</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -15678,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>11100</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>8299.5</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -15693,7 +15687,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>32948.33</v>
+        <v>1509.08</v>
       </c>
     </row>
     <row r="11">
@@ -15701,13 +15695,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>456786</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>221760</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>288430.58</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -15716,7 +15710,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>4440</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -15731,4667 +15725,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>32781.6</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>94644</v>
-      </c>
-      <c r="C12" t="n">
-        <v>138600</v>
-      </c>
-      <c r="D12" t="n">
-        <v>185987.16</v>
-      </c>
-      <c r="E12" t="n">
-        <v>79260.05</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>6660</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>18934.2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>34056</v>
-      </c>
-      <c r="C13" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D13" t="n">
-        <v>114300.85</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1665</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>8195.4</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>33462</v>
-      </c>
-      <c r="C14" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D14" t="n">
-        <v>117009.4</v>
-      </c>
-      <c r="E14" t="n">
-        <v>94399.05</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2220</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2826</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>17028</v>
-      </c>
-      <c r="C15" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D15" t="n">
-        <v>118694.72</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>3330</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>4521.6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>9108</v>
-      </c>
-      <c r="C16" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D16" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>3330</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>5934.6</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>1188</v>
-      </c>
-      <c r="C17" t="n">
-        <v>194040</v>
-      </c>
-      <c r="D17" t="n">
-        <v>280886.76</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>68820</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D18" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D19" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D20" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D22" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D23" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>166320</v>
-      </c>
-      <c r="D24" t="n">
-        <v>240760.08</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>5264.82</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1008504</v>
-      </c>
-      <c r="D4" t="n">
-        <v>792396</v>
-      </c>
-      <c r="E4" t="n">
-        <v>275400</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>13350</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3420</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>37980</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>6737.13</v>
-      </c>
-      <c r="C5" t="n">
-        <v>758520</v>
-      </c>
-      <c r="D5" t="n">
-        <v>595980</v>
-      </c>
-      <c r="E5" t="n">
-        <v>150300</v>
-      </c>
-      <c r="F5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" t="n">
-        <v>15360</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1980</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>32700</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>5794.38</v>
-      </c>
-      <c r="C6" t="n">
-        <v>397152</v>
-      </c>
-      <c r="D6" t="n">
-        <v>312048</v>
-      </c>
-      <c r="E6" t="n">
-        <v>73800</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>8460</v>
-      </c>
-      <c r="H6" t="n">
-        <v>390</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>19560</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>4125.51</v>
-      </c>
-      <c r="C7" t="n">
-        <v>213192</v>
-      </c>
-      <c r="D7" t="n">
-        <v>167508</v>
-      </c>
-      <c r="E7" t="n">
-        <v>30600</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4110</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>15450</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2721.78</v>
-      </c>
-      <c r="C8" t="n">
-        <v>69552</v>
-      </c>
-      <c r="D8" t="n">
-        <v>54648</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2700</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2280</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>6120</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1776.78</v>
-      </c>
-      <c r="C9" t="n">
-        <v>30744</v>
-      </c>
-      <c r="D9" t="n">
-        <v>24156</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>450</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>906.66</v>
-      </c>
-      <c r="C10" t="n">
-        <v>6552</v>
-      </c>
-      <c r="D10" t="n">
-        <v>5148</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>240</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>536.67</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3528</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2772</v>
-      </c>
-      <c r="E11" t="n">
-        <v>900</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>401.31</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>366.48</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1584</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>491.85</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D14" t="n">
-        <v>792</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>248.67</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>42.57</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>27.45</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>3031.71</v>
-      </c>
-      <c r="C5" t="n">
-        <v>417186</v>
-      </c>
-      <c r="D5" t="n">
-        <v>197269.38</v>
-      </c>
-      <c r="E5" t="n">
-        <v>16578.09</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>712.8</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>6867</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>4635.5</v>
-      </c>
-      <c r="C6" t="n">
-        <v>357436.8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>158208.34</v>
-      </c>
-      <c r="E6" t="n">
-        <v>12472.2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>423</v>
-      </c>
-      <c r="H6" t="n">
-        <v>222.3</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>7237.2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3919.23</v>
-      </c>
-      <c r="C7" t="n">
-        <v>213192</v>
-      </c>
-      <c r="D7" t="n">
-        <v>106870.1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>6508.62</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G7" t="n">
-        <v>616.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>9270</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2721.78</v>
-      </c>
-      <c r="C8" t="n">
-        <v>69552</v>
-      </c>
-      <c r="D8" t="n">
-        <v>40220.93</v>
-      </c>
-      <c r="E8" t="n">
-        <v>662.3099999999999</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1482</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4345.2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1776.78</v>
-      </c>
-      <c r="C9" t="n">
-        <v>30744</v>
-      </c>
-      <c r="D9" t="n">
-        <v>19397.27</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>382.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>906.66</v>
-      </c>
-      <c r="C10" t="n">
-        <v>6552</v>
-      </c>
-      <c r="D10" t="n">
-        <v>4478.76</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>240</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>186.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>536.67</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3528</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2490.64</v>
-      </c>
-      <c r="E11" t="n">
-        <v>368.82</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>401.31</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1101.28</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>366.48</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1504.01</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>491.85</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D14" t="n">
-        <v>769.8200000000001</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>248.67</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1171.37</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>42.57</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>27.45</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>6669758.7</v>
-      </c>
-      <c r="C5" t="n">
-        <v>22945230</v>
-      </c>
-      <c r="D5" t="n">
-        <v>19989306.28</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3054347.3</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5000.04</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>197196.12</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>64687.14</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>10198108.8</v>
-      </c>
-      <c r="C6" t="n">
-        <v>19659024</v>
-      </c>
-      <c r="D6" t="n">
-        <v>16031250.69</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2297878.13</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>7825.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>61499.29</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>68174.42</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>8622315.9</v>
-      </c>
-      <c r="C7" t="n">
-        <v>11725560</v>
-      </c>
-      <c r="D7" t="n">
-        <v>10829147.64</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1199148.15</v>
-      </c>
-      <c r="F7" t="n">
-        <v>25000.2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>11405.25</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>87323.39999999999</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>5987916</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3825360</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4075586.63</v>
-      </c>
-      <c r="E8" t="n">
-        <v>122023.99</v>
-      </c>
-      <c r="F8" t="n">
-        <v>39583.65</v>
-      </c>
-      <c r="G8" t="n">
-        <v>27417</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>40931.78</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>3908916</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1690920</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1965525.17</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>7076.25</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>9156.24</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1994652</v>
-      </c>
-      <c r="C10" t="n">
-        <v>360360</v>
-      </c>
-      <c r="D10" t="n">
-        <v>453832.75</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>4440</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1760.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1180674</v>
-      </c>
-      <c r="C11" t="n">
-        <v>194040</v>
-      </c>
-      <c r="D11" t="n">
-        <v>252376.75</v>
-      </c>
-      <c r="E11" t="n">
-        <v>67951.39999999999</v>
-      </c>
-      <c r="F11" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>882882</v>
-      </c>
-      <c r="C12" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D12" t="n">
-        <v>111592.3</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>806256</v>
-      </c>
-      <c r="C13" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D13" t="n">
-        <v>152401.13</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>1082070</v>
-      </c>
-      <c r="C14" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D14" t="n">
-        <v>78006.27</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>547074</v>
-      </c>
-      <c r="C15" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D15" t="n">
-        <v>118694.72</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>93654</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>60390</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>22017.06</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2242296</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1761804</v>
-      </c>
-      <c r="E4" t="n">
-        <v>820800</v>
-      </c>
-      <c r="F4" t="n">
-        <v>27</v>
-      </c>
-      <c r="G4" t="n">
-        <v>61770</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4470</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>222000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>5543.1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>433440</v>
-      </c>
-      <c r="D5" t="n">
-        <v>340560</v>
-      </c>
-      <c r="E5" t="n">
-        <v>189900</v>
-      </c>
-      <c r="F5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" t="n">
-        <v>13050</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1140</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>62820</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>524.97</v>
-      </c>
-      <c r="C6" t="n">
-        <v>55944</v>
-      </c>
-      <c r="D6" t="n">
-        <v>43956</v>
-      </c>
-      <c r="E6" t="n">
-        <v>15300</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1320</v>
-      </c>
-      <c r="H6" t="n">
-        <v>210</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>9900</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>90.09</v>
-      </c>
-      <c r="C7" t="n">
-        <v>9072</v>
-      </c>
-      <c r="D7" t="n">
-        <v>7128</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2700</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>30</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>60</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2494.4</v>
-      </c>
-      <c r="C5" t="n">
-        <v>238392</v>
-      </c>
-      <c r="D5" t="n">
-        <v>112725.36</v>
-      </c>
-      <c r="E5" t="n">
-        <v>20945.97</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>410.4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>13192.2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>419.98</v>
-      </c>
-      <c r="C6" t="n">
-        <v>50349.6</v>
-      </c>
-      <c r="D6" t="n">
-        <v>22285.69</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2585.7</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>66</v>
-      </c>
-      <c r="H6" t="n">
-        <v>119.7</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>3663</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>85.59</v>
-      </c>
-      <c r="C7" t="n">
-        <v>9072</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4547.66</v>
-      </c>
-      <c r="E7" t="n">
-        <v>574.29</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>39</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>127.8</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>72.90000000000001</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>160.2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>30</v>
+        <v>282.6</v>
       </c>
     </row>
     <row r="12">
@@ -21876,938 +17210,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>5487669</v>
-      </c>
-      <c r="C5" t="n">
-        <v>13111560</v>
-      </c>
-      <c r="D5" t="n">
-        <v>11422460.73</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3859085.51</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5000.04</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>113537.16</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>124270.52</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>923947.2</v>
-      </c>
-      <c r="C6" t="n">
-        <v>2769228</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2258209.17</v>
-      </c>
-      <c r="E6" t="n">
-        <v>476389.37</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1221</v>
-      </c>
-      <c r="H6" t="n">
-        <v>33115</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>34505.46</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>188288.1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>498960</v>
-      </c>
-      <c r="D7" t="n">
-        <v>460814.79</v>
-      </c>
-      <c r="E7" t="n">
-        <v>105807.19</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>83.25</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3560.76</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>13860</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>721.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1203.88</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>198</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>471.75</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>686.72</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1509.08</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>282.6</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/risk/Risk_Analysis_T3_25yrs_Present_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_25yrs_Present_Breaches.xlsx
@@ -538,7 +538,7 @@
         <v>74790</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J4" t="n">
         <v>35</v>
@@ -576,7 +576,7 @@
         <v>66780</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
         <v>20</v>
@@ -614,7 +614,7 @@
         <v>19380</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
         <v>12</v>
@@ -690,7 +690,7 @@
         <v>5790</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>5</v>
@@ -804,7 +804,7 @@
         <v>810</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
@@ -1546,7 +1546,7 @@
         <v>5700</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
@@ -1622,7 +1622,7 @@
         <v>5460</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>2</v>
@@ -1736,7 +1736,7 @@
         <v>780</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -2478,7 +2478,7 @@
         <v>3249</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -2554,7 +2554,7 @@
         <v>4641</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="J8" t="n">
         <v>1.7</v>
@@ -2668,7 +2668,7 @@
         <v>780</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
         <v>898835.85</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>134165.5</v>
       </c>
       <c r="J6" t="n">
         <v>58333</v>
@@ -3486,7 +3486,7 @@
         <v>1283932.65</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>551995.2</v>
       </c>
       <c r="J8" t="n">
         <v>99166.10000000001</v>
@@ -3600,7 +3600,7 @@
         <v>215787</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -9858,7 +9858,7 @@
         <v>10050</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
         <v>9</v>
@@ -9896,7 +9896,7 @@
         <v>13020</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>7</v>
@@ -9934,7 +9934,7 @@
         <v>5190</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
@@ -10010,7 +10010,7 @@
         <v>60</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -10828,7 +10828,7 @@
         <v>24040.8</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J5" t="n">
         <v>6</v>
@@ -10866,7 +10866,7 @@
         <v>11046.6</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="J6" t="n">
         <v>6</v>
@@ -10942,7 +10942,7 @@
         <v>4921.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="J8" t="n">
         <v>4.25</v>
@@ -11056,7 +11056,7 @@
         <v>810</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
@@ -11760,7 +11760,7 @@
         <v>4687.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="J5" t="n">
         <v>2.1</v>
@@ -11798,7 +11798,7 @@
         <v>2958.3</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
         <v>1.5</v>
@@ -11874,7 +11874,7 @@
         <v>51</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="J8" t="n">
         <v>0.85</v>
@@ -12692,7 +12692,7 @@
         <v>1296713.88</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>57499.5</v>
       </c>
       <c r="J5" t="n">
         <v>122499.3</v>
@@ -12730,7 +12730,7 @@
         <v>818413.6899999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>268331</v>
       </c>
       <c r="J6" t="n">
         <v>87499.5</v>
@@ -12806,7 +12806,7 @@
         <v>14109.15</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>275997.6</v>
       </c>
       <c r="J8" t="n">
         <v>49583.05</v>
@@ -13586,7 +13586,7 @@
         <v>4470</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
@@ -16420,7 +16420,7 @@
         <v>6650887.32</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>114999</v>
       </c>
       <c r="J5" t="n">
         <v>349998</v>
@@ -16458,7 +16458,7 @@
         <v>3056041.89</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>402496.5</v>
       </c>
       <c r="J6" t="n">
         <v>349998</v>
@@ -16534,7 +16534,7 @@
         <v>1361532.98</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>827992.8</v>
       </c>
       <c r="J8" t="n">
         <v>247915.25</v>
@@ -16648,7 +16648,7 @@
         <v>224086.5</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J11" t="n">
         <v>116666</v>
@@ -17314,7 +17314,7 @@
         <v>20130</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>6</v>
@@ -17352,7 +17352,7 @@
         <v>17790</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>6</v>
@@ -18284,7 +18284,7 @@
         <v>6404.4</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="J5" t="n">
         <v>1.8</v>
@@ -19216,7 +19216,7 @@
         <v>1771777.26</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>57499.5</v>
       </c>
       <c r="J5" t="n">
         <v>104999.4</v>
@@ -20110,7 +20110,7 @@
         <v>27900</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>10</v>

--- a/risk/Risk_Analysis_T3_25yrs_Present_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_25yrs_Present_Breaches.xlsx
@@ -544,7 +544,7 @@
         <v>35</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="L4" t="n">
         <v>1267410</v>
@@ -582,7 +582,7 @@
         <v>20</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>691</v>
       </c>
       <c r="L5" t="n">
         <v>921990</v>
@@ -620,7 +620,7 @@
         <v>12</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>422</v>
       </c>
       <c r="L6" t="n">
         <v>579720</v>
@@ -658,7 +658,7 @@
         <v>9</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>317</v>
       </c>
       <c r="L7" t="n">
         <v>347400</v>
@@ -696,7 +696,7 @@
         <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="L8" t="n">
         <v>244680</v>
@@ -734,7 +734,7 @@
         <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="L9" t="n">
         <v>189930</v>
@@ -772,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="L10" t="n">
         <v>97260</v>
@@ -810,7 +810,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="L11" t="n">
         <v>45090</v>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L12" t="n">
         <v>17040</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
         <v>6480</v>
@@ -962,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
         <v>4110</v>
@@ -1476,7 +1476,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L4" t="n">
         <v>34980</v>
@@ -1514,7 +1514,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="L5" t="n">
         <v>50970</v>
@@ -1552,7 +1552,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L6" t="n">
         <v>55560</v>
@@ -1590,7 +1590,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L7" t="n">
         <v>49710</v>
@@ -1628,7 +1628,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="L8" t="n">
         <v>73560</v>
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="L9" t="n">
         <v>93630</v>
@@ -1704,7 +1704,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L10" t="n">
         <v>50190</v>
@@ -1742,7 +1742,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L11" t="n">
         <v>23430</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L12" t="n">
         <v>11010</v>
@@ -1818,7 +1818,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
         <v>4020</v>
@@ -1894,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>3330</v>
@@ -2446,7 +2446,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>13.02</v>
       </c>
       <c r="L5" t="n">
         <v>10703.7</v>
@@ -2484,7 +2484,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>22.1</v>
       </c>
       <c r="L6" t="n">
         <v>20557.2</v>
@@ -2522,7 +2522,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>18.04</v>
       </c>
       <c r="L7" t="n">
         <v>29826</v>
@@ -2560,7 +2560,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>27.9</v>
       </c>
       <c r="L8" t="n">
         <v>52227.6</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="L9" t="n">
         <v>75840.3</v>
@@ -2636,7 +2636,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L10" t="n">
         <v>44669.1</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L11" t="n">
         <v>23430</v>
@@ -2712,7 +2712,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L12" t="n">
         <v>11010</v>
@@ -2750,7 +2750,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
         <v>4020</v>
@@ -2826,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>3330</v>
@@ -3378,7 +3378,7 @@
         <v>17499.9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>277768.68</v>
       </c>
       <c r="L5" t="n">
         <v>100828.85</v>
@@ -3416,7 +3416,7 @@
         <v>58333</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>471481.4</v>
       </c>
       <c r="L6" t="n">
         <v>193648.82</v>
@@ -3454,7 +3454,7 @@
         <v>122499.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>384865.36</v>
       </c>
       <c r="L7" t="n">
         <v>280960.92</v>
@@ -3492,7 +3492,7 @@
         <v>99166.10000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>595218.6</v>
       </c>
       <c r="L8" t="n">
         <v>491983.99</v>
@@ -3530,7 +3530,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1045366</v>
       </c>
       <c r="L9" t="n">
         <v>714415.63</v>
@@ -3568,7 +3568,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>554684</v>
       </c>
       <c r="L10" t="n">
         <v>420782.92</v>
@@ -3606,7 +3606,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>234674</v>
       </c>
       <c r="L11" t="n">
         <v>220710.6</v>
@@ -3644,7 +3644,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>149338</v>
       </c>
       <c r="L12" t="n">
         <v>103714.2</v>
@@ -3682,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L13" t="n">
         <v>37868.4</v>
@@ -3758,7 +3758,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L15" t="n">
         <v>31368.6</v>
@@ -4272,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L4" t="n">
         <v>102810</v>
@@ -4310,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L5" t="n">
         <v>34950</v>
@@ -4348,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
         <v>8190</v>
@@ -5242,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="L5" t="n">
         <v>7339.5</v>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="L6" t="n">
         <v>3030.3</v>
@@ -6174,7 +6174,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>134404.2</v>
       </c>
       <c r="L5" t="n">
         <v>69138.09</v>
@@ -6212,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>27734.2</v>
       </c>
       <c r="L6" t="n">
         <v>28545.43</v>
@@ -7068,7 +7068,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="L4" t="n">
         <v>53250</v>
@@ -7106,7 +7106,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L5" t="n">
         <v>13650</v>
@@ -7144,7 +7144,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
         <v>2640</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>510</v>
@@ -8038,7 +8038,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="L5" t="n">
         <v>2866.5</v>
@@ -8076,7 +8076,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="L6" t="n">
         <v>976.8</v>
@@ -8114,7 +8114,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="L7" t="n">
         <v>306</v>
@@ -8970,7 +8970,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>71682.24000000001</v>
       </c>
       <c r="L5" t="n">
         <v>27002.43</v>
@@ -9008,7 +9008,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>41601.3</v>
       </c>
       <c r="L6" t="n">
         <v>9201.459999999999</v>
@@ -9046,7 +9046,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>34987.76</v>
       </c>
       <c r="L7" t="n">
         <v>2882.52</v>
@@ -9864,7 +9864,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="L4" t="n">
         <v>221460</v>
@@ -9902,7 +9902,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="L5" t="n">
         <v>261210</v>
@@ -9940,7 +9940,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="L6" t="n">
         <v>135810</v>
@@ -9978,7 +9978,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L7" t="n">
         <v>68400</v>
@@ -10016,7 +10016,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="L8" t="n">
         <v>34170</v>
@@ -10054,7 +10054,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
         <v>8940</v>
@@ -10282,7 +10282,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>480</v>
@@ -10834,7 +10834,7 @@
         <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>290.22</v>
       </c>
       <c r="L5" t="n">
         <v>193617.9</v>
@@ -10872,7 +10872,7 @@
         <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>274.3</v>
       </c>
       <c r="L6" t="n">
         <v>214496.4</v>
@@ -10910,7 +10910,7 @@
         <v>6.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>259.94</v>
       </c>
       <c r="L7" t="n">
         <v>208440</v>
@@ -10948,7 +10948,7 @@
         <v>4.25</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>174.6</v>
       </c>
       <c r="L8" t="n">
         <v>173722.8</v>
@@ -10986,7 +10986,7 @@
         <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="L9" t="n">
         <v>153843.3</v>
@@ -11024,7 +11024,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="L10" t="n">
         <v>86561.39999999999</v>
@@ -11062,7 +11062,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="L11" t="n">
         <v>45090</v>
@@ -11100,7 +11100,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L12" t="n">
         <v>17040</v>
@@ -11138,7 +11138,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
         <v>6480</v>
@@ -11214,7 +11214,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
         <v>4110</v>
@@ -11766,7 +11766,7 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>110.46</v>
       </c>
       <c r="L5" t="n">
         <v>54854.1</v>
@@ -11804,7 +11804,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="L6" t="n">
         <v>50249.7</v>
@@ -11842,7 +11842,7 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="L7" t="n">
         <v>41040</v>
@@ -11880,7 +11880,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>27.9</v>
       </c>
       <c r="L8" t="n">
         <v>24260.7</v>
@@ -11918,7 +11918,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
         <v>7241.4</v>
@@ -12146,7 +12146,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>480</v>
@@ -12698,7 +12698,7 @@
         <v>122499.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2356553.64</v>
       </c>
       <c r="L5" t="n">
         <v>516725.62</v>
@@ -12736,7 +12736,7 @@
         <v>87499.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1664052</v>
       </c>
       <c r="L6" t="n">
         <v>473352.17</v>
@@ -12774,7 +12774,7 @@
         <v>81666.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1399510.4</v>
       </c>
       <c r="L7" t="n">
         <v>386596.8</v>
@@ -12812,7 +12812,7 @@
         <v>49583.05</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>595218.6</v>
       </c>
       <c r="L8" t="n">
         <v>228535.79</v>
@@ -12850,7 +12850,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>149338</v>
       </c>
       <c r="L9" t="n">
         <v>68213.99000000001</v>
@@ -13078,7 +13078,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L15" t="n">
         <v>4521.6</v>
@@ -13592,7 +13592,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="L4" t="n">
         <v>222000</v>
@@ -13630,7 +13630,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L5" t="n">
         <v>62820</v>
@@ -14562,7 +14562,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>7.98</v>
       </c>
       <c r="L5" t="n">
         <v>13192.2</v>
@@ -15494,7 +15494,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>170245.32</v>
       </c>
       <c r="L5" t="n">
         <v>124270.52</v>
@@ -16426,7 +16426,7 @@
         <v>349998</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>6191553.48</v>
       </c>
       <c r="L5" t="n">
         <v>1823880.62</v>
@@ -16464,7 +16464,7 @@
         <v>349998</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>5851916.2</v>
       </c>
       <c r="L6" t="n">
         <v>2020556.09</v>
@@ -16502,7 +16502,7 @@
         <v>367497.9</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>5545559.96</v>
       </c>
       <c r="L7" t="n">
         <v>1963504.8</v>
@@ -16540,7 +16540,7 @@
         <v>247915.25</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3724916.4</v>
       </c>
       <c r="L8" t="n">
         <v>1636468.78</v>
@@ -16578,7 +16578,7 @@
         <v>221665.4</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3221434</v>
       </c>
       <c r="L9" t="n">
         <v>1449203.89</v>
@@ -16616,7 +16616,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1642718</v>
       </c>
       <c r="L10" t="n">
         <v>815408.39</v>
@@ -16654,7 +16654,7 @@
         <v>116666</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>618686</v>
       </c>
       <c r="L11" t="n">
         <v>424747.8</v>
@@ -16692,7 +16692,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>234674</v>
       </c>
       <c r="L12" t="n">
         <v>160516.8</v>
@@ -16730,7 +16730,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L13" t="n">
         <v>61041.6</v>
@@ -16806,7 +16806,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>64002</v>
       </c>
       <c r="L15" t="n">
         <v>38716.2</v>
@@ -17320,7 +17320,7 @@
         <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="L4" t="n">
         <v>211470</v>
@@ -17358,7 +17358,7 @@
         <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="L5" t="n">
         <v>270240</v>
@@ -17396,7 +17396,7 @@
         <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="L6" t="n">
         <v>260910</v>
@@ -17434,7 +17434,7 @@
         <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="L7" t="n">
         <v>192540</v>
@@ -17472,7 +17472,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="L8" t="n">
         <v>123420</v>
@@ -17510,7 +17510,7 @@
         <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="L9" t="n">
         <v>83850</v>
@@ -17548,7 +17548,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="L10" t="n">
         <v>41490</v>
@@ -17586,7 +17586,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L11" t="n">
         <v>17550</v>
@@ -17624,7 +17624,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
         <v>3930</v>
@@ -17738,7 +17738,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>300</v>
@@ -18290,7 +18290,7 @@
         <v>1.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>91.14</v>
       </c>
       <c r="L5" t="n">
         <v>56750.4</v>
@@ -18328,7 +18328,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>140.4</v>
       </c>
       <c r="L6" t="n">
         <v>96536.7</v>
@@ -18366,7 +18366,7 @@
         <v>2.8</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>170.56</v>
       </c>
       <c r="L7" t="n">
         <v>115524</v>
@@ -18404,7 +18404,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>117.9</v>
       </c>
       <c r="L8" t="n">
         <v>87628.2</v>
@@ -18442,7 +18442,7 @@
         <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="L9" t="n">
         <v>67918.5</v>
@@ -18480,7 +18480,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="L10" t="n">
         <v>36926.1</v>
@@ -18518,7 +18518,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L11" t="n">
         <v>17550</v>
@@ -18556,7 +18556,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
         <v>3930</v>
@@ -18670,7 +18670,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>300</v>
@@ -19222,7 +19222,7 @@
         <v>104999.4</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1944380.76</v>
       </c>
       <c r="L5" t="n">
         <v>534588.77</v>
@@ -19260,7 +19260,7 @@
         <v>174999</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2995293.6</v>
       </c>
       <c r="L6" t="n">
         <v>909375.71</v>
@@ -19298,7 +19298,7 @@
         <v>163332.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3638727.04</v>
       </c>
       <c r="L7" t="n">
         <v>1088236.08</v>
@@ -19336,7 +19336,7 @@
         <v>99166.10000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2515278.6</v>
       </c>
       <c r="L8" t="n">
         <v>825457.64</v>
@@ -19374,7 +19374,7 @@
         <v>221665.4</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1984062</v>
       </c>
       <c r="L9" t="n">
         <v>639792.27</v>
@@ -19412,7 +19412,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1088034</v>
       </c>
       <c r="L10" t="n">
         <v>347843.86</v>
@@ -19450,7 +19450,7 @@
         <v>116666</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>384012</v>
       </c>
       <c r="L11" t="n">
         <v>165321</v>
@@ -19488,7 +19488,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>85336</v>
       </c>
       <c r="L12" t="n">
         <v>37020.6</v>
@@ -19602,7 +19602,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L15" t="n">
         <v>2826</v>
@@ -20116,7 +20116,7 @@
         <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="L4" t="n">
         <v>358740</v>
@@ -20154,7 +20154,7 @@
         <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="L5" t="n">
         <v>165450</v>
@@ -20192,7 +20192,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="L6" t="n">
         <v>61560</v>
@@ -20230,7 +20230,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
         <v>8640</v>
@@ -21086,7 +21086,7 @@
         <v>1.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>56.7</v>
       </c>
       <c r="L5" t="n">
         <v>34744.5</v>
@@ -21124,7 +21124,7 @@
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>29.9</v>
       </c>
       <c r="L6" t="n">
         <v>22777.2</v>
@@ -21162,7 +21162,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="L7" t="n">
         <v>5184</v>
@@ -22018,7 +22018,7 @@
         <v>104999.4</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1209637.8</v>
       </c>
       <c r="L5" t="n">
         <v>327293.19</v>
@@ -22056,7 +22056,7 @@
         <v>29166.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>637886.6</v>
       </c>
       <c r="L6" t="n">
         <v>214561.22</v>
@@ -22094,7 +22094,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>69975.52</v>
       </c>
       <c r="L7" t="n">
         <v>48833.28</v>

--- a/risk/Risk_Analysis_T3_25yrs_Present_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_25yrs_Present_Breaches.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,13 +511,18 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>153936.45</v>
+        <v>153787.32</v>
       </c>
       <c r="C4" t="n">
         <v>29986992</v>
@@ -532,7 +537,7 @@
         <v>160</v>
       </c>
       <c r="G4" t="n">
-        <v>474210</v>
+        <v>471870</v>
       </c>
       <c r="H4" t="n">
         <v>74790</v>
@@ -544,10 +549,13 @@
         <v>35</v>
       </c>
       <c r="K4" t="n">
-        <v>880</v>
+        <v>873</v>
       </c>
       <c r="L4" t="n">
-        <v>1267410</v>
+        <v>1264650</v>
+      </c>
+      <c r="M4" t="n">
+        <v>69390</v>
       </c>
     </row>
     <row r="5">
@@ -555,7 +563,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>115029.09</v>
+        <v>114903.81</v>
       </c>
       <c r="C5" t="n">
         <v>18902016</v>
@@ -570,7 +578,7 @@
         <v>78</v>
       </c>
       <c r="G5" t="n">
-        <v>354960</v>
+        <v>353460</v>
       </c>
       <c r="H5" t="n">
         <v>66780</v>
@@ -582,10 +590,13 @@
         <v>20</v>
       </c>
       <c r="K5" t="n">
-        <v>691</v>
+        <v>682</v>
       </c>
       <c r="L5" t="n">
-        <v>921990</v>
+        <v>919980</v>
+      </c>
+      <c r="M5" t="n">
+        <v>42990</v>
       </c>
     </row>
     <row r="6">
@@ -593,7 +604,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>84266.73</v>
+        <v>84143.07000000001</v>
       </c>
       <c r="C6" t="n">
         <v>10298232</v>
@@ -608,7 +619,7 @@
         <v>29</v>
       </c>
       <c r="G6" t="n">
-        <v>241500</v>
+        <v>240750</v>
       </c>
       <c r="H6" t="n">
         <v>19380</v>
@@ -620,10 +631,13 @@
         <v>12</v>
       </c>
       <c r="K6" t="n">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L6" t="n">
-        <v>579720</v>
+        <v>577980</v>
+      </c>
+      <c r="M6" t="n">
+        <v>20760</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +645,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>66179.16</v>
+        <v>66134.16</v>
       </c>
       <c r="C7" t="n">
         <v>6491016</v>
@@ -646,7 +660,7 @@
         <v>17</v>
       </c>
       <c r="G7" t="n">
-        <v>148770</v>
+        <v>148320</v>
       </c>
       <c r="H7" t="n">
         <v>5640</v>
@@ -661,7 +675,10 @@
         <v>317</v>
       </c>
       <c r="L7" t="n">
-        <v>347400</v>
+        <v>346380</v>
+      </c>
+      <c r="M7" t="n">
+        <v>13350</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +686,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>43910.73</v>
+        <v>43910.46</v>
       </c>
       <c r="C8" t="n">
         <v>3736656</v>
@@ -684,7 +701,7 @@
         <v>27</v>
       </c>
       <c r="G8" t="n">
-        <v>115620</v>
+        <v>115170</v>
       </c>
       <c r="H8" t="n">
         <v>5790</v>
@@ -699,7 +716,10 @@
         <v>194</v>
       </c>
       <c r="L8" t="n">
-        <v>244680</v>
+        <v>243990</v>
+      </c>
+      <c r="M8" t="n">
+        <v>8790</v>
       </c>
     </row>
     <row r="9">
@@ -707,7 +727,7 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>27650.7</v>
+        <v>27650.61</v>
       </c>
       <c r="C9" t="n">
         <v>2046240</v>
@@ -722,7 +742,7 @@
         <v>27</v>
       </c>
       <c r="G9" t="n">
-        <v>72420</v>
+        <v>72090</v>
       </c>
       <c r="H9" t="n">
         <v>3270</v>
@@ -737,7 +757,10 @@
         <v>151</v>
       </c>
       <c r="L9" t="n">
-        <v>189930</v>
+        <v>189570</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4920</v>
       </c>
     </row>
     <row r="10">
@@ -745,7 +768,7 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>17051.58</v>
+        <v>17051.31</v>
       </c>
       <c r="C10" t="n">
         <v>1049832</v>
@@ -775,7 +798,10 @@
         <v>77</v>
       </c>
       <c r="L10" t="n">
-        <v>97260</v>
+        <v>97170</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3360</v>
       </c>
     </row>
     <row r="11">
@@ -813,7 +839,10 @@
         <v>29</v>
       </c>
       <c r="L11" t="n">
-        <v>45090</v>
+        <v>44790</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2610</v>
       </c>
     </row>
     <row r="12">
@@ -851,7 +880,10 @@
         <v>11</v>
       </c>
       <c r="L12" t="n">
-        <v>17040</v>
+        <v>16860</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1590</v>
       </c>
     </row>
     <row r="13">
@@ -891,6 +923,9 @@
       <c r="L13" t="n">
         <v>6480</v>
       </c>
+      <c r="M13" t="n">
+        <v>960</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -929,6 +964,9 @@
       <c r="L14" t="n">
         <v>2790</v>
       </c>
+      <c r="M14" t="n">
+        <v>390</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -967,6 +1005,9 @@
       <c r="L15" t="n">
         <v>4110</v>
       </c>
+      <c r="M15" t="n">
+        <v>2490</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1005,6 +1046,9 @@
       <c r="L16" t="n">
         <v>1920</v>
       </c>
+      <c r="M16" t="n">
+        <v>840</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1043,6 +1087,9 @@
       <c r="L17" t="n">
         <v>150</v>
       </c>
+      <c r="M17" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1081,6 +1128,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1119,6 +1169,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1157,6 +1210,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1195,6 +1251,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1233,6 +1292,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1271,6 +1333,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1309,6 +1374,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -1358,6 +1426,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -1372,7 +1444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1443,6 +1515,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1464,7 +1541,7 @@
         <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>10080</v>
+        <v>10320</v>
       </c>
       <c r="H4" t="n">
         <v>3300</v>
@@ -1479,7 +1556,10 @@
         <v>26</v>
       </c>
       <c r="L4" t="n">
-        <v>34980</v>
+        <v>35160</v>
+      </c>
+      <c r="M4" t="n">
+        <v>11520</v>
       </c>
     </row>
     <row r="5">
@@ -1487,7 +1567,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3122.01</v>
+        <v>3121.92</v>
       </c>
       <c r="C5" t="n">
         <v>831600</v>
@@ -1502,7 +1582,7 @@
         <v>11</v>
       </c>
       <c r="G5" t="n">
-        <v>18690</v>
+        <v>18750</v>
       </c>
       <c r="H5" t="n">
         <v>2970</v>
@@ -1517,7 +1597,10 @@
         <v>31</v>
       </c>
       <c r="L5" t="n">
-        <v>50970</v>
+        <v>51270</v>
+      </c>
+      <c r="M5" t="n">
+        <v>13890</v>
       </c>
     </row>
     <row r="6">
@@ -1540,7 +1623,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>23640</v>
+        <v>23610</v>
       </c>
       <c r="H6" t="n">
         <v>5700</v>
@@ -1555,7 +1638,10 @@
         <v>34</v>
       </c>
       <c r="L6" t="n">
-        <v>55560</v>
+        <v>55590</v>
+      </c>
+      <c r="M6" t="n">
+        <v>7140</v>
       </c>
     </row>
     <row r="7">
@@ -1578,7 +1664,7 @@
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>16140</v>
+        <v>16170</v>
       </c>
       <c r="H7" t="n">
         <v>3540</v>
@@ -1594,6 +1680,9 @@
       </c>
       <c r="L7" t="n">
         <v>49710</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3870</v>
       </c>
     </row>
     <row r="8">
@@ -1616,7 +1705,7 @@
         <v>13</v>
       </c>
       <c r="G8" t="n">
-        <v>28890</v>
+        <v>28920</v>
       </c>
       <c r="H8" t="n">
         <v>5460</v>
@@ -1631,7 +1720,10 @@
         <v>31</v>
       </c>
       <c r="L8" t="n">
-        <v>73560</v>
+        <v>73890</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1860</v>
       </c>
     </row>
     <row r="9">
@@ -1669,7 +1761,10 @@
         <v>49</v>
       </c>
       <c r="L9" t="n">
-        <v>93630</v>
+        <v>93600</v>
+      </c>
+      <c r="M9" t="n">
+        <v>720</v>
       </c>
     </row>
     <row r="10">
@@ -1707,7 +1802,10 @@
         <v>26</v>
       </c>
       <c r="L10" t="n">
-        <v>50190</v>
+        <v>50310</v>
+      </c>
+      <c r="M10" t="n">
+        <v>450</v>
       </c>
     </row>
     <row r="11">
@@ -1730,7 +1828,7 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>10020</v>
+        <v>10050</v>
       </c>
       <c r="H11" t="n">
         <v>780</v>
@@ -1745,7 +1843,10 @@
         <v>11</v>
       </c>
       <c r="L11" t="n">
-        <v>23430</v>
+        <v>23490</v>
+      </c>
+      <c r="M11" t="n">
+        <v>390</v>
       </c>
     </row>
     <row r="12">
@@ -1783,7 +1884,10 @@
         <v>7</v>
       </c>
       <c r="L12" t="n">
-        <v>11010</v>
+        <v>11040</v>
+      </c>
+      <c r="M12" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="13">
@@ -1823,6 +1927,9 @@
       <c r="L13" t="n">
         <v>4020</v>
       </c>
+      <c r="M13" t="n">
+        <v>720</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1861,6 +1968,9 @@
       <c r="L14" t="n">
         <v>1440</v>
       </c>
+      <c r="M14" t="n">
+        <v>330</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1899,6 +2009,9 @@
       <c r="L15" t="n">
         <v>3330</v>
       </c>
+      <c r="M15" t="n">
+        <v>2340</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1937,6 +2050,9 @@
       <c r="L16" t="n">
         <v>1230</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1975,6 +2091,9 @@
       <c r="L17" t="n">
         <v>60</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2013,6 +2132,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2051,6 +2173,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2089,6 +2214,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2127,6 +2255,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2165,6 +2296,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2203,6 +2337,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2241,6 +2378,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -2290,6 +2430,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -2304,7 +2448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2375,6 +2519,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2411,6 +2560,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2419,7 +2571,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>1404.9</v>
+        <v>1404.86</v>
       </c>
       <c r="C5" t="n">
         <v>457380</v>
@@ -2446,10 +2598,13 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>13.02</v>
+        <v>10.26</v>
       </c>
       <c r="L5" t="n">
-        <v>10703.7</v>
+        <v>10766.7</v>
+      </c>
+      <c r="M5" t="n">
+        <v>277.8</v>
       </c>
     </row>
     <row r="6">
@@ -2472,22 +2627,25 @@
         <v>0.5</v>
       </c>
       <c r="G6" t="n">
-        <v>1182</v>
+        <v>1180.5</v>
       </c>
       <c r="H6" t="n">
         <v>3249</v>
       </c>
       <c r="I6" t="n">
-        <v>0.35</v>
+        <v>0.51</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>22.1</v>
+        <v>17.24</v>
       </c>
       <c r="L6" t="n">
-        <v>20557.2</v>
+        <v>20568.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>571.2</v>
       </c>
     </row>
     <row r="7">
@@ -2510,7 +2668,7 @@
         <v>1.2</v>
       </c>
       <c r="G7" t="n">
-        <v>2421</v>
+        <v>2425.5</v>
       </c>
       <c r="H7" t="n">
         <v>2584.2</v>
@@ -2522,10 +2680,13 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>18.04</v>
+        <v>14.04</v>
       </c>
       <c r="L7" t="n">
         <v>29826</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1354.5</v>
       </c>
     </row>
     <row r="8">
@@ -2548,22 +2709,25 @@
         <v>12.35</v>
       </c>
       <c r="G8" t="n">
-        <v>18778.5</v>
+        <v>18798</v>
       </c>
       <c r="H8" t="n">
         <v>4641</v>
       </c>
       <c r="I8" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="J8" t="n">
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>27.9</v>
+        <v>22.82</v>
       </c>
       <c r="L8" t="n">
-        <v>52227.6</v>
+        <v>52461.9</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1116</v>
       </c>
     </row>
     <row r="9">
@@ -2598,10 +2762,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>49</v>
+        <v>39.35</v>
       </c>
       <c r="L9" t="n">
-        <v>75840.3</v>
+        <v>75816</v>
+      </c>
+      <c r="M9" t="n">
+        <v>720</v>
       </c>
     </row>
     <row r="10">
@@ -2636,10 +2803,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>26</v>
+        <v>22.62</v>
       </c>
       <c r="L10" t="n">
-        <v>44669.1</v>
+        <v>44775.9</v>
+      </c>
+      <c r="M10" t="n">
+        <v>450</v>
       </c>
     </row>
     <row r="11">
@@ -2662,22 +2832,25 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>10020</v>
+        <v>10050</v>
       </c>
       <c r="H11" t="n">
         <v>780</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>11</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>23430</v>
+        <v>23490</v>
+      </c>
+      <c r="M11" t="n">
+        <v>390</v>
       </c>
     </row>
     <row r="12">
@@ -2712,10 +2885,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>7</v>
+        <v>6.49</v>
       </c>
       <c r="L12" t="n">
-        <v>11010</v>
+        <v>11040</v>
+      </c>
+      <c r="M12" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="13">
@@ -2750,10 +2926,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="L13" t="n">
         <v>4020</v>
+      </c>
+      <c r="M13" t="n">
+        <v>720</v>
       </c>
     </row>
     <row r="14">
@@ -2793,6 +2972,9 @@
       <c r="L14" t="n">
         <v>1440</v>
       </c>
+      <c r="M14" t="n">
+        <v>330</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2826,10 +3008,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="L15" t="n">
         <v>3330</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2340</v>
       </c>
     </row>
     <row r="16">
@@ -2869,6 +3054,9 @@
       <c r="L16" t="n">
         <v>1230</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2907,6 +3095,9 @@
       <c r="L17" t="n">
         <v>60</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2945,6 +3136,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2983,6 +3177,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3021,6 +3218,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3059,6 +3259,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3097,6 +3300,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3135,6 +3341,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3173,6 +3382,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -3222,6 +3434,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -3236,7 +3452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3307,6 +3523,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3343,6 +3564,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3351,16 +3575,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3090789.9</v>
+        <v>3090700.8</v>
       </c>
       <c r="C5" t="n">
-        <v>25155900</v>
+        <v>19209960</v>
       </c>
       <c r="D5" t="n">
-        <v>21915186.28</v>
+        <v>41524876.8</v>
       </c>
       <c r="E5" t="n">
-        <v>10370149.22</v>
+        <v>19418701.05</v>
       </c>
       <c r="F5" t="n">
         <v>9166.74</v>
@@ -3369,19 +3593,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>295794.18</v>
+        <v>6094440</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>17499.9</v>
+        <v>7283.4</v>
       </c>
       <c r="K5" t="n">
-        <v>277768.68</v>
+        <v>498233.12</v>
       </c>
       <c r="L5" t="n">
-        <v>100828.85</v>
+        <v>1938006</v>
+      </c>
+      <c r="M5" t="n">
+        <v>83340</v>
       </c>
     </row>
     <row r="6">
@@ -3392,34 +3619,37 @@
         <v>10008820.8</v>
       </c>
       <c r="C6" t="n">
-        <v>44182908</v>
+        <v>33739675.2</v>
       </c>
       <c r="D6" t="n">
-        <v>36029625.59</v>
+        <v>68268904.7</v>
       </c>
       <c r="E6" t="n">
-        <v>13899360.38</v>
+        <v>26027352</v>
       </c>
       <c r="F6" t="n">
         <v>20833.5</v>
       </c>
       <c r="G6" t="n">
-        <v>21867</v>
+        <v>63747</v>
       </c>
       <c r="H6" t="n">
-        <v>898835.85</v>
+        <v>18519300</v>
       </c>
       <c r="I6" t="n">
-        <v>134165.5</v>
+        <v>98471.57000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>58333</v>
+        <v>24278</v>
       </c>
       <c r="K6" t="n">
-        <v>471481.4</v>
+        <v>837008.33</v>
       </c>
       <c r="L6" t="n">
-        <v>193648.82</v>
+        <v>3702294</v>
+      </c>
+      <c r="M6" t="n">
+        <v>171360</v>
       </c>
     </row>
     <row r="7">
@@ -3430,34 +3660,37 @@
         <v>13180543.2</v>
       </c>
       <c r="C7" t="n">
-        <v>37283400</v>
+        <v>28470960</v>
       </c>
       <c r="D7" t="n">
-        <v>34433105.37</v>
+        <v>65243819.52</v>
       </c>
       <c r="E7" t="n">
-        <v>9416839.869999999</v>
+        <v>17633574.45</v>
       </c>
       <c r="F7" t="n">
         <v>50000.4</v>
       </c>
       <c r="G7" t="n">
-        <v>44788.5</v>
+        <v>130977</v>
       </c>
       <c r="H7" t="n">
-        <v>714918.9300000001</v>
+        <v>14729940</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>122499.3</v>
+        <v>50983.8</v>
       </c>
       <c r="K7" t="n">
-        <v>384865.36</v>
+        <v>681532.02</v>
       </c>
       <c r="L7" t="n">
-        <v>280960.92</v>
+        <v>5368680</v>
+      </c>
+      <c r="M7" t="n">
+        <v>406350</v>
       </c>
     </row>
     <row r="8">
@@ -3468,34 +3701,37 @@
         <v>13406580</v>
       </c>
       <c r="C8" t="n">
-        <v>37089360</v>
+        <v>28322784</v>
       </c>
       <c r="D8" t="n">
-        <v>39515470.41</v>
+        <v>74873880.58</v>
       </c>
       <c r="E8" t="n">
-        <v>9599220.890000001</v>
+        <v>17975093.4</v>
       </c>
       <c r="F8" t="n">
         <v>514587.45</v>
       </c>
       <c r="G8" t="n">
-        <v>347402.25</v>
+        <v>1015092</v>
       </c>
       <c r="H8" t="n">
-        <v>1283932.65</v>
+        <v>26453700</v>
       </c>
       <c r="I8" t="n">
-        <v>551995.2</v>
+        <v>285897.73</v>
       </c>
       <c r="J8" t="n">
-        <v>99166.10000000001</v>
+        <v>41272.6</v>
       </c>
       <c r="K8" t="n">
-        <v>595218.6</v>
+        <v>1107853.7</v>
       </c>
       <c r="L8" t="n">
-        <v>491983.99</v>
+        <v>9443142</v>
+      </c>
+      <c r="M8" t="n">
+        <v>334800</v>
       </c>
     </row>
     <row r="9">
@@ -3506,22 +3742,22 @@
         <v>15786936</v>
       </c>
       <c r="C9" t="n">
-        <v>32321520</v>
+        <v>24681888</v>
       </c>
       <c r="D9" t="n">
-        <v>37570530.23</v>
+        <v>71188609.54000001</v>
       </c>
       <c r="E9" t="n">
-        <v>6480785.71</v>
+        <v>12135644.1</v>
       </c>
       <c r="F9" t="n">
         <v>375003</v>
       </c>
       <c r="G9" t="n">
-        <v>544399.5</v>
+        <v>1589058</v>
       </c>
       <c r="H9" t="n">
-        <v>879747</v>
+        <v>18126000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -3530,10 +3766,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1045366</v>
+        <v>1910532.93</v>
       </c>
       <c r="L9" t="n">
-        <v>714415.63</v>
+        <v>13646880</v>
+      </c>
+      <c r="M9" t="n">
+        <v>216000</v>
       </c>
     </row>
     <row r="10">
@@ -3544,22 +3783,22 @@
         <v>11571714</v>
       </c>
       <c r="C10" t="n">
-        <v>21261240</v>
+        <v>16235856</v>
       </c>
       <c r="D10" t="n">
-        <v>26776132.3</v>
+        <v>50735393.28</v>
       </c>
       <c r="E10" t="n">
-        <v>6010830</v>
+        <v>11255625</v>
       </c>
       <c r="F10" t="n">
         <v>166668</v>
       </c>
       <c r="G10" t="n">
-        <v>450660</v>
+        <v>1315440</v>
       </c>
       <c r="H10" t="n">
-        <v>240685.5</v>
+        <v>4959000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -3568,10 +3807,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>554684</v>
+        <v>1098336.72</v>
       </c>
       <c r="L10" t="n">
-        <v>420782.92</v>
+        <v>8059662</v>
+      </c>
+      <c r="M10" t="n">
+        <v>135000</v>
       </c>
     </row>
     <row r="11">
@@ -3582,34 +3824,37 @@
         <v>4970988</v>
       </c>
       <c r="C11" t="n">
-        <v>12584880</v>
+        <v>9610272</v>
       </c>
       <c r="D11" t="n">
-        <v>16368435.18</v>
+        <v>31014897.41</v>
       </c>
       <c r="E11" t="n">
-        <v>3193715.65</v>
+        <v>5980416.3</v>
       </c>
       <c r="F11" t="n">
         <v>83334</v>
       </c>
       <c r="G11" t="n">
-        <v>185370</v>
+        <v>542700</v>
       </c>
       <c r="H11" t="n">
-        <v>215787</v>
+        <v>4446000</v>
       </c>
       <c r="I11" t="n">
-        <v>383330</v>
+        <v>174510.26</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>234674</v>
+        <v>479903.23</v>
       </c>
       <c r="L11" t="n">
-        <v>220710.6</v>
+        <v>4228200</v>
+      </c>
+      <c r="M11" t="n">
+        <v>117000</v>
       </c>
     </row>
     <row r="12">
@@ -3620,22 +3865,22 @@
         <v>3087612</v>
       </c>
       <c r="C12" t="n">
-        <v>5932080</v>
+        <v>4529952</v>
       </c>
       <c r="D12" t="n">
-        <v>7960250.53</v>
+        <v>15083076.1</v>
       </c>
       <c r="E12" t="n">
-        <v>1902241.15</v>
+        <v>3562056</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>74370</v>
+        <v>217080</v>
       </c>
       <c r="H12" t="n">
-        <v>41497.5</v>
+        <v>855000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -3644,10 +3889,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>149338</v>
+        <v>315079.88</v>
       </c>
       <c r="L12" t="n">
-        <v>103714.2</v>
+        <v>1987200</v>
+      </c>
+      <c r="M12" t="n">
+        <v>90000</v>
       </c>
     </row>
     <row r="13">
@@ -3658,22 +3906,22 @@
         <v>1356894</v>
       </c>
       <c r="C13" t="n">
-        <v>1774080</v>
+        <v>1354752</v>
       </c>
       <c r="D13" t="n">
-        <v>2438418.09</v>
+        <v>4620312.58</v>
       </c>
       <c r="E13" t="n">
-        <v>350999.31</v>
+        <v>657266.4</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>21090</v>
+        <v>61560</v>
       </c>
       <c r="H13" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -3682,10 +3930,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>42668</v>
+        <v>92207.84</v>
       </c>
       <c r="L13" t="n">
-        <v>37868.4</v>
+        <v>723600</v>
+      </c>
+      <c r="M13" t="n">
+        <v>216000</v>
       </c>
     </row>
     <row r="14">
@@ -3696,10 +3947,10 @@
         <v>1113156</v>
       </c>
       <c r="C14" t="n">
-        <v>498960</v>
+        <v>381024</v>
       </c>
       <c r="D14" t="n">
-        <v>702056.39</v>
+        <v>1330255.87</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -3708,10 +3959,10 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>4440</v>
+        <v>12960</v>
       </c>
       <c r="H14" t="n">
-        <v>33198</v>
+        <v>684000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -3723,7 +3974,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>13564.8</v>
+        <v>259200</v>
+      </c>
+      <c r="M14" t="n">
+        <v>99000</v>
       </c>
     </row>
     <row r="15">
@@ -3734,22 +3988,22 @@
         <v>399168</v>
       </c>
       <c r="C15" t="n">
-        <v>887040</v>
+        <v>677376</v>
       </c>
       <c r="D15" t="n">
-        <v>1266077.01</v>
+        <v>2398961.66</v>
       </c>
       <c r="E15" t="n">
-        <v>197752.16</v>
+        <v>370302.3</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1110</v>
+        <v>3240</v>
       </c>
       <c r="H15" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -3758,10 +4012,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>21334</v>
+        <v>47876.22</v>
       </c>
       <c r="L15" t="n">
-        <v>31368.6</v>
+        <v>599400</v>
+      </c>
+      <c r="M15" t="n">
+        <v>702000</v>
       </c>
     </row>
     <row r="16">
@@ -3772,10 +4029,10 @@
         <v>268686</v>
       </c>
       <c r="C16" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D16" t="n">
-        <v>160506.72</v>
+        <v>304128</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -3784,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>555</v>
+        <v>1620</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -3799,7 +4056,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>11586.6</v>
+        <v>221400</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3822,10 +4082,10 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>555</v>
+        <v>1620</v>
       </c>
       <c r="H17" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -3837,7 +4097,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>565.2</v>
+        <v>10800</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3877,6 +4140,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3915,6 +4181,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3953,6 +4222,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3991,6 +4263,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4029,6 +4304,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4067,6 +4345,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4105,6 +4386,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -4154,6 +4438,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -4168,7 +4456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4239,6 +4527,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -4260,7 +4553,7 @@
         <v>18</v>
       </c>
       <c r="G4" t="n">
-        <v>30360</v>
+        <v>30420</v>
       </c>
       <c r="H4" t="n">
         <v>1710</v>
@@ -4275,7 +4568,10 @@
         <v>44</v>
       </c>
       <c r="L4" t="n">
-        <v>102810</v>
+        <v>103020</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -4298,7 +4594,7 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>9810</v>
+        <v>9840</v>
       </c>
       <c r="H5" t="n">
         <v>480</v>
@@ -4313,7 +4609,10 @@
         <v>15</v>
       </c>
       <c r="L5" t="n">
-        <v>34950</v>
+        <v>35190</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4353,6 +4652,9 @@
       <c r="L6" t="n">
         <v>8190</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4391,6 +4693,9 @@
       <c r="L7" t="n">
         <v>1560</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -4429,6 +4734,9 @@
       <c r="L8" t="n">
         <v>360</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -4467,6 +4775,9 @@
       <c r="L9" t="n">
         <v>150</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -4505,6 +4816,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -4543,6 +4857,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4581,6 +4898,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -4619,6 +4939,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -4657,6 +4980,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -4695,6 +5021,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -4733,6 +5062,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -4771,6 +5103,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -4809,6 +5144,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -4847,6 +5185,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4885,6 +5226,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -4923,6 +5267,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4961,6 +5308,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4999,6 +5349,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5037,6 +5390,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -5086,6 +5442,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -5100,7 +5460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5171,6 +5531,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -5207,6 +5572,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5242,10 +5610,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6.3</v>
+        <v>4.96</v>
       </c>
       <c r="L5" t="n">
-        <v>7339.5</v>
+        <v>7389.9</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -5280,10 +5651,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="L6" t="n">
         <v>3030.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -5323,6 +5697,9 @@
       <c r="L7" t="n">
         <v>936</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -5361,6 +5738,9 @@
       <c r="L8" t="n">
         <v>255.6</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -5399,6 +5779,9 @@
       <c r="L9" t="n">
         <v>121.5</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -5437,6 +5820,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -5475,6 +5861,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -5513,6 +5902,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -5551,6 +5943,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -5589,6 +5984,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -5627,6 +6025,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -5665,6 +6066,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -5703,6 +6107,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -5741,6 +6148,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -5779,6 +6189,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -5817,6 +6230,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -5855,6 +6271,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -5893,6 +6312,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -5931,6 +6353,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5969,6 +6394,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -6018,6 +6446,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -6032,7 +6464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6103,6 +6535,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -6139,6 +6576,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6150,13 +6590,13 @@
         <v>2882919.6</v>
       </c>
       <c r="C5" t="n">
-        <v>12410244</v>
+        <v>9476913.6</v>
       </c>
       <c r="D5" t="n">
-        <v>10811491.9</v>
+        <v>20485605.89</v>
       </c>
       <c r="E5" t="n">
-        <v>2377635.62</v>
+        <v>4452259.5</v>
       </c>
       <c r="F5" t="n">
         <v>2500.02</v>
@@ -6165,7 +6605,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>47805.12</v>
+        <v>984960</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -6174,10 +6614,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>134404.2</v>
+        <v>241080.54</v>
       </c>
       <c r="L5" t="n">
-        <v>69138.09</v>
+        <v>1330182</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -6188,22 +6631,22 @@
         <v>311256</v>
       </c>
       <c r="C6" t="n">
-        <v>4166316</v>
+        <v>3181550.4</v>
       </c>
       <c r="D6" t="n">
-        <v>3397485.87</v>
+        <v>6437553.41</v>
       </c>
       <c r="E6" t="n">
-        <v>1345099.39</v>
+        <v>2518776</v>
       </c>
       <c r="F6" t="n">
         <v>16666.8</v>
       </c>
       <c r="G6" t="n">
-        <v>1498.5</v>
+        <v>4374</v>
       </c>
       <c r="H6" t="n">
-        <v>23653.57</v>
+        <v>487350</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -6212,10 +6655,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>27734.2</v>
+        <v>49235.78</v>
       </c>
       <c r="L6" t="n">
-        <v>28545.43</v>
+        <v>545454</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -6226,19 +6672,19 @@
         <v>68092.2</v>
       </c>
       <c r="C7" t="n">
-        <v>748440</v>
+        <v>571536</v>
       </c>
       <c r="D7" t="n">
-        <v>691222.1899999999</v>
+        <v>1309727.23</v>
       </c>
       <c r="E7" t="n">
-        <v>70538.13</v>
+        <v>132086.7</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>666</v>
+        <v>1944</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -6253,7 +6699,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>8817.120000000001</v>
+        <v>168480</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -6264,10 +6713,10 @@
         <v>38610</v>
       </c>
       <c r="C8" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D8" t="n">
-        <v>88599.71000000001</v>
+        <v>167878.66</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -6276,7 +6725,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2525.25</v>
+        <v>7371</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -6291,7 +6740,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2407.75</v>
+        <v>46008</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -6302,13 +6754,13 @@
         <v>24552</v>
       </c>
       <c r="C9" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D9" t="n">
-        <v>96665.17</v>
+        <v>183161.09</v>
       </c>
       <c r="E9" t="n">
-        <v>44388.94</v>
+        <v>83120.85000000001</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -6329,7 +6781,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1144.53</v>
+        <v>21870</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -6369,6 +6824,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -6407,6 +6865,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -6445,6 +6906,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -6483,6 +6947,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -6521,6 +6988,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -6559,6 +7029,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -6597,6 +7070,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -6635,6 +7111,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -6673,6 +7152,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -6711,6 +7193,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -6749,6 +7234,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -6787,6 +7275,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -6825,6 +7316,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -6863,6 +7357,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -6901,6 +7398,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -6950,6 +7450,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -6964,7 +7468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7035,6 +7539,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -7056,7 +7565,7 @@
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>42570</v>
+        <v>42630</v>
       </c>
       <c r="H4" t="n">
         <v>3390</v>
@@ -7071,7 +7580,10 @@
         <v>64</v>
       </c>
       <c r="L4" t="n">
-        <v>53250</v>
+        <v>53280</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -7111,6 +7623,9 @@
       <c r="L5" t="n">
         <v>13650</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -7149,6 +7664,9 @@
       <c r="L6" t="n">
         <v>2640</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -7187,6 +7705,9 @@
       <c r="L7" t="n">
         <v>510</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -7225,6 +7746,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -7263,6 +7787,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -7301,6 +7828,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -7339,6 +7869,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -7377,6 +7910,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -7415,6 +7951,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -7453,6 +7992,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -7491,6 +8033,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -7529,6 +8074,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -7567,6 +8115,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -7605,6 +8156,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -7643,6 +8197,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -7681,6 +8238,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -7719,6 +8279,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -7757,6 +8320,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -7795,6 +8361,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -7833,6 +8402,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -7882,6 +8454,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -7896,7 +8472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7967,6 +8543,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -8003,6 +8584,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8038,10 +8622,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3.36</v>
+        <v>2.65</v>
       </c>
       <c r="L5" t="n">
         <v>2866.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -8076,10 +8663,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.95</v>
+        <v>1.52</v>
       </c>
       <c r="L6" t="n">
         <v>976.8</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -8114,10 +8704,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.64</v>
+        <v>1.28</v>
       </c>
       <c r="L7" t="n">
         <v>306</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -8157,6 +8750,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -8195,6 +8791,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -8233,6 +8832,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -8271,6 +8873,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -8309,6 +8914,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -8347,6 +8955,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -8385,6 +8996,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -8423,6 +9037,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -8461,6 +9078,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -8499,6 +9119,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -8537,6 +9160,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -8575,6 +9201,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -8613,6 +9242,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -8651,6 +9283,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -8689,6 +9324,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -8727,6 +9365,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -8765,6 +9406,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -8814,6 +9458,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -8828,7 +9476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8899,6 +9547,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -8935,6 +9588,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8946,13 +9602,13 @@
         <v>2264654.7</v>
       </c>
       <c r="C5" t="n">
-        <v>7653492</v>
+        <v>5844484.8</v>
       </c>
       <c r="D5" t="n">
-        <v>6667529.4</v>
+        <v>12633629.18</v>
       </c>
       <c r="E5" t="n">
-        <v>640132.67</v>
+        <v>1198685.25</v>
       </c>
       <c r="F5" t="n">
         <v>1666.68</v>
@@ -8961,7 +9617,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>253964.7</v>
+        <v>5232600</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -8970,10 +9626,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>71682.24000000001</v>
+        <v>128576.29</v>
       </c>
       <c r="L5" t="n">
-        <v>27002.43</v>
+        <v>515970</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -8984,22 +9643,22 @@
         <v>632174.4</v>
       </c>
       <c r="C6" t="n">
-        <v>2270268</v>
+        <v>1733659.2</v>
       </c>
       <c r="D6" t="n">
-        <v>1851324.64</v>
+        <v>3507888.38</v>
       </c>
       <c r="E6" t="n">
-        <v>280229.04</v>
+        <v>524745</v>
       </c>
       <c r="F6" t="n">
         <v>4166.7</v>
       </c>
       <c r="G6" t="n">
-        <v>2608.5</v>
+        <v>7614</v>
       </c>
       <c r="H6" t="n">
-        <v>61499.29</v>
+        <v>1267110</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9008,10 +9667,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>41601.3</v>
+        <v>73853.67999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>9201.459999999999</v>
+        <v>175824</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -9022,10 +9684,10 @@
         <v>146906.1</v>
       </c>
       <c r="C7" t="n">
-        <v>332640</v>
+        <v>254016</v>
       </c>
       <c r="D7" t="n">
-        <v>307209.86</v>
+        <v>582100.99</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -9034,7 +9696,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2081.25</v>
+        <v>6075</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -9046,10 +9708,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>34987.76</v>
+        <v>61957.46</v>
       </c>
       <c r="L7" t="n">
-        <v>2882.52</v>
+        <v>55080</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -9060,10 +9725,10 @@
         <v>25938</v>
       </c>
       <c r="C8" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D8" t="n">
-        <v>29533.24</v>
+        <v>55959.55</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -9087,6 +9752,9 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9127,6 +9795,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -9165,6 +9836,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -9203,6 +9877,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -9241,6 +9918,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -9279,6 +9959,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -9317,6 +10000,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -9355,6 +10041,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -9393,6 +10082,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -9431,6 +10123,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -9469,6 +10164,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -9507,6 +10205,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -9545,6 +10246,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -9583,6 +10287,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -9621,6 +10328,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -9659,6 +10369,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -9697,6 +10410,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -9746,6 +10462,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -9760,7 +10480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9831,6 +10551,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -9855,7 +10580,7 @@
         <v>96660</v>
       </c>
       <c r="H4" t="n">
-        <v>10050</v>
+        <v>10020</v>
       </c>
       <c r="I4" t="n">
         <v>6</v>
@@ -9867,7 +10592,10 @@
         <v>227</v>
       </c>
       <c r="L4" t="n">
-        <v>221460</v>
+        <v>221820</v>
+      </c>
+      <c r="M4" t="n">
+        <v>18720</v>
       </c>
     </row>
     <row r="5">
@@ -9890,10 +10618,10 @@
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>102960</v>
+        <v>102990</v>
       </c>
       <c r="H5" t="n">
-        <v>13020</v>
+        <v>12990</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -9905,7 +10633,10 @@
         <v>263</v>
       </c>
       <c r="L5" t="n">
-        <v>261210</v>
+        <v>261180</v>
+      </c>
+      <c r="M5" t="n">
+        <v>14160</v>
       </c>
     </row>
     <row r="6">
@@ -9928,10 +10659,10 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>62520</v>
+        <v>62550</v>
       </c>
       <c r="H6" t="n">
-        <v>5190</v>
+        <v>5220</v>
       </c>
       <c r="I6" t="n">
         <v>2</v>
@@ -9943,7 +10674,10 @@
         <v>120</v>
       </c>
       <c r="L6" t="n">
-        <v>135810</v>
+        <v>135930</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6240</v>
       </c>
     </row>
     <row r="7">
@@ -9966,7 +10700,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>39120</v>
+        <v>39270</v>
       </c>
       <c r="H7" t="n">
         <v>780</v>
@@ -9978,10 +10712,13 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L7" t="n">
-        <v>68400</v>
+        <v>68460</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3570</v>
       </c>
     </row>
     <row r="8">
@@ -10021,6 +10758,9 @@
       <c r="L8" t="n">
         <v>34170</v>
       </c>
+      <c r="M8" t="n">
+        <v>2160</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -10059,6 +10799,9 @@
       <c r="L9" t="n">
         <v>8940</v>
       </c>
+      <c r="M9" t="n">
+        <v>1020</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -10097,6 +10840,9 @@
       <c r="L10" t="n">
         <v>3930</v>
       </c>
+      <c r="M10" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -10135,6 +10881,9 @@
       <c r="L11" t="n">
         <v>3480</v>
       </c>
+      <c r="M11" t="n">
+        <v>270</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -10173,6 +10922,9 @@
       <c r="L12" t="n">
         <v>2010</v>
       </c>
+      <c r="M12" t="n">
+        <v>480</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -10211,6 +10963,9 @@
       <c r="L13" t="n">
         <v>870</v>
       </c>
+      <c r="M13" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -10249,6 +11004,9 @@
       <c r="L14" t="n">
         <v>300</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -10287,6 +11045,9 @@
       <c r="L15" t="n">
         <v>480</v>
       </c>
+      <c r="M15" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -10325,6 +11086,9 @@
       <c r="L16" t="n">
         <v>630</v>
       </c>
+      <c r="M16" t="n">
+        <v>240</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -10363,6 +11127,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -10401,6 +11168,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -10439,6 +11209,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -10477,6 +11250,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -10515,6 +11291,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -10553,6 +11332,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -10591,6 +11373,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -10629,6 +11414,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -10678,6 +11466,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -10692,7 +11484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10763,6 +11555,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -10799,6 +11596,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10807,7 +11607,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>51763.09</v>
+        <v>51706.71</v>
       </c>
       <c r="C5" t="n">
         <v>10396108.8</v>
@@ -10828,16 +11628,19 @@
         <v>24040.8</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3</v>
+        <v>0.66</v>
       </c>
       <c r="J5" t="n">
         <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>290.22</v>
+        <v>225.74</v>
       </c>
       <c r="L5" t="n">
-        <v>193617.9</v>
+        <v>193195.8</v>
+      </c>
+      <c r="M5" t="n">
+        <v>859.8</v>
       </c>
     </row>
     <row r="6">
@@ -10845,7 +11648,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>67413.38</v>
+        <v>67314.46000000001</v>
       </c>
       <c r="C6" t="n">
         <v>9268408.800000001</v>
@@ -10860,22 +11663,25 @@
         <v>2.9</v>
       </c>
       <c r="G6" t="n">
-        <v>12075</v>
+        <v>12037.5</v>
       </c>
       <c r="H6" t="n">
         <v>11046.6</v>
       </c>
       <c r="I6" t="n">
-        <v>1.05</v>
+        <v>1.52</v>
       </c>
       <c r="J6" t="n">
         <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>274.3</v>
+        <v>213.45</v>
       </c>
       <c r="L6" t="n">
-        <v>214496.4</v>
+        <v>213852.6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1660.8</v>
       </c>
     </row>
     <row r="7">
@@ -10883,7 +11689,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>62870.2</v>
+        <v>62827.45</v>
       </c>
       <c r="C7" t="n">
         <v>6491016</v>
@@ -10898,7 +11704,7 @@
         <v>10.2</v>
       </c>
       <c r="G7" t="n">
-        <v>22315.5</v>
+        <v>22248</v>
       </c>
       <c r="H7" t="n">
         <v>4117.2</v>
@@ -10910,10 +11716,13 @@
         <v>6.3</v>
       </c>
       <c r="K7" t="n">
-        <v>259.94</v>
+        <v>202.25</v>
       </c>
       <c r="L7" t="n">
-        <v>208440</v>
+        <v>207828</v>
+      </c>
+      <c r="M7" t="n">
+        <v>4672.5</v>
       </c>
     </row>
     <row r="8">
@@ -10921,7 +11730,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>43910.73</v>
+        <v>43910.46</v>
       </c>
       <c r="C8" t="n">
         <v>3736656</v>
@@ -10936,22 +11745,25 @@
         <v>25.65</v>
       </c>
       <c r="G8" t="n">
-        <v>75153</v>
+        <v>74860.5</v>
       </c>
       <c r="H8" t="n">
         <v>4921.5</v>
       </c>
       <c r="I8" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="J8" t="n">
         <v>4.25</v>
       </c>
       <c r="K8" t="n">
-        <v>174.6</v>
+        <v>142.78</v>
       </c>
       <c r="L8" t="n">
-        <v>173722.8</v>
+        <v>173232.9</v>
+      </c>
+      <c r="M8" t="n">
+        <v>5274</v>
       </c>
     </row>
     <row r="9">
@@ -10959,7 +11771,7 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>27650.7</v>
+        <v>27650.61</v>
       </c>
       <c r="C9" t="n">
         <v>2046240</v>
@@ -10974,7 +11786,7 @@
         <v>27</v>
       </c>
       <c r="G9" t="n">
-        <v>61557</v>
+        <v>61276.5</v>
       </c>
       <c r="H9" t="n">
         <v>3270</v>
@@ -10986,10 +11798,13 @@
         <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>151</v>
+        <v>121.25</v>
       </c>
       <c r="L9" t="n">
-        <v>153843.3</v>
+        <v>153551.7</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4920</v>
       </c>
     </row>
     <row r="10">
@@ -10997,7 +11812,7 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>17051.58</v>
+        <v>17051.31</v>
       </c>
       <c r="C10" t="n">
         <v>1049832</v>
@@ -11024,10 +11839,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>77</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>86561.39999999999</v>
+        <v>86481.3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3360</v>
       </c>
     </row>
     <row r="11">
@@ -11056,16 +11874,19 @@
         <v>810</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>29</v>
+        <v>26.06</v>
       </c>
       <c r="L11" t="n">
-        <v>45090</v>
+        <v>44790</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2610</v>
       </c>
     </row>
     <row r="12">
@@ -11100,10 +11921,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>11</v>
+        <v>10.2</v>
       </c>
       <c r="L12" t="n">
-        <v>17040</v>
+        <v>16860</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1590</v>
       </c>
     </row>
     <row r="13">
@@ -11138,10 +11962,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="L13" t="n">
         <v>6480</v>
+      </c>
+      <c r="M13" t="n">
+        <v>960</v>
       </c>
     </row>
     <row r="14">
@@ -11181,6 +12008,9 @@
       <c r="L14" t="n">
         <v>2790</v>
       </c>
+      <c r="M14" t="n">
+        <v>390</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -11214,10 +12044,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="L15" t="n">
         <v>4110</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2490</v>
       </c>
     </row>
     <row r="16">
@@ -11257,6 +12090,9 @@
       <c r="L16" t="n">
         <v>1920</v>
       </c>
+      <c r="M16" t="n">
+        <v>840</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -11295,6 +12131,9 @@
       <c r="L17" t="n">
         <v>150</v>
       </c>
+      <c r="M17" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -11333,6 +12172,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -11371,6 +12213,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -11409,6 +12254,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -11447,6 +12295,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -11485,6 +12336,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -11523,6 +12377,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -11561,6 +12418,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -11610,6 +12470,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -11624,7 +12488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11695,6 +12559,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -11731,6 +12600,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11757,19 +12629,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4687.2</v>
+        <v>4676.4</v>
       </c>
       <c r="I5" t="n">
-        <v>0.15</v>
+        <v>0.33</v>
       </c>
       <c r="J5" t="n">
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>110.46</v>
+        <v>87.05</v>
       </c>
       <c r="L5" t="n">
-        <v>54854.1</v>
+        <v>54847.8</v>
+      </c>
+      <c r="M5" t="n">
+        <v>283.2</v>
       </c>
     </row>
     <row r="6">
@@ -11792,22 +12667,25 @@
         <v>0.1</v>
       </c>
       <c r="G6" t="n">
-        <v>3126</v>
+        <v>3127.5</v>
       </c>
       <c r="H6" t="n">
-        <v>2958.3</v>
+        <v>2975.4</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>1.01</v>
       </c>
       <c r="J6" t="n">
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>78</v>
+        <v>60.84</v>
       </c>
       <c r="L6" t="n">
-        <v>50249.7</v>
+        <v>50294.1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>499.2</v>
       </c>
     </row>
     <row r="7">
@@ -11830,7 +12708,7 @@
         <v>0.6</v>
       </c>
       <c r="G7" t="n">
-        <v>5868</v>
+        <v>5890.5</v>
       </c>
       <c r="H7" t="n">
         <v>569.4</v>
@@ -11842,10 +12720,13 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>65.59999999999999</v>
+        <v>51.68</v>
       </c>
       <c r="L7" t="n">
-        <v>41040</v>
+        <v>41076</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1249.5</v>
       </c>
     </row>
     <row r="8">
@@ -11874,16 +12755,19 @@
         <v>51</v>
       </c>
       <c r="I8" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="J8" t="n">
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>27.9</v>
+        <v>22.82</v>
       </c>
       <c r="L8" t="n">
         <v>24260.7</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1296</v>
       </c>
     </row>
     <row r="9">
@@ -11918,10 +12802,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>5.62</v>
       </c>
       <c r="L9" t="n">
         <v>7241.4</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1020</v>
       </c>
     </row>
     <row r="10">
@@ -11961,6 +12848,9 @@
       <c r="L10" t="n">
         <v>3497.7</v>
       </c>
+      <c r="M10" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -11999,6 +12889,9 @@
       <c r="L11" t="n">
         <v>3480</v>
       </c>
+      <c r="M11" t="n">
+        <v>270</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -12037,6 +12930,9 @@
       <c r="L12" t="n">
         <v>2010</v>
       </c>
+      <c r="M12" t="n">
+        <v>480</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -12075,6 +12971,9 @@
       <c r="L13" t="n">
         <v>870</v>
       </c>
+      <c r="M13" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -12113,6 +13012,9 @@
       <c r="L14" t="n">
         <v>300</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -12146,10 +13048,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="L15" t="n">
         <v>480</v>
+      </c>
+      <c r="M15" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -12189,6 +13094,9 @@
       <c r="L16" t="n">
         <v>630</v>
       </c>
+      <c r="M16" t="n">
+        <v>240</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -12227,6 +13135,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -12265,6 +13176,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -12303,6 +13217,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -12341,6 +13258,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -12379,6 +13299,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -12417,6 +13340,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -12455,6 +13381,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -12493,6 +13422,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -12542,6 +13474,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -12556,7 +13492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12627,6 +13563,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -12663,6 +13604,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12674,13 +13618,13 @@
         <v>41234767.2</v>
       </c>
       <c r="C5" t="n">
-        <v>170846676</v>
+        <v>130464734.4</v>
       </c>
       <c r="D5" t="n">
-        <v>148837319.68</v>
+        <v>282016829.95</v>
       </c>
       <c r="E5" t="n">
-        <v>22898460.01</v>
+        <v>42878683.8</v>
       </c>
       <c r="F5" t="n">
         <v>8333.4</v>
@@ -12689,19 +13633,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1296713.88</v>
+        <v>26655480</v>
       </c>
       <c r="I5" t="n">
-        <v>57499.5</v>
+        <v>64288.14</v>
       </c>
       <c r="J5" t="n">
-        <v>122499.3</v>
+        <v>50983.8</v>
       </c>
       <c r="K5" t="n">
-        <v>2356553.64</v>
+        <v>4226945.47</v>
       </c>
       <c r="L5" t="n">
-        <v>516725.62</v>
+        <v>9872604</v>
+      </c>
+      <c r="M5" t="n">
+        <v>84960</v>
       </c>
     </row>
     <row r="6">
@@ -12712,34 +13659,37 @@
         <v>53184542.4</v>
       </c>
       <c r="C6" t="n">
-        <v>120349152</v>
+        <v>91902988.8</v>
       </c>
       <c r="D6" t="n">
-        <v>98140549.89</v>
+        <v>185956632.58</v>
       </c>
       <c r="E6" t="n">
-        <v>7538161.18</v>
+        <v>14115640.5</v>
       </c>
       <c r="F6" t="n">
         <v>4166.7</v>
       </c>
       <c r="G6" t="n">
-        <v>57831</v>
+        <v>168885</v>
       </c>
       <c r="H6" t="n">
-        <v>818413.6899999999</v>
+        <v>16959780</v>
       </c>
       <c r="I6" t="n">
-        <v>268331</v>
+        <v>196943.14</v>
       </c>
       <c r="J6" t="n">
-        <v>87499.5</v>
+        <v>36417</v>
       </c>
       <c r="K6" t="n">
-        <v>1664052</v>
+        <v>2954147.04</v>
       </c>
       <c r="L6" t="n">
-        <v>473352.17</v>
+        <v>9052938</v>
+      </c>
+      <c r="M6" t="n">
+        <v>149760</v>
       </c>
     </row>
     <row r="7">
@@ -12750,34 +13700,37 @@
         <v>44852068.8</v>
       </c>
       <c r="C7" t="n">
-        <v>78059520</v>
+        <v>59609088</v>
       </c>
       <c r="D7" t="n">
-        <v>72091914.3</v>
+        <v>136599699.46</v>
       </c>
       <c r="E7" t="n">
-        <v>3738520.7</v>
+        <v>7000595.1</v>
       </c>
       <c r="F7" t="n">
         <v>25000.2</v>
       </c>
       <c r="G7" t="n">
-        <v>108558</v>
+        <v>318087</v>
       </c>
       <c r="H7" t="n">
-        <v>157524.51</v>
+        <v>3245580</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>81666.2</v>
+        <v>33989.2</v>
       </c>
       <c r="K7" t="n">
-        <v>1399510.4</v>
+        <v>2509276.97</v>
       </c>
       <c r="L7" t="n">
-        <v>386596.8</v>
+        <v>7393680</v>
+      </c>
+      <c r="M7" t="n">
+        <v>374850</v>
       </c>
     </row>
     <row r="8">
@@ -12788,34 +13741,37 @@
         <v>18892764</v>
       </c>
       <c r="C8" t="n">
-        <v>33679800</v>
+        <v>25719120</v>
       </c>
       <c r="D8" t="n">
-        <v>35882882.32</v>
+        <v>67990855.68000001</v>
       </c>
       <c r="E8" t="n">
-        <v>1301589.27</v>
+        <v>2437300.8</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>134920.5</v>
+        <v>393822</v>
       </c>
       <c r="H8" t="n">
-        <v>14109.15</v>
+        <v>290700</v>
       </c>
       <c r="I8" t="n">
-        <v>275997.6</v>
+        <v>142948.86</v>
       </c>
       <c r="J8" t="n">
-        <v>49583.05</v>
+        <v>20636.3</v>
       </c>
       <c r="K8" t="n">
-        <v>595218.6</v>
+        <v>1107853.7</v>
       </c>
       <c r="L8" t="n">
-        <v>228535.79</v>
+        <v>4366926</v>
+      </c>
+      <c r="M8" t="n">
+        <v>388800</v>
       </c>
     </row>
     <row r="9">
@@ -12826,19 +13782,19 @@
         <v>1770120</v>
       </c>
       <c r="C9" t="n">
-        <v>4546080</v>
+        <v>3471552</v>
       </c>
       <c r="D9" t="n">
-        <v>5284362.74</v>
+        <v>10012806.14</v>
       </c>
       <c r="E9" t="n">
-        <v>88777.89</v>
+        <v>166241.7</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>30192</v>
+        <v>88128</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -12850,10 +13806,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>149338</v>
+        <v>272933.28</v>
       </c>
       <c r="L9" t="n">
-        <v>68213.99000000001</v>
+        <v>1303452</v>
+      </c>
+      <c r="M9" t="n">
+        <v>306000</v>
       </c>
     </row>
     <row r="10">
@@ -12864,10 +13823,10 @@
         <v>497376</v>
       </c>
       <c r="C10" t="n">
-        <v>914760</v>
+        <v>698544</v>
       </c>
       <c r="D10" t="n">
-        <v>1152036.98</v>
+        <v>2182878.72</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -12876,10 +13835,10 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>11100</v>
+        <v>32400</v>
       </c>
       <c r="H10" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -12891,7 +13850,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>32948.33</v>
+        <v>629586</v>
+      </c>
+      <c r="M10" t="n">
+        <v>54000</v>
       </c>
     </row>
     <row r="11">
@@ -12902,10 +13864,10 @@
         <v>456786</v>
       </c>
       <c r="C11" t="n">
-        <v>221760</v>
+        <v>169344</v>
       </c>
       <c r="D11" t="n">
-        <v>288430.58</v>
+        <v>546518.02</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -12914,7 +13876,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>4440</v>
+        <v>12960</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -12929,7 +13891,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>32781.6</v>
+        <v>626400</v>
+      </c>
+      <c r="M11" t="n">
+        <v>81000</v>
       </c>
     </row>
     <row r="12">
@@ -12940,19 +13905,19 @@
         <v>94644</v>
       </c>
       <c r="C12" t="n">
-        <v>138600</v>
+        <v>105840</v>
       </c>
       <c r="D12" t="n">
-        <v>185987.16</v>
+        <v>352408.32</v>
       </c>
       <c r="E12" t="n">
-        <v>79260.05</v>
+        <v>148419</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>6660</v>
+        <v>19440</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12967,7 +13932,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>18934.2</v>
+        <v>361800</v>
+      </c>
+      <c r="M12" t="n">
+        <v>144000</v>
       </c>
     </row>
     <row r="13">
@@ -12978,10 +13946,10 @@
         <v>34056</v>
       </c>
       <c r="C13" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D13" t="n">
-        <v>114300.85</v>
+        <v>216577.15</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12990,7 +13958,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1665</v>
+        <v>4860</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13005,7 +13973,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>8195.4</v>
+        <v>156600</v>
+      </c>
+      <c r="M13" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="14">
@@ -13016,19 +13987,19 @@
         <v>33462</v>
       </c>
       <c r="C14" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D14" t="n">
-        <v>117009.4</v>
+        <v>221709.31</v>
       </c>
       <c r="E14" t="n">
-        <v>94399.05</v>
+        <v>176767.65</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>2220</v>
+        <v>6480</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13043,7 +14014,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2826</v>
+        <v>54000</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -13054,10 +14028,10 @@
         <v>17028</v>
       </c>
       <c r="C15" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D15" t="n">
-        <v>118694.72</v>
+        <v>224902.66</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13066,7 +14040,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>3330</v>
+        <v>9720</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -13078,10 +14052,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>21334</v>
+        <v>47876.22</v>
       </c>
       <c r="L15" t="n">
-        <v>4521.6</v>
+        <v>86400</v>
+      </c>
+      <c r="M15" t="n">
+        <v>27000</v>
       </c>
     </row>
     <row r="16">
@@ -13092,10 +14069,10 @@
         <v>9108</v>
       </c>
       <c r="C16" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D16" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13104,7 +14081,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>3330</v>
+        <v>9720</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -13119,7 +14096,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>5934.6</v>
+        <v>113400</v>
+      </c>
+      <c r="M16" t="n">
+        <v>72000</v>
       </c>
     </row>
     <row r="17">
@@ -13130,10 +14110,10 @@
         <v>1188</v>
       </c>
       <c r="C17" t="n">
-        <v>194040</v>
+        <v>148176</v>
       </c>
       <c r="D17" t="n">
-        <v>280886.76</v>
+        <v>532224</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13142,7 +14122,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>68820</v>
+        <v>200880</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -13157,6 +14137,9 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13168,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D18" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13195,6 +14178,9 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13206,10 +14192,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D19" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13233,6 +14219,9 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13244,10 +14233,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D20" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13271,6 +14260,9 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13311,6 +14303,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -13320,10 +14315,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D22" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13347,6 +14342,9 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13358,10 +14356,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D23" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13385,6 +14383,9 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13396,10 +14397,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>166320</v>
+        <v>127008</v>
       </c>
       <c r="D24" t="n">
-        <v>240760.08</v>
+        <v>456192</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13423,6 +14424,9 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13474,6 +14478,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -13488,7 +14496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13559,6 +14567,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -13580,7 +14593,7 @@
         <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>61770</v>
+        <v>61800</v>
       </c>
       <c r="H4" t="n">
         <v>4470</v>
@@ -13595,7 +14608,10 @@
         <v>76</v>
       </c>
       <c r="L4" t="n">
-        <v>222000</v>
+        <v>224280</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -13618,7 +14634,7 @@
         <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>13050</v>
+        <v>13020</v>
       </c>
       <c r="H5" t="n">
         <v>1140</v>
@@ -13633,7 +14649,10 @@
         <v>19</v>
       </c>
       <c r="L5" t="n">
-        <v>62820</v>
+        <v>62580</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -13656,7 +14675,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1320</v>
+        <v>1470</v>
       </c>
       <c r="H6" t="n">
         <v>210</v>
@@ -13671,7 +14690,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>9900</v>
+        <v>10260</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -13711,6 +14733,9 @@
       <c r="L7" t="n">
         <v>630</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -13749,6 +14774,9 @@
       <c r="L8" t="n">
         <v>180</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -13787,6 +14815,9 @@
       <c r="L9" t="n">
         <v>90</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -13825,6 +14856,9 @@
       <c r="L10" t="n">
         <v>180</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -13863,6 +14897,9 @@
       <c r="L11" t="n">
         <v>30</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -13901,6 +14938,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -13939,6 +14979,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -13977,6 +15020,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -14015,6 +15061,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -14053,6 +15102,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -14091,6 +15143,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -14129,6 +15184,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -14167,6 +15225,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -14205,6 +15266,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -14243,6 +15307,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -14281,6 +15348,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -14319,6 +15389,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -14357,6 +15430,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -14406,6 +15482,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -14420,7 +15500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14491,6 +15571,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -14527,6 +15612,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14562,10 +15650,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>7.98</v>
+        <v>6.29</v>
       </c>
       <c r="L5" t="n">
-        <v>13192.2</v>
+        <v>13141.8</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -14588,7 +15679,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>66</v>
+        <v>73.5</v>
       </c>
       <c r="H6" t="n">
         <v>119.7</v>
@@ -14603,7 +15694,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>3663</v>
+        <v>3796.2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -14643,6 +15737,9 @@
       <c r="L7" t="n">
         <v>378</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -14681,6 +15778,9 @@
       <c r="L8" t="n">
         <v>127.8</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -14719,6 +15819,9 @@
       <c r="L9" t="n">
         <v>72.90000000000001</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -14757,6 +15860,9 @@
       <c r="L10" t="n">
         <v>160.2</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -14795,6 +15901,9 @@
       <c r="L11" t="n">
         <v>30</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -14833,6 +15942,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -14871,6 +15983,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -14909,6 +16024,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -14947,6 +16065,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -14985,6 +16106,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -15023,6 +16147,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -15061,6 +16188,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -15099,6 +16229,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -15137,6 +16270,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -15175,6 +16311,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -15213,6 +16352,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -15251,6 +16393,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -15289,6 +16434,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -15338,6 +16486,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -15352,7 +16504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15423,6 +16575,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -15459,6 +16616,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15470,13 +16630,13 @@
         <v>5487669</v>
       </c>
       <c r="C5" t="n">
-        <v>13111560</v>
+        <v>10012464</v>
       </c>
       <c r="D5" t="n">
-        <v>11422460.73</v>
+        <v>21643269.12</v>
       </c>
       <c r="E5" t="n">
-        <v>3859085.51</v>
+        <v>7226359.65</v>
       </c>
       <c r="F5" t="n">
         <v>5000.04</v>
@@ -15485,7 +16645,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>113537.16</v>
+        <v>2339280</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -15494,10 +16654,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>170245.32</v>
+        <v>305368.68</v>
       </c>
       <c r="L5" t="n">
-        <v>124270.52</v>
+        <v>2365524</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -15508,22 +16671,22 @@
         <v>923947.2</v>
       </c>
       <c r="C6" t="n">
-        <v>2769228</v>
+        <v>2114683.2</v>
       </c>
       <c r="D6" t="n">
-        <v>2258209.17</v>
+        <v>4278852.86</v>
       </c>
       <c r="E6" t="n">
-        <v>476389.37</v>
+        <v>892066.5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1221</v>
+        <v>3969</v>
       </c>
       <c r="H6" t="n">
-        <v>33115</v>
+        <v>682290</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -15535,7 +16698,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>34505.46</v>
+        <v>683316</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -15546,19 +16712,19 @@
         <v>188288.1</v>
       </c>
       <c r="C7" t="n">
-        <v>498960</v>
+        <v>381024</v>
       </c>
       <c r="D7" t="n">
-        <v>460814.79</v>
+        <v>873151.49</v>
       </c>
       <c r="E7" t="n">
-        <v>105807.19</v>
+        <v>198130.05</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>83.25</v>
+        <v>243</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -15573,7 +16739,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3560.76</v>
+        <v>68040</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -15596,7 +16765,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>721.5</v>
+        <v>2106</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -15611,7 +16780,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1203.88</v>
+        <v>23004</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -15634,7 +16806,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>471.75</v>
+        <v>1377</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -15649,7 +16821,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>686.72</v>
+        <v>13122</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -15687,7 +16862,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1509.08</v>
+        <v>28836</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -15725,7 +16903,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>282.6</v>
+        <v>5400</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -15765,6 +16946,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -15803,6 +16987,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -15841,6 +17028,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -15879,6 +17069,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -15917,6 +17110,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -15955,6 +17151,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -15993,6 +17192,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -16031,6 +17233,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -16069,6 +17274,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -16107,6 +17315,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -16145,6 +17356,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -16183,6 +17397,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -16221,6 +17438,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -16270,6 +17490,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -16284,7 +17508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16355,6 +17579,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -16391,6 +17620,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16399,16 +17631,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>113878799.1</v>
+        <v>113754771.9</v>
       </c>
       <c r="C5" t="n">
-        <v>571785984</v>
+        <v>436636569.6</v>
       </c>
       <c r="D5" t="n">
-        <v>498125543.22</v>
+        <v>943847866.37</v>
       </c>
       <c r="E5" t="n">
-        <v>95434636.05</v>
+        <v>178706846.7</v>
       </c>
       <c r="F5" t="n">
         <v>65000.52</v>
@@ -16417,19 +17649,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6650887.32</v>
+        <v>137032560</v>
       </c>
       <c r="I5" t="n">
-        <v>114999</v>
+        <v>128576.29</v>
       </c>
       <c r="J5" t="n">
-        <v>349998</v>
+        <v>145668</v>
       </c>
       <c r="K5" t="n">
-        <v>6191553.48</v>
+        <v>10961128.55</v>
       </c>
       <c r="L5" t="n">
-        <v>1823880.62</v>
+        <v>34775244</v>
+      </c>
+      <c r="M5" t="n">
+        <v>257940</v>
       </c>
     </row>
     <row r="6">
@@ -16437,37 +17672,40 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>148309444.8</v>
+        <v>148091803.2</v>
       </c>
       <c r="C6" t="n">
-        <v>509762484</v>
+        <v>389273169.6</v>
       </c>
       <c r="D6" t="n">
-        <v>415693585.39</v>
+        <v>787655860.99</v>
       </c>
       <c r="E6" t="n">
-        <v>73868374.94</v>
+        <v>138322782</v>
       </c>
       <c r="F6" t="n">
         <v>120834.3</v>
       </c>
       <c r="G6" t="n">
-        <v>223387.5</v>
+        <v>650025</v>
       </c>
       <c r="H6" t="n">
-        <v>3056041.89</v>
+        <v>62965620</v>
       </c>
       <c r="I6" t="n">
-        <v>402496.5</v>
+        <v>295414.7</v>
       </c>
       <c r="J6" t="n">
-        <v>349998</v>
+        <v>145668</v>
       </c>
       <c r="K6" t="n">
-        <v>5851916.2</v>
+        <v>10364132.53</v>
       </c>
       <c r="L6" t="n">
-        <v>2020556.09</v>
+        <v>38493468</v>
+      </c>
+      <c r="M6" t="n">
+        <v>498240</v>
       </c>
     </row>
     <row r="7">
@@ -16475,37 +17713,40 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>138314444.4</v>
+        <v>138220394.4</v>
       </c>
       <c r="C7" t="n">
-        <v>357005880</v>
+        <v>272622672</v>
       </c>
       <c r="D7" t="n">
-        <v>329712984.48</v>
+        <v>624739889.66</v>
       </c>
       <c r="E7" t="n">
-        <v>53926397.63</v>
+        <v>100980282.15</v>
       </c>
       <c r="F7" t="n">
         <v>425003.4</v>
       </c>
       <c r="G7" t="n">
-        <v>412836.75</v>
+        <v>1201392</v>
       </c>
       <c r="H7" t="n">
-        <v>1139023.38</v>
+        <v>23468040</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>367497.9</v>
+        <v>152951.4</v>
       </c>
       <c r="K7" t="n">
-        <v>5545559.96</v>
+        <v>9820256.779999999</v>
       </c>
       <c r="L7" t="n">
-        <v>1963504.8</v>
+        <v>37409040</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1401750</v>
       </c>
     </row>
     <row r="8">
@@ -16513,37 +17754,40 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>96603606</v>
+        <v>96603012</v>
       </c>
       <c r="C8" t="n">
-        <v>205516080</v>
+        <v>156939552</v>
       </c>
       <c r="D8" t="n">
-        <v>218959415.26</v>
+        <v>414884118.53</v>
       </c>
       <c r="E8" t="n">
-        <v>37339342.29</v>
+        <v>69920066.7</v>
       </c>
       <c r="F8" t="n">
         <v>1068758.55</v>
       </c>
       <c r="G8" t="n">
-        <v>1390330.5</v>
+        <v>4042467</v>
       </c>
       <c r="H8" t="n">
-        <v>1361532.98</v>
+        <v>28052550</v>
       </c>
       <c r="I8" t="n">
-        <v>827992.8</v>
+        <v>428846.59</v>
       </c>
       <c r="J8" t="n">
-        <v>247915.25</v>
+        <v>103181.5</v>
       </c>
       <c r="K8" t="n">
-        <v>3724916.4</v>
+        <v>6933019.9</v>
       </c>
       <c r="L8" t="n">
-        <v>1636468.78</v>
+        <v>31181922</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1582200</v>
       </c>
     </row>
     <row r="9">
@@ -16551,37 +17795,40 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>60831540</v>
+        <v>60831342</v>
       </c>
       <c r="C9" t="n">
-        <v>112543200</v>
+        <v>85942080</v>
       </c>
       <c r="D9" t="n">
-        <v>130820199.6</v>
+        <v>247878005.76</v>
       </c>
       <c r="E9" t="n">
-        <v>25656809.17</v>
+        <v>48043851.3</v>
       </c>
       <c r="F9" t="n">
         <v>1125009</v>
       </c>
       <c r="G9" t="n">
-        <v>1138804.5</v>
+        <v>3308931</v>
       </c>
       <c r="H9" t="n">
-        <v>904645.5</v>
+        <v>18639000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>221665.4</v>
+        <v>92256.39999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>3221434</v>
+        <v>5887560.67</v>
       </c>
       <c r="L9" t="n">
-        <v>1449203.89</v>
+        <v>27639306</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1476000</v>
       </c>
     </row>
     <row r="10">
@@ -16589,25 +17836,25 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>37513476</v>
+        <v>37512882</v>
       </c>
       <c r="C10" t="n">
-        <v>57740760</v>
+        <v>44092944</v>
       </c>
       <c r="D10" t="n">
-        <v>72717970.76000001</v>
+        <v>137785950.72</v>
       </c>
       <c r="E10" t="n">
-        <v>13800865.68</v>
+        <v>25842915</v>
       </c>
       <c r="F10" t="n">
         <v>291669</v>
       </c>
       <c r="G10" t="n">
-        <v>762015</v>
+        <v>2224260</v>
       </c>
       <c r="H10" t="n">
-        <v>248985</v>
+        <v>5130000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -16616,10 +17863,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1642718</v>
+        <v>3252766.44</v>
       </c>
       <c r="L10" t="n">
-        <v>815408.39</v>
+        <v>15566634</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1008000</v>
       </c>
     </row>
     <row r="11">
@@ -16630,34 +17880,37 @@
         <v>21444192</v>
       </c>
       <c r="C11" t="n">
-        <v>27137880</v>
+        <v>20723472</v>
       </c>
       <c r="D11" t="n">
-        <v>35296691.72</v>
+        <v>66880142.21</v>
       </c>
       <c r="E11" t="n">
-        <v>5232257.55</v>
+        <v>9797703.300000001</v>
       </c>
       <c r="F11" t="n">
         <v>166668</v>
       </c>
       <c r="G11" t="n">
-        <v>484515</v>
+        <v>1414260</v>
       </c>
       <c r="H11" t="n">
-        <v>224086.5</v>
+        <v>4617000</v>
       </c>
       <c r="I11" t="n">
-        <v>383330</v>
+        <v>174510.26</v>
       </c>
       <c r="J11" t="n">
-        <v>116666</v>
+        <v>48556</v>
       </c>
       <c r="K11" t="n">
-        <v>618686</v>
+        <v>1265199.41</v>
       </c>
       <c r="L11" t="n">
-        <v>424747.8</v>
+        <v>8062200</v>
+      </c>
+      <c r="M11" t="n">
+        <v>783000</v>
       </c>
     </row>
     <row r="12">
@@ -16668,22 +17921,22 @@
         <v>10373814</v>
       </c>
       <c r="C12" t="n">
-        <v>8038800</v>
+        <v>6138720</v>
       </c>
       <c r="D12" t="n">
-        <v>10787255.38</v>
+        <v>20439682.56</v>
       </c>
       <c r="E12" t="n">
-        <v>2219281.34</v>
+        <v>4155732</v>
       </c>
       <c r="F12" t="n">
         <v>125001</v>
       </c>
       <c r="G12" t="n">
-        <v>155400</v>
+        <v>453600</v>
       </c>
       <c r="H12" t="n">
-        <v>41497.5</v>
+        <v>855000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -16692,10 +17945,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>234674</v>
+        <v>495125.53</v>
       </c>
       <c r="L12" t="n">
-        <v>160516.8</v>
+        <v>3034800</v>
+      </c>
+      <c r="M12" t="n">
+        <v>477000</v>
       </c>
     </row>
     <row r="13">
@@ -16706,22 +17962,22 @@
         <v>4226706</v>
       </c>
       <c r="C13" t="n">
-        <v>3021480</v>
+        <v>2307312</v>
       </c>
       <c r="D13" t="n">
-        <v>4152930.81</v>
+        <v>7868969.86</v>
       </c>
       <c r="E13" t="n">
-        <v>614248.79</v>
+        <v>1150216.2</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>42180</v>
+        <v>123120</v>
       </c>
       <c r="H13" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -16730,10 +17986,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>42668</v>
+        <v>92207.84</v>
       </c>
       <c r="L13" t="n">
-        <v>61041.6</v>
+        <v>1166400</v>
+      </c>
+      <c r="M13" t="n">
+        <v>288000</v>
       </c>
     </row>
     <row r="14">
@@ -16744,22 +18003,22 @@
         <v>3067614</v>
       </c>
       <c r="C14" t="n">
-        <v>887040</v>
+        <v>677376</v>
       </c>
       <c r="D14" t="n">
-        <v>1248100.25</v>
+        <v>2364899.33</v>
       </c>
       <c r="E14" t="n">
-        <v>188798.1</v>
+        <v>353535.3</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>28860</v>
+        <v>84240</v>
       </c>
       <c r="H14" t="n">
-        <v>33198</v>
+        <v>684000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -16771,7 +18030,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>26281.8</v>
+        <v>502200</v>
+      </c>
+      <c r="M14" t="n">
+        <v>117000</v>
       </c>
     </row>
     <row r="15">
@@ -16782,22 +18044,22 @@
         <v>1315314</v>
       </c>
       <c r="C15" t="n">
-        <v>1136520</v>
+        <v>867888</v>
       </c>
       <c r="D15" t="n">
-        <v>1622161.17</v>
+        <v>3073669.63</v>
       </c>
       <c r="E15" t="n">
-        <v>197752.16</v>
+        <v>370302.3</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>7215</v>
+        <v>21060</v>
       </c>
       <c r="H15" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -16806,10 +18068,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>64002</v>
+        <v>143628.65</v>
       </c>
       <c r="L15" t="n">
-        <v>38716.2</v>
+        <v>739800</v>
+      </c>
+      <c r="M15" t="n">
+        <v>747000</v>
       </c>
     </row>
     <row r="16">
@@ -16820,10 +18085,10 @@
         <v>656370</v>
       </c>
       <c r="C16" t="n">
-        <v>194040</v>
+        <v>148176</v>
       </c>
       <c r="D16" t="n">
-        <v>280886.76</v>
+        <v>532224</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16832,7 +18097,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>3885</v>
+        <v>11340</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -16847,7 +18112,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>18086.4</v>
+        <v>345600</v>
+      </c>
+      <c r="M16" t="n">
+        <v>252000</v>
       </c>
     </row>
     <row r="17">
@@ -16858,10 +18126,10 @@
         <v>336204</v>
       </c>
       <c r="C17" t="n">
-        <v>194040</v>
+        <v>148176</v>
       </c>
       <c r="D17" t="n">
-        <v>280886.76</v>
+        <v>532224</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -16870,10 +18138,10 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>72150</v>
+        <v>210600</v>
       </c>
       <c r="H17" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -16885,7 +18153,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1413</v>
+        <v>27000</v>
+      </c>
+      <c r="M17" t="n">
+        <v>27000</v>
       </c>
     </row>
     <row r="18">
@@ -16896,10 +18167,10 @@
         <v>42570</v>
       </c>
       <c r="C18" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D18" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -16924,6 +18195,9 @@
       </c>
       <c r="L18" t="n">
         <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="19">
@@ -16934,10 +18208,10 @@
         <v>10692</v>
       </c>
       <c r="C19" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D19" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -16962,6 +18236,9 @@
       </c>
       <c r="L19" t="n">
         <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="20">
@@ -16972,10 +18249,10 @@
         <v>2178</v>
       </c>
       <c r="C20" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D20" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -17000,6 +18277,9 @@
       </c>
       <c r="L20" t="n">
         <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="21">
@@ -17010,10 +18290,10 @@
         <v>12474</v>
       </c>
       <c r="C21" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D21" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -17038,6 +18318,9 @@
       </c>
       <c r="L21" t="n">
         <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="22">
@@ -17048,10 +18331,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D22" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -17075,6 +18358,9 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17086,10 +18372,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D23" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -17113,6 +18399,9 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17124,10 +18413,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>221760</v>
+        <v>169344</v>
       </c>
       <c r="D24" t="n">
-        <v>321013.44</v>
+        <v>608256</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -17151,6 +18440,9 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17202,6 +18494,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -17216,7 +18512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17287,13 +18583,18 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>18559.35</v>
+        <v>18475.65</v>
       </c>
       <c r="C4" t="n">
         <v>3993696</v>
@@ -17308,10 +18609,10 @@
         <v>22</v>
       </c>
       <c r="G4" t="n">
-        <v>74520</v>
+        <v>72270</v>
       </c>
       <c r="H4" t="n">
-        <v>20130</v>
+        <v>20160</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -17320,10 +18621,13 @@
         <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="L4" t="n">
-        <v>211470</v>
+        <v>208830</v>
+      </c>
+      <c r="M4" t="n">
+        <v>30480</v>
       </c>
     </row>
     <row r="5">
@@ -17331,7 +18635,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>29824.92</v>
+        <v>29795.85</v>
       </c>
       <c r="C5" t="n">
         <v>4540536</v>
@@ -17346,7 +18650,7 @@
         <v>24</v>
       </c>
       <c r="G5" t="n">
-        <v>94020</v>
+        <v>93240</v>
       </c>
       <c r="H5" t="n">
         <v>17790</v>
@@ -17358,10 +18662,13 @@
         <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="L5" t="n">
-        <v>270240</v>
+        <v>268770</v>
+      </c>
+      <c r="M5" t="n">
+        <v>10080</v>
       </c>
     </row>
     <row r="6">
@@ -17369,7 +18676,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>30416.76</v>
+        <v>30412.62</v>
       </c>
       <c r="C6" t="n">
         <v>4382280</v>
@@ -17384,7 +18691,7 @@
         <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>101280</v>
+        <v>100620</v>
       </c>
       <c r="H6" t="n">
         <v>2490</v>
@@ -17396,10 +18703,13 @@
         <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L6" t="n">
-        <v>260910</v>
+        <v>260220</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4800</v>
       </c>
     </row>
     <row r="7">
@@ -17407,7 +18717,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>31164.39</v>
+        <v>31163.94</v>
       </c>
       <c r="C7" t="n">
         <v>3758328</v>
@@ -17422,7 +18732,7 @@
         <v>11</v>
       </c>
       <c r="G7" t="n">
-        <v>82020</v>
+        <v>81630</v>
       </c>
       <c r="H7" t="n">
         <v>720</v>
@@ -17437,7 +18747,10 @@
         <v>208</v>
       </c>
       <c r="L7" t="n">
-        <v>192540</v>
+        <v>191640</v>
+      </c>
+      <c r="M7" t="n">
+        <v>4320</v>
       </c>
     </row>
     <row r="8">
@@ -17445,7 +18758,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>25109.01</v>
+        <v>25108.92</v>
       </c>
       <c r="C8" t="n">
         <v>2292192</v>
@@ -17460,7 +18773,7 @@
         <v>13</v>
       </c>
       <c r="G8" t="n">
-        <v>70650</v>
+        <v>70200</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -17475,7 +18788,10 @@
         <v>131</v>
       </c>
       <c r="L8" t="n">
-        <v>123420</v>
+        <v>122730</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3540</v>
       </c>
     </row>
     <row r="9">
@@ -17498,7 +18814,7 @@
         <v>17</v>
       </c>
       <c r="G9" t="n">
-        <v>34470</v>
+        <v>34170</v>
       </c>
       <c r="H9" t="n">
         <v>30</v>
@@ -17510,10 +18826,13 @@
         <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L9" t="n">
-        <v>83850</v>
+        <v>83580</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2910</v>
       </c>
     </row>
     <row r="10">
@@ -17551,7 +18870,10 @@
         <v>51</v>
       </c>
       <c r="L10" t="n">
-        <v>41490</v>
+        <v>41400</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2370</v>
       </c>
     </row>
     <row r="11">
@@ -17589,7 +18911,10 @@
         <v>18</v>
       </c>
       <c r="L11" t="n">
-        <v>17550</v>
+        <v>17250</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1950</v>
       </c>
     </row>
     <row r="12">
@@ -17627,7 +18952,10 @@
         <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>3930</v>
+        <v>3750</v>
+      </c>
+      <c r="M12" t="n">
+        <v>780</v>
       </c>
     </row>
     <row r="13">
@@ -17667,6 +18995,9 @@
       <c r="L13" t="n">
         <v>1440</v>
       </c>
+      <c r="M13" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -17705,6 +19036,9 @@
       <c r="L14" t="n">
         <v>510</v>
       </c>
+      <c r="M14" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -17743,6 +19077,9 @@
       <c r="L15" t="n">
         <v>300</v>
       </c>
+      <c r="M15" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -17781,6 +19118,9 @@
       <c r="L16" t="n">
         <v>60</v>
       </c>
+      <c r="M16" t="n">
+        <v>600</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -17819,6 +19159,9 @@
       <c r="L17" t="n">
         <v>90</v>
       </c>
+      <c r="M17" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -17857,6 +19200,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -17895,6 +19241,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -17933,6 +19282,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -17971,6 +19323,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -18009,6 +19364,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -18047,6 +19405,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -18085,6 +19446,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -18134,6 +19498,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -18148,7 +19516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18219,6 +19587,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -18255,6 +19628,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18263,7 +19639,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>13421.21</v>
+        <v>13408.13</v>
       </c>
       <c r="C5" t="n">
         <v>2497294.8</v>
@@ -18284,16 +19660,19 @@
         <v>6404.4</v>
       </c>
       <c r="I5" t="n">
-        <v>0.15</v>
+        <v>0.33</v>
       </c>
       <c r="J5" t="n">
         <v>1.8</v>
       </c>
       <c r="K5" t="n">
-        <v>91.14</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>56750.4</v>
+        <v>56441.7</v>
+      </c>
+      <c r="M5" t="n">
+        <v>201.6</v>
       </c>
     </row>
     <row r="6">
@@ -18301,7 +19680,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>24333.41</v>
+        <v>24330.1</v>
       </c>
       <c r="C6" t="n">
         <v>3944052</v>
@@ -18316,7 +19695,7 @@
         <v>0.7</v>
       </c>
       <c r="G6" t="n">
-        <v>5064</v>
+        <v>5031</v>
       </c>
       <c r="H6" t="n">
         <v>1419.3</v>
@@ -18328,10 +19707,13 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>140.4</v>
+        <v>109</v>
       </c>
       <c r="L6" t="n">
-        <v>96536.7</v>
+        <v>96281.39999999999</v>
+      </c>
+      <c r="M6" t="n">
+        <v>384</v>
       </c>
     </row>
     <row r="7">
@@ -18339,7 +19721,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>29606.17</v>
+        <v>29605.74</v>
       </c>
       <c r="C7" t="n">
         <v>3758328</v>
@@ -18354,7 +19736,7 @@
         <v>6.6</v>
       </c>
       <c r="G7" t="n">
-        <v>12303</v>
+        <v>12244.5</v>
       </c>
       <c r="H7" t="n">
         <v>525.6</v>
@@ -18366,10 +19748,13 @@
         <v>2.8</v>
       </c>
       <c r="K7" t="n">
-        <v>170.56</v>
+        <v>132.7</v>
       </c>
       <c r="L7" t="n">
-        <v>115524</v>
+        <v>114984</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1512</v>
       </c>
     </row>
     <row r="8">
@@ -18377,7 +19762,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>25109.01</v>
+        <v>25108.92</v>
       </c>
       <c r="C8" t="n">
         <v>2292192</v>
@@ -18392,7 +19777,7 @@
         <v>12.35</v>
       </c>
       <c r="G8" t="n">
-        <v>45922.5</v>
+        <v>45630</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -18404,10 +19789,13 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>117.9</v>
+        <v>96.42</v>
       </c>
       <c r="L8" t="n">
-        <v>87628.2</v>
+        <v>87138.3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2124</v>
       </c>
     </row>
     <row r="9">
@@ -18430,7 +19818,7 @@
         <v>17</v>
       </c>
       <c r="G9" t="n">
-        <v>29299.5</v>
+        <v>29044.5</v>
       </c>
       <c r="H9" t="n">
         <v>30</v>
@@ -18442,10 +19830,13 @@
         <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>93</v>
+        <v>75.48</v>
       </c>
       <c r="L9" t="n">
-        <v>67918.5</v>
+        <v>67699.8</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2910</v>
       </c>
     </row>
     <row r="10">
@@ -18480,10 +19871,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>51</v>
+        <v>44.37</v>
       </c>
       <c r="L10" t="n">
-        <v>36926.1</v>
+        <v>36846</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2370</v>
       </c>
     </row>
     <row r="11">
@@ -18518,10 +19912,13 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>18</v>
+        <v>16.17</v>
       </c>
       <c r="L11" t="n">
-        <v>17550</v>
+        <v>17250</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1950</v>
       </c>
     </row>
     <row r="12">
@@ -18556,10 +19953,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>3.71</v>
       </c>
       <c r="L12" t="n">
-        <v>3930</v>
+        <v>3750</v>
+      </c>
+      <c r="M12" t="n">
+        <v>780</v>
       </c>
     </row>
     <row r="13">
@@ -18599,6 +19999,9 @@
       <c r="L13" t="n">
         <v>1440</v>
       </c>
+      <c r="M13" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -18637,6 +20040,9 @@
       <c r="L14" t="n">
         <v>510</v>
       </c>
+      <c r="M14" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -18670,10 +20076,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="L15" t="n">
         <v>300</v>
+      </c>
+      <c r="M15" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="16">
@@ -18713,6 +20122,9 @@
       <c r="L16" t="n">
         <v>60</v>
       </c>
+      <c r="M16" t="n">
+        <v>600</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -18751,6 +20163,9 @@
       <c r="L17" t="n">
         <v>90</v>
       </c>
+      <c r="M17" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -18789,6 +20204,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -18827,6 +20245,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -18865,6 +20286,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -18903,6 +20327,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -18941,6 +20368,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -18979,6 +20409,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -19017,6 +20450,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -19066,6 +20502,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -19080,7 +20520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19151,6 +20591,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -19187,6 +20632,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19195,16 +20643,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>29526670.8</v>
+        <v>29497891.5</v>
       </c>
       <c r="C5" t="n">
-        <v>137351214</v>
+        <v>104886381.6</v>
       </c>
       <c r="D5" t="n">
-        <v>119656917.1</v>
+        <v>226725827.33</v>
       </c>
       <c r="E5" t="n">
-        <v>37859274.94</v>
+        <v>70893670.5</v>
       </c>
       <c r="F5" t="n">
         <v>20000.16</v>
@@ -19213,19 +20661,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1771777.26</v>
+        <v>36505080</v>
       </c>
       <c r="I5" t="n">
-        <v>57499.5</v>
+        <v>64288.14</v>
       </c>
       <c r="J5" t="n">
-        <v>104999.4</v>
+        <v>43700.4</v>
       </c>
       <c r="K5" t="n">
-        <v>1944380.76</v>
+        <v>3342983.49</v>
       </c>
       <c r="L5" t="n">
-        <v>534588.77</v>
+        <v>10159506</v>
+      </c>
+      <c r="M5" t="n">
+        <v>60480</v>
       </c>
     </row>
     <row r="6">
@@ -19233,37 +20684,40 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>53533497.6</v>
+        <v>53526211.2</v>
       </c>
       <c r="C6" t="n">
-        <v>216922860</v>
+        <v>165650184</v>
       </c>
       <c r="D6" t="n">
-        <v>176893051.68</v>
+        <v>335176807.68</v>
       </c>
       <c r="E6" t="n">
-        <v>41333783.4</v>
+        <v>77399887.5</v>
       </c>
       <c r="F6" t="n">
         <v>29166.9</v>
       </c>
       <c r="G6" t="n">
-        <v>93684</v>
+        <v>271674</v>
       </c>
       <c r="H6" t="n">
-        <v>392649.34</v>
+        <v>8090010</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>174999</v>
+        <v>72834</v>
       </c>
       <c r="K6" t="n">
-        <v>2995293.6</v>
+        <v>5292846.78</v>
       </c>
       <c r="L6" t="n">
-        <v>909375.71</v>
+        <v>17330652</v>
+      </c>
+      <c r="M6" t="n">
+        <v>115200</v>
       </c>
     </row>
     <row r="7">
@@ -19271,37 +20725,40 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>65133575.1</v>
+        <v>65132634.6</v>
       </c>
       <c r="C7" t="n">
-        <v>206708040</v>
+        <v>157849776</v>
       </c>
       <c r="D7" t="n">
-        <v>190905328.46</v>
+        <v>361727258.11</v>
       </c>
       <c r="E7" t="n">
-        <v>37420476.06</v>
+        <v>70071994.34999999</v>
       </c>
       <c r="F7" t="n">
         <v>275002.2</v>
       </c>
       <c r="G7" t="n">
-        <v>227605.5</v>
+        <v>661203</v>
       </c>
       <c r="H7" t="n">
-        <v>145407.24</v>
+        <v>2995920</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>163332.4</v>
+        <v>67978.39999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>3638727.04</v>
+        <v>6443575.42</v>
       </c>
       <c r="L7" t="n">
-        <v>1088236.08</v>
+        <v>20697120</v>
+      </c>
+      <c r="M7" t="n">
+        <v>453600</v>
       </c>
     </row>
     <row r="8">
@@ -19309,22 +20766,22 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>55239822</v>
+        <v>55239624</v>
       </c>
       <c r="C8" t="n">
-        <v>126070560</v>
+        <v>96272064</v>
       </c>
       <c r="D8" t="n">
-        <v>134317159.51</v>
+        <v>254504042.5</v>
       </c>
       <c r="E8" t="n">
-        <v>25991110.81</v>
+        <v>48669850.35</v>
       </c>
       <c r="F8" t="n">
         <v>514587.45</v>
       </c>
       <c r="G8" t="n">
-        <v>849566.25</v>
+        <v>2464020</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -19333,13 +20790,16 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>99166.10000000001</v>
+        <v>41272.6</v>
       </c>
       <c r="K8" t="n">
-        <v>2515278.6</v>
+        <v>4681575.3</v>
       </c>
       <c r="L8" t="n">
-        <v>825457.64</v>
+        <v>15684894</v>
+      </c>
+      <c r="M8" t="n">
+        <v>637200</v>
       </c>
     </row>
     <row r="9">
@@ -19350,34 +20810,37 @@
         <v>37894428</v>
       </c>
       <c r="C9" t="n">
-        <v>72626400</v>
+        <v>55460160</v>
       </c>
       <c r="D9" t="n">
-        <v>84420916.98</v>
+        <v>159960683.52</v>
       </c>
       <c r="E9" t="n">
-        <v>18643356.14</v>
+        <v>34910757</v>
       </c>
       <c r="F9" t="n">
         <v>708339</v>
       </c>
       <c r="G9" t="n">
-        <v>542040.75</v>
+        <v>1568403</v>
       </c>
       <c r="H9" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>221665.4</v>
+        <v>92256.39999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>1984062</v>
+        <v>3665103.99</v>
       </c>
       <c r="L9" t="n">
-        <v>639792.27</v>
+        <v>12185964</v>
+      </c>
+      <c r="M9" t="n">
+        <v>873000</v>
       </c>
     </row>
     <row r="10">
@@ -19388,19 +20851,19 @@
         <v>22584870</v>
       </c>
       <c r="C10" t="n">
-        <v>35065800</v>
+        <v>26777520</v>
       </c>
       <c r="D10" t="n">
-        <v>44161417.67</v>
+        <v>83677017.59999999</v>
       </c>
       <c r="E10" t="n">
-        <v>7790035.68</v>
+        <v>14587290</v>
       </c>
       <c r="F10" t="n">
         <v>125001</v>
       </c>
       <c r="G10" t="n">
-        <v>288600</v>
+        <v>842400</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -19412,10 +20875,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1088034</v>
+        <v>2154429.72</v>
       </c>
       <c r="L10" t="n">
-        <v>347843.86</v>
+        <v>6632280</v>
+      </c>
+      <c r="M10" t="n">
+        <v>711000</v>
       </c>
     </row>
     <row r="11">
@@ -19426,19 +20892,19 @@
         <v>14357574</v>
       </c>
       <c r="C11" t="n">
-        <v>13915440</v>
+        <v>10626336</v>
       </c>
       <c r="D11" t="n">
-        <v>18099018.63</v>
+        <v>34294005.5</v>
       </c>
       <c r="E11" t="n">
-        <v>1970590.51</v>
+        <v>3690044.1</v>
       </c>
       <c r="F11" t="n">
         <v>41667</v>
       </c>
       <c r="G11" t="n">
-        <v>292485</v>
+        <v>853740</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -19447,13 +20913,16 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>116666</v>
+        <v>48556</v>
       </c>
       <c r="K11" t="n">
-        <v>384012</v>
+        <v>785296.1899999999</v>
       </c>
       <c r="L11" t="n">
-        <v>165321</v>
+        <v>3105000</v>
+      </c>
+      <c r="M11" t="n">
+        <v>585000</v>
       </c>
     </row>
     <row r="12">
@@ -19464,19 +20933,19 @@
         <v>5962770</v>
       </c>
       <c r="C12" t="n">
-        <v>1829520</v>
+        <v>1397088</v>
       </c>
       <c r="D12" t="n">
-        <v>2455030.54</v>
+        <v>4651789.82</v>
       </c>
       <c r="E12" t="n">
-        <v>237780.14</v>
+        <v>445257</v>
       </c>
       <c r="F12" t="n">
         <v>83334</v>
       </c>
       <c r="G12" t="n">
-        <v>72150</v>
+        <v>210600</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -19488,10 +20957,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>85336</v>
+        <v>180045.65</v>
       </c>
       <c r="L12" t="n">
-        <v>37020.6</v>
+        <v>675000</v>
+      </c>
+      <c r="M12" t="n">
+        <v>234000</v>
       </c>
     </row>
     <row r="13">
@@ -19502,19 +20974,19 @@
         <v>1657260</v>
       </c>
       <c r="C13" t="n">
-        <v>1053360</v>
+        <v>804384</v>
       </c>
       <c r="D13" t="n">
-        <v>1447810.74</v>
+        <v>2743310.59</v>
       </c>
       <c r="E13" t="n">
-        <v>263249.48</v>
+        <v>492949.8</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>17205</v>
+        <v>50220</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -19529,7 +21001,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>13564.8</v>
+        <v>259200</v>
+      </c>
+      <c r="M13" t="n">
+        <v>27000</v>
       </c>
     </row>
     <row r="14">
@@ -19540,19 +21015,19 @@
         <v>744480</v>
       </c>
       <c r="C14" t="n">
-        <v>221760</v>
+        <v>169344</v>
       </c>
       <c r="D14" t="n">
-        <v>312025.06</v>
+        <v>591224.83</v>
       </c>
       <c r="E14" t="n">
-        <v>94399.05</v>
+        <v>176767.65</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>13875</v>
+        <v>40500</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -19567,7 +21042,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>4804.2</v>
+        <v>91800</v>
+      </c>
+      <c r="M14" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="15">
@@ -19578,10 +21056,10 @@
         <v>342540</v>
       </c>
       <c r="C15" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D15" t="n">
-        <v>118694.72</v>
+        <v>224902.66</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -19590,7 +21068,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>2775</v>
+        <v>8100</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -19602,10 +21080,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>21334</v>
+        <v>47876.22</v>
       </c>
       <c r="L15" t="n">
-        <v>2826</v>
+        <v>54000</v>
+      </c>
+      <c r="M15" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="16">
@@ -19616,10 +21097,10 @@
         <v>282744</v>
       </c>
       <c r="C16" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D16" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -19643,7 +21124,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>565.2</v>
+        <v>10800</v>
+      </c>
+      <c r="M16" t="n">
+        <v>180000</v>
       </c>
     </row>
     <row r="17">
@@ -19666,7 +21150,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>2775</v>
+        <v>8100</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -19681,7 +21165,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>847.8</v>
+        <v>16200</v>
+      </c>
+      <c r="M17" t="n">
+        <v>27000</v>
       </c>
     </row>
     <row r="18">
@@ -19721,6 +21208,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>9000</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -19759,6 +21249,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>18000</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -19797,6 +21290,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>18000</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -19806,10 +21302,10 @@
         <v>12474</v>
       </c>
       <c r="C21" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D21" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -19834,6 +21330,9 @@
       </c>
       <c r="L21" t="n">
         <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="22">
@@ -19873,6 +21372,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -19911,6 +21413,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -19920,10 +21425,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D24" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -19947,6 +21452,9 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19998,6 +21506,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -20012,7 +21524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20083,6 +21595,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -20104,10 +21621,10 @@
         <v>21</v>
       </c>
       <c r="G4" t="n">
-        <v>129960</v>
+        <v>129990</v>
       </c>
       <c r="H4" t="n">
-        <v>27900</v>
+        <v>27960</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -20119,7 +21636,10 @@
         <v>256</v>
       </c>
       <c r="L4" t="n">
-        <v>358740</v>
+        <v>357180</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -20142,7 +21662,7 @@
         <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>75210</v>
+        <v>75420</v>
       </c>
       <c r="H5" t="n">
         <v>25680</v>
@@ -20157,7 +21677,10 @@
         <v>135</v>
       </c>
       <c r="L5" t="n">
-        <v>165450</v>
+        <v>166440</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -20180,10 +21703,10 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>27900</v>
+        <v>28050</v>
       </c>
       <c r="H6" t="n">
-        <v>4260</v>
+        <v>4320</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -20195,7 +21718,10 @@
         <v>46</v>
       </c>
       <c r="L6" t="n">
-        <v>61560</v>
+        <v>61380</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -20235,6 +21761,9 @@
       <c r="L7" t="n">
         <v>8640</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -20271,7 +21800,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2880</v>
+        <v>2850</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -20294,7 +21826,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H9" t="n">
         <v>60</v>
@@ -20310,6 +21842,9 @@
       </c>
       <c r="L9" t="n">
         <v>630</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -20349,6 +21884,9 @@
       <c r="L10" t="n">
         <v>270</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -20387,6 +21925,9 @@
       <c r="L11" t="n">
         <v>30</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -20425,6 +21966,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -20463,6 +22007,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -20501,6 +22048,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -20539,6 +22089,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -20577,6 +22130,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -20615,6 +22171,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -20653,6 +22212,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -20691,6 +22253,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -20729,6 +22294,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -20767,6 +22335,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -20805,6 +22376,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -20843,6 +22417,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -20881,6 +22458,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -20930,6 +22510,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -20944,7 +22528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21015,6 +22599,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -21051,6 +22640,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21086,10 +22678,13 @@
         <v>1.8</v>
       </c>
       <c r="K5" t="n">
-        <v>56.7</v>
+        <v>44.68</v>
       </c>
       <c r="L5" t="n">
-        <v>34744.5</v>
+        <v>34952.4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -21112,10 +22707,10 @@
         <v>0.5</v>
       </c>
       <c r="G6" t="n">
-        <v>1395</v>
+        <v>1402.5</v>
       </c>
       <c r="H6" t="n">
-        <v>2428.2</v>
+        <v>2462.4</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -21124,10 +22719,13 @@
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>29.9</v>
+        <v>23.32</v>
       </c>
       <c r="L6" t="n">
-        <v>22777.2</v>
+        <v>22710.6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -21162,10 +22760,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3.28</v>
+        <v>2.55</v>
       </c>
       <c r="L7" t="n">
         <v>5184</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -21203,7 +22804,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2044.8</v>
+        <v>2023.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -21226,7 +22830,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>25.5</v>
+        <v>51</v>
       </c>
       <c r="H9" t="n">
         <v>60</v>
@@ -21242,6 +22846,9 @@
       </c>
       <c r="L9" t="n">
         <v>510.3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -21281,6 +22888,9 @@
       <c r="L10" t="n">
         <v>240.3</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -21319,6 +22929,9 @@
       <c r="L11" t="n">
         <v>30</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -21357,6 +22970,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -21395,6 +23011,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -21433,6 +23052,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -21471,6 +23093,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -21509,6 +23134,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -21547,6 +23175,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -21585,6 +23216,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -21623,6 +23257,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -21661,6 +23298,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -21699,6 +23339,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -21737,6 +23380,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -21775,6 +23421,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -21813,6 +23462,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -21862,6 +23514,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -21876,7 +23532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21947,6 +23603,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -21983,6 +23644,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21994,13 +23658,13 @@
         <v>18944976.6</v>
       </c>
       <c r="C5" t="n">
-        <v>68225850</v>
+        <v>52099740</v>
       </c>
       <c r="D5" t="n">
-        <v>59436641.58</v>
+        <v>112620499.2</v>
       </c>
       <c r="E5" t="n">
-        <v>4810139.76</v>
+        <v>9007263.449999999</v>
       </c>
       <c r="F5" t="n">
         <v>6666.72</v>
@@ -22009,19 +23673,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2557573.92</v>
+        <v>52695360</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>104999.4</v>
+        <v>43700.4</v>
       </c>
       <c r="K5" t="n">
-        <v>1209637.8</v>
+        <v>2169724.86</v>
       </c>
       <c r="L5" t="n">
-        <v>327293.19</v>
+        <v>6291432</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -22032,34 +23699,37 @@
         <v>12782721.6</v>
       </c>
       <c r="C6" t="n">
-        <v>36224496</v>
+        <v>27662342.4</v>
       </c>
       <c r="D6" t="n">
-        <v>29539817.26</v>
+        <v>55972021.25</v>
       </c>
       <c r="E6" t="n">
-        <v>2129740.7</v>
+        <v>3988062</v>
       </c>
       <c r="F6" t="n">
         <v>20833.5</v>
       </c>
       <c r="G6" t="n">
-        <v>25807.5</v>
+        <v>75735</v>
       </c>
       <c r="H6" t="n">
-        <v>671761.53</v>
+        <v>14035680</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>29166.5</v>
+        <v>12139</v>
       </c>
       <c r="K6" t="n">
-        <v>637886.6</v>
+        <v>1132423.03</v>
       </c>
       <c r="L6" t="n">
-        <v>214561.22</v>
+        <v>4087908</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -22070,22 +23740,22 @@
         <v>917928</v>
       </c>
       <c r="C7" t="n">
-        <v>6292440</v>
+        <v>4805136</v>
       </c>
       <c r="D7" t="n">
-        <v>5811386.56</v>
+        <v>11011410.43</v>
       </c>
       <c r="E7" t="n">
-        <v>317421.57</v>
+        <v>594390.15</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2497.5</v>
+        <v>7290</v>
       </c>
       <c r="H7" t="n">
-        <v>121172.7</v>
+        <v>2496600</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -22094,10 +23764,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>69975.52</v>
+        <v>123914.91</v>
       </c>
       <c r="L7" t="n">
-        <v>48833.28</v>
+        <v>933120</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -22108,10 +23781,10 @@
         <v>168894</v>
       </c>
       <c r="C8" t="n">
-        <v>693000</v>
+        <v>529200</v>
       </c>
       <c r="D8" t="n">
-        <v>738330.91</v>
+        <v>1398988.8</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -22120,10 +23793,10 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3607.5</v>
+        <v>10530</v>
       </c>
       <c r="H8" t="n">
-        <v>63491.18</v>
+        <v>1308150</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -22135,7 +23808,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>19262.02</v>
+        <v>364230</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -22146,10 +23822,10 @@
         <v>60984</v>
       </c>
       <c r="C9" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D9" t="n">
-        <v>128886.9</v>
+        <v>244214.78</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -22158,10 +23834,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>471.75</v>
+        <v>2754</v>
       </c>
       <c r="H9" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -22173,7 +23849,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>4807.03</v>
+        <v>91854</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -22211,7 +23890,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2263.63</v>
+        <v>43254</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -22237,7 +23919,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -22249,7 +23931,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>282.6</v>
+        <v>5400</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -22289,6 +23974,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -22327,6 +24015,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -22365,6 +24056,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -22403,6 +24097,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -22441,6 +24138,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -22479,6 +24179,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -22517,6 +24220,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -22555,6 +24261,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -22593,6 +24302,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -22631,6 +24343,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -22669,6 +24384,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -22707,6 +24425,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -22745,6 +24466,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -22794,6 +24518,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>

--- a/risk/Risk_Analysis_T3_25yrs_Present_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_25yrs_Present_Breaches.xlsx
@@ -549,7 +549,7 @@
         <v>35</v>
       </c>
       <c r="K4" t="n">
-        <v>873</v>
+        <v>352</v>
       </c>
       <c r="L4" t="n">
         <v>1264650</v>
@@ -590,7 +590,7 @@
         <v>20</v>
       </c>
       <c r="K5" t="n">
-        <v>682</v>
+        <v>237</v>
       </c>
       <c r="L5" t="n">
         <v>919980</v>
@@ -631,7 +631,7 @@
         <v>12</v>
       </c>
       <c r="K6" t="n">
-        <v>421</v>
+        <v>110</v>
       </c>
       <c r="L6" t="n">
         <v>577980</v>
@@ -672,7 +672,7 @@
         <v>9</v>
       </c>
       <c r="K7" t="n">
-        <v>317</v>
+        <v>88</v>
       </c>
       <c r="L7" t="n">
         <v>346380</v>
@@ -713,7 +713,7 @@
         <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>194</v>
+        <v>40</v>
       </c>
       <c r="L8" t="n">
         <v>243990</v>
@@ -754,7 +754,7 @@
         <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="L9" t="n">
         <v>189570</v>
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="L10" t="n">
         <v>97170</v>
@@ -836,7 +836,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>44790</v>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>16860</v>
@@ -918,7 +918,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>6480</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>4110</v>
@@ -1553,7 +1553,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="L4" t="n">
         <v>35160</v>
@@ -1594,7 +1594,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="L5" t="n">
         <v>51270</v>
@@ -1635,7 +1635,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="L6" t="n">
         <v>55590</v>
@@ -1676,7 +1676,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
         <v>49710</v>
@@ -1717,7 +1717,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
         <v>73890</v>
@@ -1758,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="L9" t="n">
         <v>93600</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>50310</v>
@@ -1840,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>23490</v>
@@ -1881,7 +1881,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>11040</v>
@@ -1922,7 +1922,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>4020</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>3330</v>
@@ -2598,7 +2598,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>10.26</v>
+        <v>6.62</v>
       </c>
       <c r="L5" t="n">
         <v>10766.7</v>
@@ -2639,7 +2639,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>17.24</v>
+        <v>4.56</v>
       </c>
       <c r="L6" t="n">
         <v>20568.3</v>
@@ -2680,7 +2680,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>14.04</v>
+        <v>2.55</v>
       </c>
       <c r="L7" t="n">
         <v>29826</v>
@@ -2721,7 +2721,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>22.82</v>
+        <v>2.21</v>
       </c>
       <c r="L8" t="n">
         <v>52461.9</v>
@@ -2762,7 +2762,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>39.35</v>
+        <v>6.42</v>
       </c>
       <c r="L9" t="n">
         <v>75816</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>22.62</v>
+        <v>1.74</v>
       </c>
       <c r="L10" t="n">
         <v>44775.9</v>
@@ -2844,7 +2844,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>9.880000000000001</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>23490</v>
@@ -2885,7 +2885,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>11040</v>
@@ -2926,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>4020</v>
@@ -3008,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>3330</v>
@@ -3602,7 +3602,7 @@
         <v>7283.4</v>
       </c>
       <c r="K5" t="n">
-        <v>498233.12</v>
+        <v>321440.72</v>
       </c>
       <c r="L5" t="n">
         <v>1938006</v>
@@ -3643,7 +3643,7 @@
         <v>24278</v>
       </c>
       <c r="K6" t="n">
-        <v>837008.33</v>
+        <v>221561.03</v>
       </c>
       <c r="L6" t="n">
         <v>3702294</v>
@@ -3684,7 +3684,7 @@
         <v>50983.8</v>
       </c>
       <c r="K7" t="n">
-        <v>681532.02</v>
+        <v>123914.91</v>
       </c>
       <c r="L7" t="n">
         <v>5368680</v>
@@ -3725,7 +3725,7 @@
         <v>41272.6</v>
       </c>
       <c r="K8" t="n">
-        <v>1107853.7</v>
+        <v>107211.65</v>
       </c>
       <c r="L8" t="n">
         <v>9443142</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1910532.93</v>
+        <v>311923.74</v>
       </c>
       <c r="L9" t="n">
         <v>13646880</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1098336.72</v>
+        <v>84487.44</v>
       </c>
       <c r="L10" t="n">
         <v>8059662</v>
@@ -3848,7 +3848,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>479903.23</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>4228200</v>
@@ -3889,7 +3889,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>315079.88</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>1987200</v>
@@ -3930,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>92207.84</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>723600</v>
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>47876.22</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>599400</v>
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="L4" t="n">
         <v>103020</v>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L5" t="n">
         <v>35190</v>
@@ -4647,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>8190</v>
@@ -5610,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4.96</v>
+        <v>2.32</v>
       </c>
       <c r="L5" t="n">
         <v>7389.9</v>
@@ -5651,7 +5651,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.01</v>
+        <v>0.51</v>
       </c>
       <c r="L6" t="n">
         <v>3030.3</v>
@@ -6614,7 +6614,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>241080.54</v>
+        <v>112504.25</v>
       </c>
       <c r="L5" t="n">
         <v>1330182</v>
@@ -6655,7 +6655,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>49235.78</v>
+        <v>24617.89</v>
       </c>
       <c r="L6" t="n">
         <v>545454</v>
@@ -7577,7 +7577,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
         <v>53280</v>
@@ -7618,7 +7618,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>13650</v>
@@ -7659,7 +7659,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>2640</v>
@@ -7700,7 +7700,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>510</v>
@@ -8622,7 +8622,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>2866.5</v>
@@ -8663,7 +8663,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>976.8</v>
@@ -8704,7 +8704,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>306</v>
@@ -9626,7 +9626,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>128576.29</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>515970</v>
@@ -9667,7 +9667,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>73853.67999999999</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>175824</v>
@@ -9708,7 +9708,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>61957.46</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>55080</v>
@@ -10589,7 +10589,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>227</v>
+        <v>124</v>
       </c>
       <c r="L4" t="n">
         <v>221820</v>
@@ -10630,7 +10630,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>263</v>
+        <v>98</v>
       </c>
       <c r="L5" t="n">
         <v>261180</v>
@@ -10671,7 +10671,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="L6" t="n">
         <v>135930</v>
@@ -10712,7 +10712,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="L7" t="n">
         <v>68460</v>
@@ -10753,7 +10753,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
         <v>34170</v>
@@ -10794,7 +10794,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
         <v>8940</v>
@@ -11040,7 +11040,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>480</v>
@@ -11634,7 +11634,7 @@
         <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>225.74</v>
+        <v>78.45</v>
       </c>
       <c r="L5" t="n">
         <v>193195.8</v>
@@ -11675,7 +11675,7 @@
         <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>213.45</v>
+        <v>55.77</v>
       </c>
       <c r="L6" t="n">
         <v>213852.6</v>
@@ -11716,7 +11716,7 @@
         <v>6.3</v>
       </c>
       <c r="K7" t="n">
-        <v>202.25</v>
+        <v>56.14</v>
       </c>
       <c r="L7" t="n">
         <v>207828</v>
@@ -11757,7 +11757,7 @@
         <v>4.25</v>
       </c>
       <c r="K8" t="n">
-        <v>142.78</v>
+        <v>29.44</v>
       </c>
       <c r="L8" t="n">
         <v>173232.9</v>
@@ -11798,7 +11798,7 @@
         <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>121.25</v>
+        <v>28.1</v>
       </c>
       <c r="L9" t="n">
         <v>153551.7</v>
@@ -11839,7 +11839,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>66.98999999999999</v>
+        <v>5.22</v>
       </c>
       <c r="L10" t="n">
         <v>86481.3</v>
@@ -11880,7 +11880,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>26.06</v>
+        <v>0.9</v>
       </c>
       <c r="L11" t="n">
         <v>44790</v>
@@ -11921,7 +11921,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>16860</v>
@@ -11962,7 +11962,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>6480</v>
@@ -12044,7 +12044,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>4110</v>
@@ -12638,7 +12638,7 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>87.05</v>
+        <v>32.44</v>
       </c>
       <c r="L5" t="n">
         <v>54847.8</v>
@@ -12679,7 +12679,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>60.84</v>
+        <v>17.24</v>
       </c>
       <c r="L6" t="n">
         <v>50294.1</v>
@@ -12720,7 +12720,7 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>51.68</v>
+        <v>18.5</v>
       </c>
       <c r="L7" t="n">
         <v>41076</v>
@@ -12761,7 +12761,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>22.82</v>
+        <v>3.68</v>
       </c>
       <c r="L8" t="n">
         <v>24260.7</v>
@@ -12802,7 +12802,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>5.62</v>
+        <v>3.21</v>
       </c>
       <c r="L9" t="n">
         <v>7241.4</v>
@@ -13048,7 +13048,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>480</v>
@@ -13642,7 +13642,7 @@
         <v>50983.8</v>
       </c>
       <c r="K5" t="n">
-        <v>4226945.47</v>
+        <v>1575059.53</v>
       </c>
       <c r="L5" t="n">
         <v>9872604</v>
@@ -13683,7 +13683,7 @@
         <v>36417</v>
       </c>
       <c r="K6" t="n">
-        <v>2954147.04</v>
+        <v>837008.33</v>
       </c>
       <c r="L6" t="n">
         <v>9052938</v>
@@ -13724,7 +13724,7 @@
         <v>33989.2</v>
       </c>
       <c r="K7" t="n">
-        <v>2509276.97</v>
+        <v>898383.11</v>
       </c>
       <c r="L7" t="n">
         <v>7393680</v>
@@ -13765,7 +13765,7 @@
         <v>20636.3</v>
       </c>
       <c r="K8" t="n">
-        <v>1107853.7</v>
+        <v>178686.08</v>
       </c>
       <c r="L8" t="n">
         <v>4366926</v>
@@ -13806,7 +13806,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>272933.28</v>
+        <v>155961.87</v>
       </c>
       <c r="L9" t="n">
         <v>1303452</v>
@@ -14052,7 +14052,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>47876.22</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>86400</v>
@@ -14605,7 +14605,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="L4" t="n">
         <v>224280</v>
@@ -14646,7 +14646,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="L5" t="n">
         <v>62580</v>
@@ -15650,7 +15650,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6.29</v>
+        <v>3.64</v>
       </c>
       <c r="L5" t="n">
         <v>13141.8</v>
@@ -16654,7 +16654,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>305368.68</v>
+        <v>176792.4</v>
       </c>
       <c r="L5" t="n">
         <v>2365524</v>
@@ -17658,7 +17658,7 @@
         <v>145668</v>
       </c>
       <c r="K5" t="n">
-        <v>10961128.55</v>
+        <v>3809072.53</v>
       </c>
       <c r="L5" t="n">
         <v>34775244</v>
@@ -17699,7 +17699,7 @@
         <v>145668</v>
       </c>
       <c r="K6" t="n">
-        <v>10364132.53</v>
+        <v>2707968.12</v>
       </c>
       <c r="L6" t="n">
         <v>38493468</v>
@@ -17740,7 +17740,7 @@
         <v>152951.4</v>
       </c>
       <c r="K7" t="n">
-        <v>9820256.779999999</v>
+        <v>2726128.06</v>
       </c>
       <c r="L7" t="n">
         <v>37409040</v>
@@ -17781,7 +17781,7 @@
         <v>103181.5</v>
       </c>
       <c r="K8" t="n">
-        <v>6933019.9</v>
+        <v>1429488.64</v>
       </c>
       <c r="L8" t="n">
         <v>31181922</v>
@@ -17822,7 +17822,7 @@
         <v>92256.39999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>5887560.67</v>
+        <v>1364666.38</v>
       </c>
       <c r="L9" t="n">
         <v>27639306</v>
@@ -17863,7 +17863,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>3252766.44</v>
+        <v>253462.32</v>
       </c>
       <c r="L10" t="n">
         <v>15566634</v>
@@ -17904,7 +17904,7 @@
         <v>48556</v>
       </c>
       <c r="K11" t="n">
-        <v>1265199.41</v>
+        <v>43627.57</v>
       </c>
       <c r="L11" t="n">
         <v>8062200</v>
@@ -17945,7 +17945,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>495125.53</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>3034800</v>
@@ -17986,7 +17986,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>92207.84</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>1166400</v>
@@ -18068,7 +18068,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>143628.65</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>739800</v>
@@ -18621,7 +18621,7 @@
         <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>179</v>
+        <v>75</v>
       </c>
       <c r="L4" t="n">
         <v>208830</v>
@@ -18662,7 +18662,7 @@
         <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>208</v>
+        <v>64</v>
       </c>
       <c r="L5" t="n">
         <v>268770</v>
@@ -18703,7 +18703,7 @@
         <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>215</v>
+        <v>59</v>
       </c>
       <c r="L6" t="n">
         <v>260220</v>
@@ -18744,7 +18744,7 @@
         <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>208</v>
+        <v>55</v>
       </c>
       <c r="L7" t="n">
         <v>191640</v>
@@ -18785,7 +18785,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>131</v>
+        <v>32</v>
       </c>
       <c r="L8" t="n">
         <v>122730</v>
@@ -18826,7 +18826,7 @@
         <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="L9" t="n">
         <v>83580</v>
@@ -18867,7 +18867,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>41400</v>
@@ -18908,7 +18908,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>17250</v>
@@ -18949,7 +18949,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>3750</v>
@@ -19072,7 +19072,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>300</v>
@@ -19666,7 +19666,7 @@
         <v>1.8</v>
       </c>
       <c r="K5" t="n">
-        <v>68.84999999999999</v>
+        <v>21.18</v>
       </c>
       <c r="L5" t="n">
         <v>56441.7</v>
@@ -19707,7 +19707,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>109</v>
+        <v>29.91</v>
       </c>
       <c r="L6" t="n">
         <v>96281.39999999999</v>
@@ -19748,7 +19748,7 @@
         <v>2.8</v>
       </c>
       <c r="K7" t="n">
-        <v>132.7</v>
+        <v>35.09</v>
       </c>
       <c r="L7" t="n">
         <v>114984</v>
@@ -19789,7 +19789,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>96.42</v>
+        <v>23.55</v>
       </c>
       <c r="L8" t="n">
         <v>87138.3</v>
@@ -19830,7 +19830,7 @@
         <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>75.48</v>
+        <v>17.67</v>
       </c>
       <c r="L9" t="n">
         <v>67699.8</v>
@@ -19871,7 +19871,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>44.37</v>
+        <v>3.48</v>
       </c>
       <c r="L10" t="n">
         <v>36846</v>
@@ -19912,7 +19912,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>16.17</v>
+        <v>0.9</v>
       </c>
       <c r="L11" t="n">
         <v>17250</v>
@@ -19953,7 +19953,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>3750</v>
@@ -20076,7 +20076,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>300</v>
@@ -20670,7 +20670,7 @@
         <v>43700.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3342983.49</v>
+        <v>1028610.3</v>
       </c>
       <c r="L5" t="n">
         <v>10159506</v>
@@ -20711,7 +20711,7 @@
         <v>72834</v>
       </c>
       <c r="K6" t="n">
-        <v>5292846.78</v>
+        <v>1452455.63</v>
       </c>
       <c r="L6" t="n">
         <v>17330652</v>
@@ -20752,7 +20752,7 @@
         <v>67978.39999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>6443575.42</v>
+        <v>1703830.04</v>
       </c>
       <c r="L7" t="n">
         <v>20697120</v>
@@ -20793,7 +20793,7 @@
         <v>41272.6</v>
       </c>
       <c r="K8" t="n">
-        <v>4681575.3</v>
+        <v>1143590.91</v>
       </c>
       <c r="L8" t="n">
         <v>15684894</v>
@@ -20834,7 +20834,7 @@
         <v>92256.39999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>3665103.99</v>
+        <v>857790.3</v>
       </c>
       <c r="L9" t="n">
         <v>12185964</v>
@@ -20875,7 +20875,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2154429.72</v>
+        <v>168974.88</v>
       </c>
       <c r="L10" t="n">
         <v>6632280</v>
@@ -20916,7 +20916,7 @@
         <v>48556</v>
       </c>
       <c r="K11" t="n">
-        <v>785296.1899999999</v>
+        <v>43627.57</v>
       </c>
       <c r="L11" t="n">
         <v>3105000</v>
@@ -20957,7 +20957,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>180045.65</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>675000</v>
@@ -21080,7 +21080,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>47876.22</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>54000</v>
@@ -21633,7 +21633,7 @@
         <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>256</v>
+        <v>72</v>
       </c>
       <c r="L4" t="n">
         <v>357180</v>
@@ -21674,7 +21674,7 @@
         <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>135</v>
+        <v>37</v>
       </c>
       <c r="L5" t="n">
         <v>166440</v>
@@ -21715,7 +21715,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="L6" t="n">
         <v>61380</v>
@@ -21756,7 +21756,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>8640</v>
@@ -22678,7 +22678,7 @@
         <v>1.8</v>
       </c>
       <c r="K5" t="n">
-        <v>44.68</v>
+        <v>12.25</v>
       </c>
       <c r="L5" t="n">
         <v>34952.4</v>
@@ -22719,7 +22719,7 @@
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>23.32</v>
+        <v>3.55</v>
       </c>
       <c r="L6" t="n">
         <v>22710.6</v>
@@ -22760,7 +22760,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>5184</v>
@@ -23682,7 +23682,7 @@
         <v>43700.4</v>
       </c>
       <c r="K5" t="n">
-        <v>2169724.86</v>
+        <v>594665.33</v>
       </c>
       <c r="L5" t="n">
         <v>6291432</v>
@@ -23723,7 +23723,7 @@
         <v>12139</v>
       </c>
       <c r="K6" t="n">
-        <v>1132423.03</v>
+        <v>172325.24</v>
       </c>
       <c r="L6" t="n">
         <v>4087908</v>
@@ -23764,7 +23764,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>123914.91</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>933120</v>

--- a/risk/Risk_Analysis_T3_25yrs_Present_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_25yrs_Present_Breaches.xlsx
@@ -560,7 +560,7 @@
         <v>471870</v>
       </c>
       <c r="H4" t="n">
-        <v>74790</v>
+        <v>80400</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
@@ -572,22 +572,22 @@
         <v>352</v>
       </c>
       <c r="L4" t="n">
-        <v>1264650</v>
+        <v>1356930</v>
       </c>
       <c r="M4" t="n">
-        <v>69390</v>
+        <v>50220</v>
       </c>
       <c r="N4" t="n">
-        <v>56280</v>
+        <v>64620</v>
       </c>
       <c r="O4" t="n">
-        <v>228270</v>
+        <v>241320</v>
       </c>
       <c r="P4" t="n">
-        <v>57900</v>
+        <v>20070</v>
       </c>
       <c r="Q4" t="n">
-        <v>190696.28</v>
+        <v>1976167.06</v>
       </c>
     </row>
     <row r="5">
@@ -613,7 +613,7 @@
         <v>353460</v>
       </c>
       <c r="H5" t="n">
-        <v>66780</v>
+        <v>72330</v>
       </c>
       <c r="I5" t="n">
         <v>2</v>
@@ -625,22 +625,22 @@
         <v>237</v>
       </c>
       <c r="L5" t="n">
-        <v>919980</v>
+        <v>956400</v>
       </c>
       <c r="M5" t="n">
-        <v>42990</v>
+        <v>40800</v>
       </c>
       <c r="N5" t="n">
-        <v>20850</v>
+        <v>30420</v>
       </c>
       <c r="O5" t="n">
-        <v>173490</v>
+        <v>196110</v>
       </c>
       <c r="P5" t="n">
-        <v>71400</v>
+        <v>49140</v>
       </c>
       <c r="Q5" t="n">
-        <v>142480.72</v>
+        <v>1476513.96</v>
       </c>
     </row>
     <row r="6">
@@ -666,7 +666,7 @@
         <v>240750</v>
       </c>
       <c r="H6" t="n">
-        <v>19380</v>
+        <v>22020</v>
       </c>
       <c r="I6" t="n">
         <v>3</v>
@@ -678,22 +678,22 @@
         <v>110</v>
       </c>
       <c r="L6" t="n">
-        <v>577980</v>
+        <v>608550</v>
       </c>
       <c r="M6" t="n">
-        <v>20760</v>
+        <v>29010</v>
       </c>
       <c r="N6" t="n">
-        <v>4950</v>
+        <v>9240</v>
       </c>
       <c r="O6" t="n">
-        <v>102300</v>
+        <v>117810</v>
       </c>
       <c r="P6" t="n">
-        <v>69300</v>
+        <v>54120</v>
       </c>
       <c r="Q6" t="n">
-        <v>104337.41</v>
+        <v>1081238.45</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>148320</v>
       </c>
       <c r="H7" t="n">
-        <v>5640</v>
+        <v>7080</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -731,22 +731,22 @@
         <v>88</v>
       </c>
       <c r="L7" t="n">
-        <v>346380</v>
+        <v>382200</v>
       </c>
       <c r="M7" t="n">
-        <v>13350</v>
+        <v>30870</v>
       </c>
       <c r="N7" t="n">
-        <v>690</v>
+        <v>2850</v>
       </c>
       <c r="O7" t="n">
-        <v>70680</v>
+        <v>79560</v>
       </c>
       <c r="P7" t="n">
-        <v>74130</v>
+        <v>60690</v>
       </c>
       <c r="Q7" t="n">
-        <v>82006.36</v>
+        <v>849823.96</v>
       </c>
     </row>
     <row r="8">
@@ -772,7 +772,7 @@
         <v>115170</v>
       </c>
       <c r="H8" t="n">
-        <v>5790</v>
+        <v>5580</v>
       </c>
       <c r="I8" t="n">
         <v>3</v>
@@ -784,22 +784,22 @@
         <v>40</v>
       </c>
       <c r="L8" t="n">
-        <v>243990</v>
+        <v>273060</v>
       </c>
       <c r="M8" t="n">
-        <v>8790</v>
+        <v>33750</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O8" t="n">
-        <v>29700</v>
+        <v>49530</v>
       </c>
       <c r="P8" t="n">
-        <v>81750</v>
+        <v>79920</v>
       </c>
       <c r="Q8" t="n">
-        <v>54448.97</v>
+        <v>564249.41</v>
       </c>
     </row>
     <row r="9">
@@ -825,7 +825,7 @@
         <v>72090</v>
       </c>
       <c r="H9" t="n">
-        <v>3270</v>
+        <v>4230</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -837,22 +837,22 @@
         <v>35</v>
       </c>
       <c r="L9" t="n">
-        <v>189570</v>
+        <v>226080</v>
       </c>
       <c r="M9" t="n">
-        <v>4920</v>
+        <v>27180</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>8760</v>
+        <v>20730</v>
       </c>
       <c r="P9" t="n">
-        <v>80970</v>
+        <v>95520</v>
       </c>
       <c r="Q9" t="n">
-        <v>34286.76</v>
+        <v>355310.34</v>
       </c>
     </row>
     <row r="10">
@@ -878,7 +878,7 @@
         <v>41190</v>
       </c>
       <c r="H10" t="n">
-        <v>900</v>
+        <v>1410</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -890,22 +890,22 @@
         <v>6</v>
       </c>
       <c r="L10" t="n">
-        <v>97170</v>
+        <v>144300</v>
       </c>
       <c r="M10" t="n">
-        <v>3360</v>
+        <v>25560</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3420</v>
+        <v>10230</v>
       </c>
       <c r="P10" t="n">
-        <v>72330</v>
+        <v>113070</v>
       </c>
       <c r="Q10" t="n">
-        <v>21143.62</v>
+        <v>219109.33</v>
       </c>
     </row>
     <row r="11">
@@ -931,7 +931,7 @@
         <v>26190</v>
       </c>
       <c r="H11" t="n">
-        <v>810</v>
+        <v>1080</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -943,22 +943,22 @@
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>44790</v>
+        <v>84720</v>
       </c>
       <c r="M11" t="n">
-        <v>2610</v>
+        <v>21660</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3540</v>
+        <v>4350</v>
       </c>
       <c r="P11" t="n">
-        <v>48030</v>
+        <v>81930</v>
       </c>
       <c r="Q11" t="n">
-        <v>12086.73</v>
+        <v>125253.58</v>
       </c>
     </row>
     <row r="12">
@@ -984,7 +984,7 @@
         <v>8400</v>
       </c>
       <c r="H12" t="n">
-        <v>150</v>
+        <v>270</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -996,22 +996,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>16860</v>
+        <v>42780</v>
       </c>
       <c r="M12" t="n">
-        <v>1590</v>
+        <v>11310</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>360</v>
+        <v>780</v>
       </c>
       <c r="P12" t="n">
-        <v>38970</v>
+        <v>62490</v>
       </c>
       <c r="Q12" t="n">
-        <v>5847.06</v>
+        <v>60592.5</v>
       </c>
     </row>
     <row r="13">
@@ -1037,7 +1037,7 @@
         <v>2280</v>
       </c>
       <c r="H13" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1049,22 +1049,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>6480</v>
+        <v>19860</v>
       </c>
       <c r="M13" t="n">
-        <v>960</v>
+        <v>6000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="P13" t="n">
-        <v>27330</v>
+        <v>31350</v>
       </c>
       <c r="Q13" t="n">
-        <v>2382.33</v>
+        <v>24687.81</v>
       </c>
     </row>
     <row r="14">
@@ -1090,7 +1090,7 @@
         <v>1560</v>
       </c>
       <c r="H14" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1102,10 +1102,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2790</v>
+        <v>12660</v>
       </c>
       <c r="M14" t="n">
-        <v>390</v>
+        <v>1560</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1114,10 +1114,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>39930</v>
+        <v>57450</v>
       </c>
       <c r="Q14" t="n">
-        <v>1729.02</v>
+        <v>17917.65</v>
       </c>
     </row>
     <row r="15">
@@ -1143,7 +1143,7 @@
         <v>390</v>
       </c>
       <c r="H15" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1155,22 +1155,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>4110</v>
+        <v>9480</v>
       </c>
       <c r="M15" t="n">
-        <v>2490</v>
+        <v>3660</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P15" t="n">
-        <v>20130</v>
+        <v>37050</v>
       </c>
       <c r="Q15" t="n">
-        <v>741.36</v>
+        <v>7682.63</v>
       </c>
     </row>
     <row r="16">
@@ -1208,10 +1208,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1920</v>
+        <v>6180</v>
       </c>
       <c r="M16" t="n">
-        <v>840</v>
+        <v>2820</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1220,10 +1220,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>18240</v>
+        <v>22140</v>
       </c>
       <c r="Q16" t="n">
-        <v>369.95</v>
+        <v>3833.8</v>
       </c>
     </row>
     <row r="17">
@@ -1249,7 +1249,7 @@
         <v>3900</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1261,22 +1261,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
+        <v>3210</v>
+      </c>
+      <c r="M17" t="n">
+        <v>510</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
         <v>150</v>
       </c>
-      <c r="M17" t="n">
-        <v>90</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>60</v>
-      </c>
       <c r="P17" t="n">
-        <v>18960</v>
+        <v>34560</v>
       </c>
       <c r="Q17" t="n">
-        <v>189.5</v>
+        <v>1963.74</v>
       </c>
     </row>
     <row r="18">
@@ -1314,10 +1314,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>210</v>
+        <v>960</v>
       </c>
       <c r="Q18" t="n">
-        <v>23.99</v>
+        <v>248.65</v>
       </c>
     </row>
     <row r="19">
@@ -1370,7 +1370,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1382,7 +1382,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.03</v>
+        <v>62.45</v>
       </c>
     </row>
     <row r="20">
@@ -1423,7 +1423,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -1435,7 +1435,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.23</v>
+        <v>12.72</v>
       </c>
     </row>
     <row r="21">
@@ -1476,7 +1476,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -1488,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.03</v>
+        <v>72.86</v>
       </c>
     </row>
     <row r="22">
@@ -1852,7 +1852,7 @@
         <v>10320</v>
       </c>
       <c r="H4" t="n">
-        <v>3300</v>
+        <v>3840</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1864,22 +1864,22 @@
         <v>11</v>
       </c>
       <c r="L4" t="n">
-        <v>35160</v>
+        <v>26220</v>
       </c>
       <c r="M4" t="n">
-        <v>11520</v>
+        <v>2640</v>
       </c>
       <c r="N4" t="n">
-        <v>810</v>
+        <v>540</v>
       </c>
       <c r="O4" t="n">
-        <v>270</v>
+        <v>330</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>488.24</v>
+        <v>55333.98</v>
       </c>
     </row>
     <row r="5">
@@ -1905,7 +1905,7 @@
         <v>18750</v>
       </c>
       <c r="H5" t="n">
-        <v>2970</v>
+        <v>2730</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1917,22 +1917,22 @@
         <v>20</v>
       </c>
       <c r="L5" t="n">
-        <v>51270</v>
+        <v>41670</v>
       </c>
       <c r="M5" t="n">
-        <v>13890</v>
+        <v>8040</v>
       </c>
       <c r="N5" t="n">
-        <v>150</v>
+        <v>570</v>
       </c>
       <c r="O5" t="n">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>936.58</v>
+        <v>106145.28</v>
       </c>
     </row>
     <row r="6">
@@ -1958,7 +1958,7 @@
         <v>23610</v>
       </c>
       <c r="H6" t="n">
-        <v>5700</v>
+        <v>5610</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -1970,22 +1970,22 @@
         <v>9</v>
       </c>
       <c r="L6" t="n">
-        <v>55590</v>
+        <v>55380</v>
       </c>
       <c r="M6" t="n">
-        <v>7140</v>
+        <v>5310</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="O6" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1706.05</v>
+        <v>193352.22</v>
       </c>
     </row>
     <row r="7">
@@ -2011,7 +2011,7 @@
         <v>16170</v>
       </c>
       <c r="H7" t="n">
-        <v>3540</v>
+        <v>4200</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -2023,22 +2023,22 @@
         <v>4</v>
       </c>
       <c r="L7" t="n">
-        <v>49710</v>
+        <v>51510</v>
       </c>
       <c r="M7" t="n">
-        <v>3870</v>
+        <v>3660</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1891.94</v>
+        <v>214420.32</v>
       </c>
     </row>
     <row r="8">
@@ -2064,7 +2064,7 @@
         <v>28920</v>
       </c>
       <c r="H8" t="n">
-        <v>5460</v>
+        <v>4740</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
@@ -2076,22 +2076,22 @@
         <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>73890</v>
+        <v>72270</v>
       </c>
       <c r="M8" t="n">
-        <v>1860</v>
+        <v>4560</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1828.17</v>
+        <v>207192.6</v>
       </c>
     </row>
     <row r="9">
@@ -2117,7 +2117,7 @@
         <v>34620</v>
       </c>
       <c r="H9" t="n">
-        <v>3180</v>
+        <v>3990</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -2129,22 +2129,22 @@
         <v>8</v>
       </c>
       <c r="L9" t="n">
-        <v>93600</v>
+        <v>98760</v>
       </c>
       <c r="M9" t="n">
-        <v>720</v>
+        <v>3870</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2152.76</v>
+        <v>243979.92</v>
       </c>
     </row>
     <row r="10">
@@ -2170,7 +2170,7 @@
         <v>24360</v>
       </c>
       <c r="H10" t="n">
-        <v>870</v>
+        <v>1080</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -2182,10 +2182,10 @@
         <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>50310</v>
+        <v>60060</v>
       </c>
       <c r="M10" t="n">
-        <v>450</v>
+        <v>3900</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -2197,7 +2197,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1577.96</v>
+        <v>178835.58</v>
       </c>
     </row>
     <row r="11">
@@ -2223,7 +2223,7 @@
         <v>10050</v>
       </c>
       <c r="H11" t="n">
-        <v>780</v>
+        <v>930</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -2235,10 +2235,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>23490</v>
+        <v>29940</v>
       </c>
       <c r="M11" t="n">
-        <v>390</v>
+        <v>3120</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -2250,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>677.86</v>
+        <v>76824.36</v>
       </c>
     </row>
     <row r="12">
@@ -2276,7 +2276,7 @@
         <v>4020</v>
       </c>
       <c r="H12" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -2288,10 +2288,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>11040</v>
+        <v>16080</v>
       </c>
       <c r="M12" t="n">
-        <v>300</v>
+        <v>2940</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>421.04</v>
+        <v>47717.64</v>
       </c>
     </row>
     <row r="13">
@@ -2329,7 +2329,7 @@
         <v>1140</v>
       </c>
       <c r="H13" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2341,10 +2341,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>4020</v>
+        <v>8310</v>
       </c>
       <c r="M13" t="n">
-        <v>720</v>
+        <v>2040</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2356,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>185.03</v>
+        <v>20970.18</v>
       </c>
     </row>
     <row r="14">
@@ -2382,7 +2382,7 @@
         <v>240</v>
       </c>
       <c r="H14" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -2394,10 +2394,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1440</v>
+        <v>2940</v>
       </c>
       <c r="M14" t="n">
-        <v>330</v>
+        <v>780</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>151.79</v>
+        <v>17203.32</v>
       </c>
     </row>
     <row r="15">
@@ -2435,7 +2435,7 @@
         <v>60</v>
       </c>
       <c r="H15" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>3330</v>
+        <v>5460</v>
       </c>
       <c r="M15" t="n">
-        <v>2340</v>
+        <v>3450</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>54.43</v>
+        <v>6168.96</v>
       </c>
     </row>
     <row r="16">
@@ -2500,10 +2500,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1230</v>
+        <v>2310</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1860</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>36.64</v>
+        <v>4152.42</v>
       </c>
     </row>
     <row r="17">
@@ -2541,7 +2541,7 @@
         <v>30</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2553,10 +2553,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>60</v>
+        <v>930</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.97</v>
+        <v>789.48</v>
       </c>
     </row>
     <row r="18">
@@ -2606,7 +2606,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.65</v>
+        <v>186.66</v>
       </c>
     </row>
     <row r="19">
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.08</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="20">
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1069.2</v>
+        <v>982.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -3209,22 +3209,22 @@
         <v>6.62</v>
       </c>
       <c r="L5" t="n">
-        <v>10766.7</v>
+        <v>8750.700000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>277.8</v>
+        <v>160.8</v>
       </c>
       <c r="N5" t="n">
-        <v>1.5</v>
+        <v>5.7</v>
       </c>
       <c r="O5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>46.83</v>
+        <v>5307.26</v>
       </c>
     </row>
     <row r="6">
@@ -3250,7 +3250,7 @@
         <v>1180.5</v>
       </c>
       <c r="H6" t="n">
-        <v>3249</v>
+        <v>3197.7</v>
       </c>
       <c r="I6" t="n">
         <v>0.51</v>
@@ -3262,22 +3262,22 @@
         <v>4.56</v>
       </c>
       <c r="L6" t="n">
-        <v>20568.3</v>
+        <v>20490.6</v>
       </c>
       <c r="M6" t="n">
-        <v>571.2</v>
+        <v>424.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O6" t="n">
-        <v>45</v>
+        <v>37.5</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1279.54</v>
+        <v>145014.16</v>
       </c>
     </row>
     <row r="7">
@@ -3303,7 +3303,7 @@
         <v>2425.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2584.2</v>
+        <v>3066</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3315,22 +3315,22 @@
         <v>2.55</v>
       </c>
       <c r="L7" t="n">
-        <v>29826</v>
+        <v>30906</v>
       </c>
       <c r="M7" t="n">
-        <v>1354.5</v>
+        <v>1281</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>10.5</v>
+        <v>42</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1513.56</v>
+        <v>171536.26</v>
       </c>
     </row>
     <row r="8">
@@ -3356,7 +3356,7 @@
         <v>18798</v>
       </c>
       <c r="H8" t="n">
-        <v>4641</v>
+        <v>4029</v>
       </c>
       <c r="I8" t="n">
         <v>1.47</v>
@@ -3368,22 +3368,22 @@
         <v>2.21</v>
       </c>
       <c r="L8" t="n">
-        <v>52461.9</v>
+        <v>51311.7</v>
       </c>
       <c r="M8" t="n">
-        <v>1023</v>
+        <v>2508</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1736.76</v>
+        <v>196832.97</v>
       </c>
     </row>
     <row r="9">
@@ -3409,7 +3409,7 @@
         <v>29427</v>
       </c>
       <c r="H9" t="n">
-        <v>3180</v>
+        <v>3990</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -3421,22 +3421,22 @@
         <v>6.42</v>
       </c>
       <c r="L9" t="n">
-        <v>75816</v>
+        <v>79995.60000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>504</v>
+        <v>2709</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>49.5</v>
+        <v>99</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2088.18</v>
+        <v>236660.52</v>
       </c>
     </row>
     <row r="10">
@@ -3462,7 +3462,7 @@
         <v>24360</v>
       </c>
       <c r="H10" t="n">
-        <v>870</v>
+        <v>1080</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -3474,10 +3474,10 @@
         <v>1.74</v>
       </c>
       <c r="L10" t="n">
-        <v>44775.9</v>
+        <v>53453.4</v>
       </c>
       <c r="M10" t="n">
-        <v>382.5</v>
+        <v>3315</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -3489,7 +3489,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1577.96</v>
+        <v>178835.58</v>
       </c>
     </row>
     <row r="11">
@@ -3515,7 +3515,7 @@
         <v>10050</v>
       </c>
       <c r="H11" t="n">
-        <v>780</v>
+        <v>930</v>
       </c>
       <c r="I11" t="n">
         <v>0.9</v>
@@ -3527,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>23490</v>
+        <v>29940</v>
       </c>
       <c r="M11" t="n">
-        <v>351</v>
+        <v>2808</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>677.86</v>
+        <v>76824.36</v>
       </c>
     </row>
     <row r="12">
@@ -3568,7 +3568,7 @@
         <v>4020</v>
       </c>
       <c r="H12" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -3580,10 +3580,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>11040</v>
+        <v>16080</v>
       </c>
       <c r="M12" t="n">
-        <v>285</v>
+        <v>2793</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>421.04</v>
+        <v>47717.64</v>
       </c>
     </row>
     <row r="13">
@@ -3621,7 +3621,7 @@
         <v>1140</v>
       </c>
       <c r="H13" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -3633,10 +3633,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>4020</v>
+        <v>8310</v>
       </c>
       <c r="M13" t="n">
-        <v>720</v>
+        <v>2040</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>185.03</v>
+        <v>20970.18</v>
       </c>
     </row>
     <row r="14">
@@ -3674,7 +3674,7 @@
         <v>240</v>
       </c>
       <c r="H14" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -3686,10 +3686,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1440</v>
+        <v>2940</v>
       </c>
       <c r="M14" t="n">
-        <v>330</v>
+        <v>780</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>151.79</v>
+        <v>17203.32</v>
       </c>
     </row>
     <row r="15">
@@ -3727,7 +3727,7 @@
         <v>60</v>
       </c>
       <c r="H15" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -3739,10 +3739,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>3330</v>
+        <v>5460</v>
       </c>
       <c r="M15" t="n">
-        <v>2340</v>
+        <v>3450</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>54.43</v>
+        <v>6168.96</v>
       </c>
     </row>
     <row r="16">
@@ -3792,10 +3792,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1230</v>
+        <v>2310</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1860</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>36.64</v>
+        <v>4152.42</v>
       </c>
     </row>
     <row r="17">
@@ -3833,7 +3833,7 @@
         <v>30</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -3845,10 +3845,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>60</v>
+        <v>930</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.97</v>
+        <v>789.48</v>
       </c>
     </row>
     <row r="18">
@@ -3898,7 +3898,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.65</v>
+        <v>186.66</v>
       </c>
     </row>
     <row r="19">
@@ -3966,7 +3966,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.08</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="20">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6094440</v>
+        <v>5601960</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -4501,22 +4501,22 @@
         <v>321440.72</v>
       </c>
       <c r="L5" t="n">
-        <v>1938006</v>
+        <v>1575126</v>
       </c>
       <c r="M5" t="n">
-        <v>97230</v>
+        <v>56280</v>
       </c>
       <c r="N5" t="n">
-        <v>255</v>
+        <v>969</v>
       </c>
       <c r="O5" t="n">
-        <v>3060</v>
+        <v>3570</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>28097.28</v>
+        <v>3184358.4</v>
       </c>
     </row>
     <row r="6">
@@ -4542,7 +4542,7 @@
         <v>63747</v>
       </c>
       <c r="H6" t="n">
-        <v>18519300</v>
+        <v>18226890</v>
       </c>
       <c r="I6" t="n">
         <v>98471.57000000001</v>
@@ -4554,22 +4554,22 @@
         <v>221561.03</v>
       </c>
       <c r="L6" t="n">
-        <v>3702294</v>
+        <v>3688308</v>
       </c>
       <c r="M6" t="n">
-        <v>199920</v>
+        <v>148680</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1275</v>
       </c>
       <c r="O6" t="n">
-        <v>7650</v>
+        <v>6375</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>767722.05</v>
+        <v>87008499</v>
       </c>
     </row>
     <row r="7">
@@ -4595,7 +4595,7 @@
         <v>130977</v>
       </c>
       <c r="H7" t="n">
-        <v>14729940</v>
+        <v>17476200</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -4607,22 +4607,22 @@
         <v>123914.91</v>
       </c>
       <c r="L7" t="n">
-        <v>5368680</v>
+        <v>5563080</v>
       </c>
       <c r="M7" t="n">
-        <v>474075</v>
+        <v>448350</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1785</v>
+        <v>7140</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>908133.12</v>
+        <v>102921753.6</v>
       </c>
     </row>
     <row r="8">
@@ -4648,7 +4648,7 @@
         <v>1015092</v>
       </c>
       <c r="H8" t="n">
-        <v>26453700</v>
+        <v>22965300</v>
       </c>
       <c r="I8" t="n">
         <v>285897.73</v>
@@ -4660,22 +4660,22 @@
         <v>107211.65</v>
       </c>
       <c r="L8" t="n">
-        <v>9443142</v>
+        <v>9236106</v>
       </c>
       <c r="M8" t="n">
-        <v>358050</v>
+        <v>877800</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>13770</v>
+        <v>9180</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1042056.9</v>
+        <v>118099782</v>
       </c>
     </row>
     <row r="9">
@@ -4701,7 +4701,7 @@
         <v>1589058</v>
       </c>
       <c r="H9" t="n">
-        <v>18126000</v>
+        <v>22743000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -4713,22 +4713,22 @@
         <v>311923.74</v>
       </c>
       <c r="L9" t="n">
-        <v>13646880</v>
+        <v>14399208</v>
       </c>
       <c r="M9" t="n">
-        <v>176400</v>
+        <v>948150</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>8415</v>
+        <v>16830</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1252908.65</v>
+        <v>141996313.44</v>
       </c>
     </row>
     <row r="10">
@@ -4754,7 +4754,7 @@
         <v>1315440</v>
       </c>
       <c r="H10" t="n">
-        <v>4959000</v>
+        <v>6156000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -4766,10 +4766,10 @@
         <v>84487.44</v>
       </c>
       <c r="L10" t="n">
-        <v>8059662</v>
+        <v>9621612</v>
       </c>
       <c r="M10" t="n">
-        <v>133875</v>
+        <v>1160250</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -4781,7 +4781,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>946776.6</v>
+        <v>107301348</v>
       </c>
     </row>
     <row r="11">
@@ -4807,7 +4807,7 @@
         <v>542700</v>
       </c>
       <c r="H11" t="n">
-        <v>4446000</v>
+        <v>5301000</v>
       </c>
       <c r="I11" t="n">
         <v>174510.26</v>
@@ -4819,10 +4819,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>4228200</v>
+        <v>5389200</v>
       </c>
       <c r="M11" t="n">
-        <v>122850</v>
+        <v>982800</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -4834,7 +4834,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>406717.2</v>
+        <v>46094616</v>
       </c>
     </row>
     <row r="12">
@@ -4860,7 +4860,7 @@
         <v>217080</v>
       </c>
       <c r="H12" t="n">
-        <v>855000</v>
+        <v>1026000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -4872,10 +4872,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1987200</v>
+        <v>2894400</v>
       </c>
       <c r="M12" t="n">
-        <v>99750</v>
+        <v>977550</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -4887,7 +4887,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>252622.8</v>
+        <v>28630584</v>
       </c>
     </row>
     <row r="13">
@@ -4913,7 +4913,7 @@
         <v>61560</v>
       </c>
       <c r="H13" t="n">
-        <v>171000</v>
+        <v>684000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -4925,10 +4925,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>723600</v>
+        <v>1495800</v>
       </c>
       <c r="M13" t="n">
-        <v>252000</v>
+        <v>714000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>111018.6</v>
+        <v>12582108</v>
       </c>
     </row>
     <row r="14">
@@ -4966,7 +4966,7 @@
         <v>12960</v>
       </c>
       <c r="H14" t="n">
-        <v>684000</v>
+        <v>513000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -4978,10 +4978,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>259200</v>
+        <v>529200</v>
       </c>
       <c r="M14" t="n">
-        <v>115500</v>
+        <v>273000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>91076.39999999999</v>
+        <v>10321992</v>
       </c>
     </row>
     <row r="15">
@@ -5019,7 +5019,7 @@
         <v>3240</v>
       </c>
       <c r="H15" t="n">
-        <v>171000</v>
+        <v>1026000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -5031,10 +5031,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>599400</v>
+        <v>982800</v>
       </c>
       <c r="M15" t="n">
-        <v>819000</v>
+        <v>1207500</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -5046,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>32659.2</v>
+        <v>3701376</v>
       </c>
     </row>
     <row r="16">
@@ -5084,10 +5084,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>221400</v>
+        <v>415800</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>651000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>21983.4</v>
+        <v>2491452</v>
       </c>
     </row>
     <row r="17">
@@ -5125,7 +5125,7 @@
         <v>1620</v>
       </c>
       <c r="H17" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -5137,10 +5137,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>10800</v>
+        <v>167400</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>168000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -5152,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4179.6</v>
+        <v>473688</v>
       </c>
     </row>
     <row r="18">
@@ -5190,7 +5190,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>988.2</v>
+        <v>111996</v>
       </c>
     </row>
     <row r="19">
@@ -5258,7 +5258,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>48.6</v>
+        <v>5508</v>
       </c>
     </row>
     <row r="20">
@@ -5728,7 +5728,7 @@
         <v>30420</v>
       </c>
       <c r="H4" t="n">
-        <v>1710</v>
+        <v>3030</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -5740,22 +5740,22 @@
         <v>29</v>
       </c>
       <c r="L4" t="n">
-        <v>103020</v>
+        <v>119010</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3150</v>
+        <v>3690</v>
       </c>
       <c r="O4" t="n">
-        <v>18810</v>
+        <v>20760</v>
       </c>
       <c r="P4" t="n">
-        <v>10560</v>
+        <v>9240</v>
       </c>
       <c r="Q4" t="n">
-        <v>17842.96</v>
+        <v>93910.32000000001</v>
       </c>
     </row>
     <row r="5">
@@ -5781,7 +5781,7 @@
         <v>9840</v>
       </c>
       <c r="H5" t="n">
-        <v>480</v>
+        <v>810</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
         <v>7</v>
       </c>
       <c r="L5" t="n">
-        <v>35190</v>
+        <v>50040</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1350</v>
+        <v>1920</v>
       </c>
       <c r="O5" t="n">
-        <v>4410</v>
+        <v>8310</v>
       </c>
       <c r="P5" t="n">
-        <v>8340</v>
+        <v>12510</v>
       </c>
       <c r="Q5" t="n">
-        <v>6639.45</v>
+        <v>34944.48</v>
       </c>
     </row>
     <row r="6">
@@ -5834,7 +5834,7 @@
         <v>1620</v>
       </c>
       <c r="H6" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -5846,22 +5846,22 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
+        <v>11700</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>810</v>
+      </c>
+      <c r="P6" t="n">
         <v>8190</v>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>180</v>
-      </c>
-      <c r="P6" t="n">
-        <v>5970</v>
-      </c>
       <c r="Q6" t="n">
-        <v>403.22</v>
+        <v>2122.2</v>
       </c>
     </row>
     <row r="7">
@@ -5887,7 +5887,7 @@
         <v>240</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -5899,7 +5899,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1560</v>
+        <v>3240</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -5911,10 +5911,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>5760</v>
+        <v>8880</v>
       </c>
       <c r="Q7" t="n">
-        <v>74.28</v>
+        <v>390.96</v>
       </c>
     </row>
     <row r="8">
@@ -5952,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>360</v>
+        <v>1620</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -5964,10 +5964,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4890</v>
+        <v>9960</v>
       </c>
       <c r="Q8" t="n">
-        <v>40.01</v>
+        <v>210.6</v>
       </c>
     </row>
     <row r="9">
@@ -6005,7 +6005,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>150</v>
+        <v>780</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4320</v>
+        <v>11730</v>
       </c>
       <c r="Q9" t="n">
-        <v>25.44</v>
+        <v>133.92</v>
       </c>
     </row>
     <row r="10">
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -6070,10 +6070,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>510</v>
+        <v>1440</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.82</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="11">
@@ -7073,7 +7073,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>172.8</v>
+        <v>291.6</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -7085,22 +7085,22 @@
         <v>2.32</v>
       </c>
       <c r="L5" t="n">
-        <v>7389.9</v>
+        <v>10508.4</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>13.5</v>
+        <v>19.2</v>
       </c>
       <c r="O5" t="n">
-        <v>220.5</v>
+        <v>415.5</v>
       </c>
       <c r="P5" t="n">
-        <v>166.8</v>
+        <v>250.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>331.97</v>
+        <v>1747.22</v>
       </c>
     </row>
     <row r="6">
@@ -7126,7 +7126,7 @@
         <v>81</v>
       </c>
       <c r="H6" t="n">
-        <v>85.5</v>
+        <v>171</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -7138,7 +7138,7 @@
         <v>0.51</v>
       </c>
       <c r="L6" t="n">
-        <v>3030.3</v>
+        <v>4329</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -7147,13 +7147,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>45</v>
+        <v>202.5</v>
       </c>
       <c r="P6" t="n">
-        <v>895.5</v>
+        <v>1228.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>302.41</v>
+        <v>1591.65</v>
       </c>
     </row>
     <row r="7">
@@ -7179,7 +7179,7 @@
         <v>36</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>43.8</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -7191,7 +7191,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>936</v>
+        <v>1944</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -7203,10 +7203,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1440</v>
+        <v>2220</v>
       </c>
       <c r="Q7" t="n">
-        <v>59.43</v>
+        <v>312.77</v>
       </c>
     </row>
     <row r="8">
@@ -7244,7 +7244,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>255.6</v>
+        <v>1150.2</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -7256,10 +7256,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1858.2</v>
+        <v>3784.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>38.01</v>
+        <v>200.07</v>
       </c>
     </row>
     <row r="9">
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>121.5</v>
+        <v>631.8</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -7309,10 +7309,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2160</v>
+        <v>5865</v>
       </c>
       <c r="Q9" t="n">
-        <v>24.68</v>
+        <v>129.9</v>
       </c>
     </row>
     <row r="10">
@@ -7350,7 +7350,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -7362,10 +7362,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>433.5</v>
+        <v>1224</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.82</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="11">
@@ -8365,7 +8365,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>984960</v>
+        <v>1662120</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -8377,22 +8377,22 @@
         <v>112504.25</v>
       </c>
       <c r="L5" t="n">
-        <v>1330182</v>
+        <v>1891512</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2295</v>
+        <v>3264</v>
       </c>
       <c r="O5" t="n">
-        <v>37485</v>
+        <v>70635</v>
       </c>
       <c r="P5" t="n">
-        <v>10842</v>
+        <v>16263</v>
       </c>
       <c r="Q5" t="n">
-        <v>199183.54</v>
+        <v>1048334.4</v>
       </c>
     </row>
     <row r="6">
@@ -8418,7 +8418,7 @@
         <v>4374</v>
       </c>
       <c r="H6" t="n">
-        <v>487350</v>
+        <v>974700</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -8430,7 +8430,7 @@
         <v>24617.89</v>
       </c>
       <c r="L6" t="n">
-        <v>545454</v>
+        <v>779220</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -8439,13 +8439,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>7650</v>
+        <v>34425</v>
       </c>
       <c r="P6" t="n">
-        <v>58207.5</v>
+        <v>79852.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>181448.1</v>
+        <v>954990</v>
       </c>
     </row>
     <row r="7">
@@ -8471,7 +8471,7 @@
         <v>1944</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>249660</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -8483,7 +8483,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>168480</v>
+        <v>349920</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -8495,10 +8495,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>93600</v>
+        <v>144300</v>
       </c>
       <c r="Q7" t="n">
-        <v>35655.55</v>
+        <v>187660.8</v>
       </c>
     </row>
     <row r="8">
@@ -8536,7 +8536,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>46008</v>
+        <v>207036</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -8548,10 +8548,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>120783</v>
+        <v>246012</v>
       </c>
       <c r="Q8" t="n">
-        <v>22807.98</v>
+        <v>120042</v>
       </c>
     </row>
     <row r="9">
@@ -8589,7 +8589,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>21870</v>
+        <v>113724</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -8601,10 +8601,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>140400</v>
+        <v>381225</v>
       </c>
       <c r="Q9" t="n">
-        <v>14808.87</v>
+        <v>77941.44</v>
       </c>
     </row>
     <row r="10">
@@ -8642,7 +8642,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>4806</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -8654,10 +8654,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>28177.5</v>
+        <v>79560</v>
       </c>
       <c r="Q10" t="n">
-        <v>492.48</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="11">
@@ -9604,7 +9604,7 @@
         <v>42630</v>
       </c>
       <c r="H4" t="n">
-        <v>3390</v>
+        <v>3360</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -9616,22 +9616,22 @@
         <v>8</v>
       </c>
       <c r="L4" t="n">
-        <v>53280</v>
+        <v>69390</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>17430</v>
+        <v>21420</v>
       </c>
       <c r="O4" t="n">
-        <v>26730</v>
+        <v>28140</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>18282.73</v>
+        <v>99208.62</v>
       </c>
     </row>
     <row r="5">
@@ -9657,7 +9657,7 @@
         <v>10020</v>
       </c>
       <c r="H5" t="n">
-        <v>2550</v>
+        <v>3030</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -9669,22 +9669,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>13650</v>
+        <v>16770</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6300</v>
+        <v>6870</v>
       </c>
       <c r="O5" t="n">
-        <v>27450</v>
+        <v>26100</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2950.91</v>
+        <v>16012.71</v>
       </c>
     </row>
     <row r="6">
@@ -9710,7 +9710,7 @@
         <v>2820</v>
       </c>
       <c r="H6" t="n">
-        <v>390</v>
+        <v>660</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9722,22 +9722,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2640</v>
+        <v>5880</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2460</v>
+        <v>3870</v>
       </c>
       <c r="O6" t="n">
-        <v>20130</v>
+        <v>23760</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>463.36</v>
+        <v>2514.33</v>
       </c>
     </row>
     <row r="7">
@@ -9763,7 +9763,7 @@
         <v>750</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -9775,22 +9775,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>510</v>
+        <v>1170</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>150</v>
+        <v>1230</v>
       </c>
       <c r="O7" t="n">
-        <v>6000</v>
+        <v>8040</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>90.67</v>
+        <v>492.03</v>
       </c>
     </row>
     <row r="8">
@@ -9837,13 +9837,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>990</v>
+        <v>2040</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>15.21</v>
+        <v>82.53</v>
       </c>
     </row>
     <row r="9">
@@ -9890,13 +9890,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>240</v>
+        <v>540</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.74</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -10949,7 +10949,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>918</v>
+        <v>1090.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -10961,22 +10961,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2866.5</v>
+        <v>3521.7</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>63</v>
+        <v>68.7</v>
       </c>
       <c r="O5" t="n">
-        <v>1372.5</v>
+        <v>1305</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>147.55</v>
+        <v>800.64</v>
       </c>
     </row>
     <row r="6">
@@ -11002,7 +11002,7 @@
         <v>141</v>
       </c>
       <c r="H6" t="n">
-        <v>222.3</v>
+        <v>376.2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -11014,22 +11014,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>976.8</v>
+        <v>2175.6</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>123</v>
+        <v>193.5</v>
       </c>
       <c r="O6" t="n">
-        <v>5032.5</v>
+        <v>5940</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>347.52</v>
+        <v>1885.75</v>
       </c>
     </row>
     <row r="7">
@@ -11055,7 +11055,7 @@
         <v>112.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>240.9</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -11067,22 +11067,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>306</v>
+        <v>702</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>10.5</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>2100</v>
+        <v>2814</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>72.54000000000001</v>
+        <v>393.62</v>
       </c>
     </row>
     <row r="8">
@@ -11129,13 +11129,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>445.5</v>
+        <v>918</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>14.45</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -11182,13 +11182,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>132</v>
+        <v>297</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.69</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="10">
@@ -12241,7 +12241,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5232600</v>
+        <v>6217560</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -12253,22 +12253,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>515970</v>
+        <v>633906</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>10710</v>
+        <v>11679</v>
       </c>
       <c r="O5" t="n">
-        <v>233325</v>
+        <v>221850</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>88527.41</v>
+        <v>480381.3</v>
       </c>
     </row>
     <row r="6">
@@ -12294,7 +12294,7 @@
         <v>7614</v>
       </c>
       <c r="H6" t="n">
-        <v>1267110</v>
+        <v>2144340</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -12306,22 +12306,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>175824</v>
+        <v>391608</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>20910</v>
+        <v>32895</v>
       </c>
       <c r="O6" t="n">
-        <v>855525</v>
+        <v>1009800</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>208509.8</v>
+        <v>1131448.5</v>
       </c>
     </row>
     <row r="7">
@@ -12347,7 +12347,7 @@
         <v>6075</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1373130</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -12359,22 +12359,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>55080</v>
+        <v>126360</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1785</v>
+        <v>14637</v>
       </c>
       <c r="O7" t="n">
-        <v>357000</v>
+        <v>478380</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>43523.57</v>
+        <v>236174.4</v>
       </c>
     </row>
     <row r="8">
@@ -12421,13 +12421,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>75735</v>
+        <v>156060</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>8669.190000000001</v>
+        <v>47042.1</v>
       </c>
     </row>
     <row r="9">
@@ -12474,13 +12474,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>22440</v>
+        <v>50490</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1013.55</v>
+        <v>5499.9</v>
       </c>
     </row>
     <row r="10">
@@ -13480,7 +13480,7 @@
         <v>96660</v>
       </c>
       <c r="H4" t="n">
-        <v>10020</v>
+        <v>11580</v>
       </c>
       <c r="I4" t="n">
         <v>6</v>
@@ -13492,19 +13492,19 @@
         <v>124</v>
       </c>
       <c r="L4" t="n">
-        <v>221820</v>
+        <v>215040</v>
       </c>
       <c r="M4" t="n">
-        <v>18720</v>
+        <v>1500</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>38070</v>
+        <v>41520</v>
       </c>
       <c r="P4" t="n">
-        <v>33420</v>
+        <v>6990</v>
       </c>
       <c r="Q4" t="n">
         <v>41845.54</v>
@@ -13533,7 +13533,7 @@
         <v>102990</v>
       </c>
       <c r="H5" t="n">
-        <v>12990</v>
+        <v>13410</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -13545,19 +13545,19 @@
         <v>98</v>
       </c>
       <c r="L5" t="n">
-        <v>261180</v>
+        <v>249690</v>
       </c>
       <c r="M5" t="n">
-        <v>14160</v>
+        <v>5850</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>39570</v>
+        <v>45540</v>
       </c>
       <c r="P5" t="n">
-        <v>41970</v>
+        <v>24060</v>
       </c>
       <c r="Q5" t="n">
         <v>51647.59</v>
@@ -13586,7 +13586,7 @@
         <v>62550</v>
       </c>
       <c r="H6" t="n">
-        <v>5220</v>
+        <v>5850</v>
       </c>
       <c r="I6" t="n">
         <v>2</v>
@@ -13598,19 +13598,19 @@
         <v>34</v>
       </c>
       <c r="L6" t="n">
-        <v>135930</v>
+        <v>130650</v>
       </c>
       <c r="M6" t="n">
-        <v>6240</v>
+        <v>4530</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>29550</v>
+        <v>29190</v>
       </c>
       <c r="P6" t="n">
-        <v>36960</v>
+        <v>31830</v>
       </c>
       <c r="Q6" t="n">
         <v>37470.93</v>
@@ -13639,7 +13639,7 @@
         <v>39270</v>
       </c>
       <c r="H7" t="n">
-        <v>780</v>
+        <v>660</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -13651,19 +13651,19 @@
         <v>29</v>
       </c>
       <c r="L7" t="n">
-        <v>68460</v>
+        <v>72000</v>
       </c>
       <c r="M7" t="n">
-        <v>3570</v>
+        <v>9630</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>25110</v>
+        <v>27840</v>
       </c>
       <c r="P7" t="n">
-        <v>33240</v>
+        <v>30000</v>
       </c>
       <c r="Q7" t="n">
         <v>26610.8</v>
@@ -13692,7 +13692,7 @@
         <v>11220</v>
       </c>
       <c r="H8" t="n">
-        <v>60</v>
+        <v>420</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -13704,19 +13704,19 @@
         <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>34170</v>
+        <v>42900</v>
       </c>
       <c r="M8" t="n">
-        <v>2160</v>
+        <v>12060</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>9000</v>
+        <v>12960</v>
       </c>
       <c r="P8" t="n">
-        <v>39090</v>
+        <v>42840</v>
       </c>
       <c r="Q8" t="n">
         <v>10648.65</v>
@@ -13757,19 +13757,19 @@
         <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>8940</v>
+        <v>21210</v>
       </c>
       <c r="M9" t="n">
-        <v>1020</v>
+        <v>12960</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>450</v>
+        <v>1530</v>
       </c>
       <c r="P9" t="n">
-        <v>37680</v>
+        <v>41790</v>
       </c>
       <c r="Q9" t="n">
         <v>997.7</v>
@@ -13810,10 +13810,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3930</v>
+        <v>24420</v>
       </c>
       <c r="M10" t="n">
-        <v>180</v>
+        <v>9390</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -13822,7 +13822,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>34830</v>
+        <v>55590</v>
       </c>
       <c r="Q10" t="n">
         <v>280.34</v>
@@ -13863,19 +13863,19 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>3480</v>
+        <v>26190</v>
       </c>
       <c r="M11" t="n">
-        <v>270</v>
+        <v>12480</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>25350</v>
+        <v>49440</v>
       </c>
       <c r="Q11" t="n">
         <v>257.46</v>
@@ -13904,7 +13904,7 @@
         <v>360</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -13916,10 +13916,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2010</v>
+        <v>15690</v>
       </c>
       <c r="M12" t="n">
-        <v>480</v>
+        <v>2490</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -13928,7 +13928,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>15090</v>
+        <v>25620</v>
       </c>
       <c r="Q12" t="n">
         <v>53.34</v>
@@ -13969,10 +13969,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>870</v>
+        <v>6240</v>
       </c>
       <c r="M13" t="n">
-        <v>150</v>
+        <v>1080</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -13981,7 +13981,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>12420</v>
+        <v>13770</v>
       </c>
       <c r="Q13" t="n">
         <v>19.2</v>
@@ -14022,10 +14022,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>300</v>
+        <v>5430</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -14034,7 +14034,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>14670</v>
+        <v>28740</v>
       </c>
       <c r="Q14" t="n">
         <v>18.86</v>
@@ -14075,10 +14075,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>480</v>
+        <v>2460</v>
       </c>
       <c r="M15" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -14087,7 +14087,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>5550</v>
+        <v>15810</v>
       </c>
       <c r="Q15" t="n">
         <v>9.6</v>
@@ -14128,10 +14128,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>630</v>
+        <v>2850</v>
       </c>
       <c r="M16" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -14140,7 +14140,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3030</v>
+        <v>6450</v>
       </c>
       <c r="Q16" t="n">
         <v>5.13</v>
@@ -14181,7 +14181,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>570</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -14193,7 +14193,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>450</v>
+        <v>750</v>
       </c>
       <c r="Q17" t="n">
         <v>0.67</v>
@@ -14825,7 +14825,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>24040.8</v>
+        <v>26038.8</v>
       </c>
       <c r="I5" t="n">
         <v>0.66</v>
@@ -14837,22 +14837,22 @@
         <v>78.45</v>
       </c>
       <c r="L5" t="n">
-        <v>193195.8</v>
+        <v>200844</v>
       </c>
       <c r="M5" t="n">
-        <v>859.8</v>
+        <v>816</v>
       </c>
       <c r="N5" t="n">
-        <v>208.5</v>
+        <v>304.2</v>
       </c>
       <c r="O5" t="n">
-        <v>8674.5</v>
+        <v>9805.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1428</v>
+        <v>982.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>7124.04</v>
+        <v>73825.7</v>
       </c>
     </row>
     <row r="6">
@@ -14878,7 +14878,7 @@
         <v>12037.5</v>
       </c>
       <c r="H6" t="n">
-        <v>11046.6</v>
+        <v>12551.4</v>
       </c>
       <c r="I6" t="n">
         <v>1.52</v>
@@ -14890,22 +14890,22 @@
         <v>55.77</v>
       </c>
       <c r="L6" t="n">
-        <v>213852.6</v>
+        <v>225163.5</v>
       </c>
       <c r="M6" t="n">
-        <v>1660.8</v>
+        <v>2320.8</v>
       </c>
       <c r="N6" t="n">
-        <v>247.5</v>
+        <v>462</v>
       </c>
       <c r="O6" t="n">
-        <v>25575</v>
+        <v>29452.5</v>
       </c>
       <c r="P6" t="n">
-        <v>10395</v>
+        <v>8118</v>
       </c>
       <c r="Q6" t="n">
-        <v>78253.06</v>
+        <v>810928.84</v>
       </c>
     </row>
     <row r="7">
@@ -14931,7 +14931,7 @@
         <v>22248</v>
       </c>
       <c r="H7" t="n">
-        <v>4117.2</v>
+        <v>5168.4</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -14943,22 +14943,22 @@
         <v>56.14</v>
       </c>
       <c r="L7" t="n">
-        <v>207828</v>
+        <v>229320</v>
       </c>
       <c r="M7" t="n">
-        <v>4672.5</v>
+        <v>10804.5</v>
       </c>
       <c r="N7" t="n">
-        <v>48.3</v>
+        <v>199.5</v>
       </c>
       <c r="O7" t="n">
-        <v>24738</v>
+        <v>27846</v>
       </c>
       <c r="P7" t="n">
-        <v>18532.5</v>
+        <v>15172.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>65605.09</v>
+        <v>679859.16</v>
       </c>
     </row>
     <row r="8">
@@ -14984,7 +14984,7 @@
         <v>74860.5</v>
       </c>
       <c r="H8" t="n">
-        <v>4921.5</v>
+        <v>4743</v>
       </c>
       <c r="I8" t="n">
         <v>2.21</v>
@@ -14996,22 +14996,22 @@
         <v>29.44</v>
       </c>
       <c r="L8" t="n">
-        <v>173232.9</v>
+        <v>193872.6</v>
       </c>
       <c r="M8" t="n">
-        <v>4834.5</v>
+        <v>18562.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O8" t="n">
-        <v>13365</v>
+        <v>22288.5</v>
       </c>
       <c r="P8" t="n">
-        <v>31065</v>
+        <v>30369.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>51726.52</v>
+        <v>536036.9399999999</v>
       </c>
     </row>
     <row r="9">
@@ -15037,7 +15037,7 @@
         <v>61276.5</v>
       </c>
       <c r="H9" t="n">
-        <v>3270</v>
+        <v>4230</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -15049,22 +15049,22 @@
         <v>28.1</v>
       </c>
       <c r="L9" t="n">
-        <v>153551.7</v>
+        <v>183124.8</v>
       </c>
       <c r="M9" t="n">
-        <v>3444</v>
+        <v>19026</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4818</v>
+        <v>11401.5</v>
       </c>
       <c r="P9" t="n">
-        <v>40485</v>
+        <v>47760</v>
       </c>
       <c r="Q9" t="n">
-        <v>33258.15</v>
+        <v>344651.03</v>
       </c>
     </row>
     <row r="10">
@@ -15090,7 +15090,7 @@
         <v>41190</v>
       </c>
       <c r="H10" t="n">
-        <v>900</v>
+        <v>1410</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -15102,22 +15102,22 @@
         <v>5.22</v>
       </c>
       <c r="L10" t="n">
-        <v>86481.3</v>
+        <v>128427</v>
       </c>
       <c r="M10" t="n">
-        <v>2856</v>
+        <v>21726</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2394</v>
+        <v>7161</v>
       </c>
       <c r="P10" t="n">
-        <v>61480.5</v>
+        <v>96109.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>21143.62</v>
+        <v>219109.33</v>
       </c>
     </row>
     <row r="11">
@@ -15143,7 +15143,7 @@
         <v>26190</v>
       </c>
       <c r="H11" t="n">
-        <v>810</v>
+        <v>1080</v>
       </c>
       <c r="I11" t="n">
         <v>0.9</v>
@@ -15155,22 +15155,22 @@
         <v>0.9</v>
       </c>
       <c r="L11" t="n">
-        <v>44790</v>
+        <v>84720</v>
       </c>
       <c r="M11" t="n">
-        <v>2349</v>
+        <v>19494</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3009</v>
+        <v>3697.5</v>
       </c>
       <c r="P11" t="n">
-        <v>43227</v>
+        <v>73737</v>
       </c>
       <c r="Q11" t="n">
-        <v>12086.73</v>
+        <v>125253.58</v>
       </c>
     </row>
     <row r="12">
@@ -15196,7 +15196,7 @@
         <v>8400</v>
       </c>
       <c r="H12" t="n">
-        <v>150</v>
+        <v>270</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -15208,22 +15208,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>16860</v>
+        <v>42780</v>
       </c>
       <c r="M12" t="n">
-        <v>1510.5</v>
+        <v>10744.5</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>360</v>
+        <v>780</v>
       </c>
       <c r="P12" t="n">
-        <v>38970</v>
+        <v>62490</v>
       </c>
       <c r="Q12" t="n">
-        <v>5847.06</v>
+        <v>60592.5</v>
       </c>
     </row>
     <row r="13">
@@ -15249,7 +15249,7 @@
         <v>2280</v>
       </c>
       <c r="H13" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -15261,22 +15261,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>6480</v>
+        <v>19860</v>
       </c>
       <c r="M13" t="n">
-        <v>960</v>
+        <v>6000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="P13" t="n">
-        <v>27330</v>
+        <v>31350</v>
       </c>
       <c r="Q13" t="n">
-        <v>2382.33</v>
+        <v>24687.81</v>
       </c>
     </row>
     <row r="14">
@@ -15302,7 +15302,7 @@
         <v>1560</v>
       </c>
       <c r="H14" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -15314,10 +15314,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2790</v>
+        <v>12660</v>
       </c>
       <c r="M14" t="n">
-        <v>390</v>
+        <v>1560</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -15326,10 +15326,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>39930</v>
+        <v>57450</v>
       </c>
       <c r="Q14" t="n">
-        <v>1729.02</v>
+        <v>17917.65</v>
       </c>
     </row>
     <row r="15">
@@ -15355,7 +15355,7 @@
         <v>390</v>
       </c>
       <c r="H15" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -15367,22 +15367,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>4110</v>
+        <v>9480</v>
       </c>
       <c r="M15" t="n">
-        <v>2490</v>
+        <v>3660</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P15" t="n">
-        <v>20130</v>
+        <v>37050</v>
       </c>
       <c r="Q15" t="n">
-        <v>741.36</v>
+        <v>7682.63</v>
       </c>
     </row>
     <row r="16">
@@ -15420,10 +15420,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1920</v>
+        <v>6180</v>
       </c>
       <c r="M16" t="n">
-        <v>840</v>
+        <v>2820</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -15432,10 +15432,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>18240</v>
+        <v>22140</v>
       </c>
       <c r="Q16" t="n">
-        <v>369.95</v>
+        <v>3833.8</v>
       </c>
     </row>
     <row r="17">
@@ -15461,7 +15461,7 @@
         <v>3900</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -15473,22 +15473,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
+        <v>3210</v>
+      </c>
+      <c r="M17" t="n">
+        <v>510</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
         <v>150</v>
       </c>
-      <c r="M17" t="n">
-        <v>90</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>60</v>
-      </c>
       <c r="P17" t="n">
-        <v>18960</v>
+        <v>34560</v>
       </c>
       <c r="Q17" t="n">
-        <v>189.5</v>
+        <v>1963.74</v>
       </c>
     </row>
     <row r="18">
@@ -15526,10 +15526,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -15538,10 +15538,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>210</v>
+        <v>960</v>
       </c>
       <c r="Q18" t="n">
-        <v>23.99</v>
+        <v>248.65</v>
       </c>
     </row>
     <row r="19">
@@ -15582,7 +15582,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -15594,7 +15594,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.03</v>
+        <v>62.45</v>
       </c>
     </row>
     <row r="20">
@@ -15635,7 +15635,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -15647,7 +15647,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.23</v>
+        <v>12.72</v>
       </c>
     </row>
     <row r="21">
@@ -15688,7 +15688,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -15700,7 +15700,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.03</v>
+        <v>72.86</v>
       </c>
     </row>
     <row r="22">
@@ -16117,7 +16117,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4676.4</v>
+        <v>4827.6</v>
       </c>
       <c r="I5" t="n">
         <v>0.33</v>
@@ -16129,19 +16129,19 @@
         <v>32.44</v>
       </c>
       <c r="L5" t="n">
-        <v>54847.8</v>
+        <v>52434.9</v>
       </c>
       <c r="M5" t="n">
-        <v>283.2</v>
+        <v>117</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1978.5</v>
+        <v>2277</v>
       </c>
       <c r="P5" t="n">
-        <v>839.4</v>
+        <v>481.2</v>
       </c>
       <c r="Q5" t="n">
         <v>2582.38</v>
@@ -16170,7 +16170,7 @@
         <v>3127.5</v>
       </c>
       <c r="H6" t="n">
-        <v>2975.4</v>
+        <v>3334.5</v>
       </c>
       <c r="I6" t="n">
         <v>1.01</v>
@@ -16182,19 +16182,19 @@
         <v>17.24</v>
       </c>
       <c r="L6" t="n">
-        <v>50294.1</v>
+        <v>48340.5</v>
       </c>
       <c r="M6" t="n">
-        <v>499.2</v>
+        <v>362.4</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>7387.5</v>
+        <v>7297.5</v>
       </c>
       <c r="P6" t="n">
-        <v>5544</v>
+        <v>4774.5</v>
       </c>
       <c r="Q6" t="n">
         <v>28103.2</v>
@@ -16223,7 +16223,7 @@
         <v>5890.5</v>
       </c>
       <c r="H7" t="n">
-        <v>569.4</v>
+        <v>481.8</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -16235,19 +16235,19 @@
         <v>18.5</v>
       </c>
       <c r="L7" t="n">
-        <v>41076</v>
+        <v>43200</v>
       </c>
       <c r="M7" t="n">
-        <v>1249.5</v>
+        <v>3370.5</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>8788.5</v>
+        <v>9744</v>
       </c>
       <c r="P7" t="n">
-        <v>8310</v>
+        <v>7500</v>
       </c>
       <c r="Q7" t="n">
         <v>21288.64</v>
@@ -16276,7 +16276,7 @@
         <v>7293</v>
       </c>
       <c r="H8" t="n">
-        <v>51</v>
+        <v>357</v>
       </c>
       <c r="I8" t="n">
         <v>0.74</v>
@@ -16288,19 +16288,19 @@
         <v>3.68</v>
       </c>
       <c r="L8" t="n">
-        <v>24260.7</v>
+        <v>30459</v>
       </c>
       <c r="M8" t="n">
-        <v>1188</v>
+        <v>6633</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4050</v>
+        <v>5832</v>
       </c>
       <c r="P8" t="n">
-        <v>14854.2</v>
+        <v>16279.2</v>
       </c>
       <c r="Q8" t="n">
         <v>10116.22</v>
@@ -16341,19 +16341,19 @@
         <v>3.21</v>
       </c>
       <c r="L9" t="n">
-        <v>7241.4</v>
+        <v>17180.1</v>
       </c>
       <c r="M9" t="n">
-        <v>714</v>
+        <v>9072</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>247.5</v>
+        <v>841.5</v>
       </c>
       <c r="P9" t="n">
-        <v>18840</v>
+        <v>20895</v>
       </c>
       <c r="Q9" t="n">
         <v>967.77</v>
@@ -16394,10 +16394,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3497.7</v>
+        <v>21733.8</v>
       </c>
       <c r="M10" t="n">
-        <v>153</v>
+        <v>7981.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>29605.5</v>
+        <v>47251.5</v>
       </c>
       <c r="Q10" t="n">
         <v>280.34</v>
@@ -16447,19 +16447,19 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>3480</v>
+        <v>26190</v>
       </c>
       <c r="M11" t="n">
-        <v>243</v>
+        <v>11232</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>25.5</v>
       </c>
       <c r="P11" t="n">
-        <v>22815</v>
+        <v>44496</v>
       </c>
       <c r="Q11" t="n">
         <v>257.46</v>
@@ -16488,7 +16488,7 @@
         <v>360</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -16500,10 +16500,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2010</v>
+        <v>15690</v>
       </c>
       <c r="M12" t="n">
-        <v>456</v>
+        <v>2365.5</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -16512,7 +16512,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>15090</v>
+        <v>25620</v>
       </c>
       <c r="Q12" t="n">
         <v>53.34</v>
@@ -16553,10 +16553,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>870</v>
+        <v>6240</v>
       </c>
       <c r="M13" t="n">
-        <v>150</v>
+        <v>1080</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -16565,7 +16565,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>12420</v>
+        <v>13770</v>
       </c>
       <c r="Q13" t="n">
         <v>19.2</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>300</v>
+        <v>5430</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -16618,7 +16618,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>14670</v>
+        <v>28740</v>
       </c>
       <c r="Q14" t="n">
         <v>18.86</v>
@@ -16659,10 +16659,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>480</v>
+        <v>2460</v>
       </c>
       <c r="M15" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -16671,7 +16671,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>5550</v>
+        <v>15810</v>
       </c>
       <c r="Q15" t="n">
         <v>9.6</v>
@@ -16712,10 +16712,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>630</v>
+        <v>2850</v>
       </c>
       <c r="M16" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -16724,7 +16724,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3030</v>
+        <v>6450</v>
       </c>
       <c r="Q16" t="n">
         <v>5.13</v>
@@ -16765,7 +16765,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>570</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -16777,7 +16777,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>450</v>
+        <v>750</v>
       </c>
       <c r="Q17" t="n">
         <v>0.67</v>
@@ -17409,7 +17409,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>26655480</v>
+        <v>27517320</v>
       </c>
       <c r="I5" t="n">
         <v>64288.14</v>
@@ -17421,19 +17421,19 @@
         <v>1575059.53</v>
       </c>
       <c r="L5" t="n">
-        <v>9872604</v>
+        <v>9438282</v>
       </c>
       <c r="M5" t="n">
-        <v>99120</v>
+        <v>40950</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>336345</v>
+        <v>387090</v>
       </c>
       <c r="P5" t="n">
-        <v>54561</v>
+        <v>31278</v>
       </c>
       <c r="Q5" t="n">
         <v>1549427.62</v>
@@ -17462,7 +17462,7 @@
         <v>168885</v>
       </c>
       <c r="H6" t="n">
-        <v>16959780</v>
+        <v>19006650</v>
       </c>
       <c r="I6" t="n">
         <v>196943.14</v>
@@ -17474,19 +17474,19 @@
         <v>837008.33</v>
       </c>
       <c r="L6" t="n">
-        <v>9052938</v>
+        <v>8701290</v>
       </c>
       <c r="M6" t="n">
-        <v>174720</v>
+        <v>126840</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1255875</v>
+        <v>1240575</v>
       </c>
       <c r="P6" t="n">
-        <v>360360</v>
+        <v>310342.5</v>
       </c>
       <c r="Q6" t="n">
         <v>16861917.42</v>
@@ -17515,7 +17515,7 @@
         <v>318087</v>
       </c>
       <c r="H7" t="n">
-        <v>3245580</v>
+        <v>2746260</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -17527,19 +17527,19 @@
         <v>898383.11</v>
       </c>
       <c r="L7" t="n">
-        <v>7393680</v>
+        <v>7776000</v>
       </c>
       <c r="M7" t="n">
-        <v>437325</v>
+        <v>1179675</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1494045</v>
+        <v>1656480</v>
       </c>
       <c r="P7" t="n">
-        <v>540150</v>
+        <v>487500</v>
       </c>
       <c r="Q7" t="n">
         <v>12773182.46</v>
@@ -17568,7 +17568,7 @@
         <v>393822</v>
       </c>
       <c r="H8" t="n">
-        <v>290700</v>
+        <v>2034900</v>
       </c>
       <c r="I8" t="n">
         <v>142948.86</v>
@@ -17580,19 +17580,19 @@
         <v>178686.08</v>
       </c>
       <c r="L8" t="n">
-        <v>4366926</v>
+        <v>5482620</v>
       </c>
       <c r="M8" t="n">
-        <v>415800</v>
+        <v>2321550</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>688500</v>
+        <v>991440</v>
       </c>
       <c r="P8" t="n">
-        <v>965523</v>
+        <v>1058148</v>
       </c>
       <c r="Q8" t="n">
         <v>6069729.82</v>
@@ -17633,19 +17633,19 @@
         <v>155961.87</v>
       </c>
       <c r="L9" t="n">
-        <v>1303452</v>
+        <v>3092418</v>
       </c>
       <c r="M9" t="n">
-        <v>249900</v>
+        <v>3175200</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>42075</v>
+        <v>143055</v>
       </c>
       <c r="P9" t="n">
-        <v>1224600</v>
+        <v>1358175</v>
       </c>
       <c r="Q9" t="n">
         <v>580663.73</v>
@@ -17686,10 +17686,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>629586</v>
+        <v>3912084</v>
       </c>
       <c r="M10" t="n">
-        <v>53550</v>
+        <v>2793525</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -17698,7 +17698,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1924357.5</v>
+        <v>3071347.5</v>
       </c>
       <c r="Q10" t="n">
         <v>168203.52</v>
@@ -17739,19 +17739,19 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>626400</v>
+        <v>4714200</v>
       </c>
       <c r="M11" t="n">
-        <v>85050</v>
+        <v>3931200</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4335</v>
       </c>
       <c r="P11" t="n">
-        <v>1482975</v>
+        <v>2892240</v>
       </c>
       <c r="Q11" t="n">
         <v>154476.72</v>
@@ -17780,7 +17780,7 @@
         <v>19440</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>513000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -17792,10 +17792,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>361800</v>
+        <v>2824200</v>
       </c>
       <c r="M12" t="n">
-        <v>159600</v>
+        <v>827925</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -17804,7 +17804,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>980850</v>
+        <v>1665300</v>
       </c>
       <c r="Q12" t="n">
         <v>32006.88</v>
@@ -17845,10 +17845,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>156600</v>
+        <v>1123200</v>
       </c>
       <c r="M13" t="n">
-        <v>52500</v>
+        <v>378000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -17857,7 +17857,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>807300</v>
+        <v>895050</v>
       </c>
       <c r="Q13" t="n">
         <v>11517.12</v>
@@ -17898,10 +17898,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>54000</v>
+        <v>977400</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>84000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -17910,7 +17910,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>953550</v>
+        <v>1868100</v>
       </c>
       <c r="Q14" t="n">
         <v>11316.24</v>
@@ -17951,10 +17951,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>86400</v>
+        <v>442800</v>
       </c>
       <c r="M15" t="n">
-        <v>31500</v>
+        <v>52500</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -17963,7 +17963,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>360750</v>
+        <v>1027650</v>
       </c>
       <c r="Q15" t="n">
         <v>5758.56</v>
@@ -18004,10 +18004,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>113400</v>
+        <v>513000</v>
       </c>
       <c r="M16" t="n">
-        <v>84000</v>
+        <v>105000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -18016,7 +18016,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>196950</v>
+        <v>419250</v>
       </c>
       <c r="Q16" t="n">
         <v>3080.16</v>
@@ -18057,7 +18057,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>102600</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -18069,7 +18069,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>29250</v>
+        <v>48750</v>
       </c>
       <c r="Q17" t="n">
         <v>401.76</v>
@@ -18648,7 +18648,7 @@
         <v>61800</v>
       </c>
       <c r="H4" t="n">
-        <v>4470</v>
+        <v>5430</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -18660,22 +18660,22 @@
         <v>33</v>
       </c>
       <c r="L4" t="n">
-        <v>224280</v>
+        <v>267060</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2370</v>
+        <v>2610</v>
       </c>
       <c r="O4" t="n">
-        <v>48330</v>
+        <v>53370</v>
       </c>
       <c r="P4" t="n">
-        <v>5550</v>
+        <v>2130</v>
       </c>
       <c r="Q4" t="n">
-        <v>21136.38</v>
+        <v>242187.66</v>
       </c>
     </row>
     <row r="5">
@@ -18701,7 +18701,7 @@
         <v>13020</v>
       </c>
       <c r="H5" t="n">
-        <v>1140</v>
+        <v>1530</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -18713,22 +18713,22 @@
         <v>11</v>
       </c>
       <c r="L5" t="n">
-        <v>62580</v>
+        <v>81690</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1020</v>
+        <v>1830</v>
       </c>
       <c r="O5" t="n">
-        <v>21780</v>
+        <v>31050</v>
       </c>
       <c r="P5" t="n">
-        <v>4140</v>
+        <v>6600</v>
       </c>
       <c r="Q5" t="n">
-        <v>5321.38</v>
+        <v>60974.1</v>
       </c>
     </row>
     <row r="6">
@@ -18754,7 +18754,7 @@
         <v>1470</v>
       </c>
       <c r="H6" t="n">
-        <v>210</v>
+        <v>270</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -18766,22 +18766,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>10260</v>
+        <v>17760</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>30</v>
+        <v>420</v>
       </c>
       <c r="O6" t="n">
-        <v>3360</v>
+        <v>5460</v>
       </c>
       <c r="P6" t="n">
-        <v>2730</v>
+        <v>5610</v>
       </c>
       <c r="Q6" t="n">
-        <v>503.97</v>
+        <v>5774.67</v>
       </c>
     </row>
     <row r="7">
@@ -18819,7 +18819,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>630</v>
+        <v>2610</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -18828,13 +18828,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>60</v>
+        <v>330</v>
       </c>
       <c r="P7" t="n">
-        <v>3060</v>
+        <v>7530</v>
       </c>
       <c r="Q7" t="n">
-        <v>86.48999999999999</v>
+        <v>990.99</v>
       </c>
     </row>
     <row r="8">
@@ -18872,7 +18872,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -18884,10 +18884,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>960</v>
+        <v>3600</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.05</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="9">
@@ -18925,22 +18925,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
+        <v>210</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
         <v>90</v>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>30</v>
-      </c>
       <c r="Q9" t="n">
-        <v>0.09</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="10">
@@ -19031,7 +19031,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -19993,7 +19993,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>410.4</v>
+        <v>550.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -20005,22 +20005,22 @@
         <v>3.64</v>
       </c>
       <c r="L5" t="n">
-        <v>13141.8</v>
+        <v>17154.9</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>10.2</v>
+        <v>18.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1089</v>
+        <v>1552.5</v>
       </c>
       <c r="P5" t="n">
-        <v>82.8</v>
+        <v>132</v>
       </c>
       <c r="Q5" t="n">
-        <v>266.07</v>
+        <v>3048.71</v>
       </c>
     </row>
     <row r="6">
@@ -20046,7 +20046,7 @@
         <v>73.5</v>
       </c>
       <c r="H6" t="n">
-        <v>119.7</v>
+        <v>153.9</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -20058,22 +20058,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>3796.2</v>
+        <v>6571.2</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.5</v>
+        <v>21</v>
       </c>
       <c r="O6" t="n">
-        <v>840</v>
+        <v>1365</v>
       </c>
       <c r="P6" t="n">
-        <v>409.5</v>
+        <v>841.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>377.98</v>
+        <v>4331</v>
       </c>
     </row>
     <row r="7">
@@ -20111,7 +20111,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>378</v>
+        <v>1566</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -20120,13 +20120,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>21</v>
+        <v>115.5</v>
       </c>
       <c r="P7" t="n">
-        <v>765</v>
+        <v>1882.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>69.19</v>
+        <v>792.79</v>
       </c>
     </row>
     <row r="8">
@@ -20164,7 +20164,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>127.8</v>
+        <v>340.8</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -20176,10 +20176,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>364.8</v>
+        <v>1368</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.75</v>
+        <v>65.83</v>
       </c>
     </row>
     <row r="9">
@@ -20217,7 +20217,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>72.90000000000001</v>
+        <v>170.1</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -20229,10 +20229,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.08</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="10">
@@ -20323,7 +20323,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -21285,7 +21285,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2339280</v>
+        <v>3139560</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -21297,22 +21297,22 @@
         <v>176792.4</v>
       </c>
       <c r="L5" t="n">
-        <v>2365524</v>
+        <v>3087882</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1734</v>
+        <v>3111</v>
       </c>
       <c r="O5" t="n">
-        <v>185130</v>
+        <v>263925</v>
       </c>
       <c r="P5" t="n">
-        <v>5382</v>
+        <v>8580</v>
       </c>
       <c r="Q5" t="n">
-        <v>159641.28</v>
+        <v>1829223</v>
       </c>
     </row>
     <row r="6">
@@ -21338,7 +21338,7 @@
         <v>3969</v>
       </c>
       <c r="H6" t="n">
-        <v>682290</v>
+        <v>877230</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -21350,22 +21350,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>683316</v>
+        <v>1182816</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>255</v>
+        <v>3570</v>
       </c>
       <c r="O6" t="n">
-        <v>142800</v>
+        <v>232050</v>
       </c>
       <c r="P6" t="n">
-        <v>26617.5</v>
+        <v>54697.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>226787.04</v>
+        <v>2598601.5</v>
       </c>
     </row>
     <row r="7">
@@ -21403,7 +21403,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>68040</v>
+        <v>281880</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -21412,13 +21412,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3570</v>
+        <v>19635</v>
       </c>
       <c r="P7" t="n">
-        <v>49725</v>
+        <v>122362.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>41513.47</v>
+        <v>475675.2</v>
       </c>
     </row>
     <row r="8">
@@ -21456,7 +21456,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>23004</v>
+        <v>61344</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -21468,10 +21468,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>23712</v>
+        <v>88920</v>
       </c>
       <c r="Q8" t="n">
-        <v>3447.36</v>
+        <v>39501</v>
       </c>
     </row>
     <row r="9">
@@ -21509,7 +21509,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>13122</v>
+        <v>30618</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -21521,10 +21521,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>975</v>
+        <v>2925</v>
       </c>
       <c r="Q9" t="n">
-        <v>50.28</v>
+        <v>576.1799999999999</v>
       </c>
     </row>
     <row r="10">
@@ -21615,7 +21615,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>5400</v>
+        <v>16200</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -22577,7 +22577,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>137032560</v>
+        <v>148421160</v>
       </c>
       <c r="I5" t="n">
         <v>128576.29</v>
@@ -22589,22 +22589,22 @@
         <v>3809072.53</v>
       </c>
       <c r="L5" t="n">
-        <v>34775244</v>
+        <v>36151920</v>
       </c>
       <c r="M5" t="n">
-        <v>300930</v>
+        <v>285600</v>
       </c>
       <c r="N5" t="n">
-        <v>35445</v>
+        <v>51714</v>
       </c>
       <c r="O5" t="n">
-        <v>1474665</v>
+        <v>1666935</v>
       </c>
       <c r="P5" t="n">
-        <v>92820</v>
+        <v>63882</v>
       </c>
       <c r="Q5" t="n">
-        <v>4274421.73</v>
+        <v>44295418.76</v>
       </c>
     </row>
     <row r="6">
@@ -22630,7 +22630,7 @@
         <v>650025</v>
       </c>
       <c r="H6" t="n">
-        <v>62965620</v>
+        <v>71542980</v>
       </c>
       <c r="I6" t="n">
         <v>295414.7</v>
@@ -22642,22 +22642,22 @@
         <v>2707968.12</v>
       </c>
       <c r="L6" t="n">
-        <v>38493468</v>
+        <v>40529430</v>
       </c>
       <c r="M6" t="n">
-        <v>581280</v>
+        <v>812280</v>
       </c>
       <c r="N6" t="n">
-        <v>42075</v>
+        <v>78540</v>
       </c>
       <c r="O6" t="n">
-        <v>4347750</v>
+        <v>5006925</v>
       </c>
       <c r="P6" t="n">
-        <v>675675</v>
+        <v>527670</v>
       </c>
       <c r="Q6" t="n">
-        <v>46951833.06</v>
+        <v>486557302.28</v>
       </c>
     </row>
     <row r="7">
@@ -22683,7 +22683,7 @@
         <v>1201392</v>
       </c>
       <c r="H7" t="n">
-        <v>23468040</v>
+        <v>29459880</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -22695,22 +22695,22 @@
         <v>2726128.06</v>
       </c>
       <c r="L7" t="n">
-        <v>37409040</v>
+        <v>41277600</v>
       </c>
       <c r="M7" t="n">
-        <v>1635375</v>
+        <v>3781575</v>
       </c>
       <c r="N7" t="n">
-        <v>8211</v>
+        <v>33915</v>
       </c>
       <c r="O7" t="n">
-        <v>4205460</v>
+        <v>4733820</v>
       </c>
       <c r="P7" t="n">
-        <v>1204612.5</v>
+        <v>986212.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>39363052.03</v>
+        <v>407915498.88</v>
       </c>
     </row>
     <row r="8">
@@ -22736,7 +22736,7 @@
         <v>4042467</v>
       </c>
       <c r="H8" t="n">
-        <v>28052550</v>
+        <v>27035100</v>
       </c>
       <c r="I8" t="n">
         <v>428846.59</v>
@@ -22748,22 +22748,22 @@
         <v>1429488.64</v>
       </c>
       <c r="L8" t="n">
-        <v>31181922</v>
+        <v>34897068</v>
       </c>
       <c r="M8" t="n">
-        <v>1692075</v>
+        <v>6496875</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3060</v>
       </c>
       <c r="O8" t="n">
-        <v>2272050</v>
+        <v>3789045</v>
       </c>
       <c r="P8" t="n">
-        <v>2019225</v>
+        <v>1974024</v>
       </c>
       <c r="Q8" t="n">
-        <v>31035913.13</v>
+        <v>321622164.27</v>
       </c>
     </row>
     <row r="9">
@@ -22789,7 +22789,7 @@
         <v>3308931</v>
       </c>
       <c r="H9" t="n">
-        <v>18639000</v>
+        <v>24111000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -22801,22 +22801,22 @@
         <v>1364666.38</v>
       </c>
       <c r="L9" t="n">
-        <v>27639306</v>
+        <v>32962464</v>
       </c>
       <c r="M9" t="n">
-        <v>1205400</v>
+        <v>6659100</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>819060</v>
+        <v>1938255</v>
       </c>
       <c r="P9" t="n">
-        <v>2631525</v>
+        <v>3104400</v>
       </c>
       <c r="Q9" t="n">
-        <v>19954892.22</v>
+        <v>206790617.01</v>
       </c>
     </row>
     <row r="10">
@@ -22842,7 +22842,7 @@
         <v>2224260</v>
       </c>
       <c r="H10" t="n">
-        <v>5130000</v>
+        <v>8037000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -22854,22 +22854,22 @@
         <v>253462.32</v>
       </c>
       <c r="L10" t="n">
-        <v>15566634</v>
+        <v>23116860</v>
       </c>
       <c r="M10" t="n">
-        <v>999600</v>
+        <v>7604100</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>406980</v>
+        <v>1217370</v>
       </c>
       <c r="P10" t="n">
-        <v>3996232.5</v>
+        <v>6247117.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>12686174.64</v>
+        <v>131465600.1</v>
       </c>
     </row>
     <row r="11">
@@ -22895,7 +22895,7 @@
         <v>1414260</v>
       </c>
       <c r="H11" t="n">
-        <v>4617000</v>
+        <v>6156000</v>
       </c>
       <c r="I11" t="n">
         <v>174510.26</v>
@@ -22907,22 +22907,22 @@
         <v>43627.57</v>
       </c>
       <c r="L11" t="n">
-        <v>8062200</v>
+        <v>15249600</v>
       </c>
       <c r="M11" t="n">
-        <v>822150</v>
+        <v>6822900</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>511530</v>
+        <v>628575</v>
       </c>
       <c r="P11" t="n">
-        <v>2809755</v>
+        <v>4792905</v>
       </c>
       <c r="Q11" t="n">
-        <v>7252035.84</v>
+        <v>75152145.59999999</v>
       </c>
     </row>
     <row r="12">
@@ -22948,7 +22948,7 @@
         <v>453600</v>
       </c>
       <c r="H12" t="n">
-        <v>855000</v>
+        <v>1539000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -22960,22 +22960,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3034800</v>
+        <v>7700400</v>
       </c>
       <c r="M12" t="n">
-        <v>528675</v>
+        <v>3760575</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>61200</v>
+        <v>132600</v>
       </c>
       <c r="P12" t="n">
-        <v>2533050</v>
+        <v>4061850</v>
       </c>
       <c r="Q12" t="n">
-        <v>3508235.28</v>
+        <v>36355502.7</v>
       </c>
     </row>
     <row r="13">
@@ -23001,7 +23001,7 @@
         <v>123120</v>
       </c>
       <c r="H13" t="n">
-        <v>171000</v>
+        <v>684000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -23013,22 +23013,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1166400</v>
+        <v>3574800</v>
       </c>
       <c r="M13" t="n">
-        <v>336000</v>
+        <v>2100000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>10200</v>
+        <v>40800</v>
       </c>
       <c r="P13" t="n">
-        <v>1776450</v>
+        <v>2037750</v>
       </c>
       <c r="Q13" t="n">
-        <v>1429395.12</v>
+        <v>14812683.3</v>
       </c>
     </row>
     <row r="14">
@@ -23054,7 +23054,7 @@
         <v>84240</v>
       </c>
       <c r="H14" t="n">
-        <v>684000</v>
+        <v>513000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23066,10 +23066,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>502200</v>
+        <v>2278800</v>
       </c>
       <c r="M14" t="n">
-        <v>136500</v>
+        <v>546000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -23078,10 +23078,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2595450</v>
+        <v>3734250</v>
       </c>
       <c r="Q14" t="n">
-        <v>1037411.28</v>
+        <v>10750592.7</v>
       </c>
     </row>
     <row r="15">
@@ -23107,7 +23107,7 @@
         <v>21060</v>
       </c>
       <c r="H15" t="n">
-        <v>171000</v>
+        <v>1026000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -23119,22 +23119,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>739800</v>
+        <v>1706400</v>
       </c>
       <c r="M15" t="n">
-        <v>871500</v>
+        <v>1281000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>10200</v>
+        <v>20400</v>
       </c>
       <c r="P15" t="n">
-        <v>1308450</v>
+        <v>2408250</v>
       </c>
       <c r="Q15" t="n">
-        <v>444815.28</v>
+        <v>4609577.7</v>
       </c>
     </row>
     <row r="16">
@@ -23172,10 +23172,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>345600</v>
+        <v>1112400</v>
       </c>
       <c r="M16" t="n">
-        <v>294000</v>
+        <v>987000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -23184,10 +23184,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1185600</v>
+        <v>1439100</v>
       </c>
       <c r="Q16" t="n">
-        <v>221972.4</v>
+        <v>2300278.5</v>
       </c>
     </row>
     <row r="17">
@@ -23213,7 +23213,7 @@
         <v>210600</v>
       </c>
       <c r="H17" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -23225,22 +23225,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>27000</v>
+        <v>577800</v>
       </c>
       <c r="M17" t="n">
-        <v>31500</v>
+        <v>178500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>10200</v>
+        <v>25500</v>
       </c>
       <c r="P17" t="n">
-        <v>1232400</v>
+        <v>2246400</v>
       </c>
       <c r="Q17" t="n">
-        <v>113698.08</v>
+        <v>1178242.2</v>
       </c>
     </row>
     <row r="18">
@@ -23278,10 +23278,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="M18" t="n">
-        <v>10500</v>
+        <v>42000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -23290,10 +23290,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>13650</v>
+        <v>62400</v>
       </c>
       <c r="Q18" t="n">
-        <v>14396.4</v>
+        <v>149188.5</v>
       </c>
     </row>
     <row r="19">
@@ -23334,7 +23334,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -23346,7 +23346,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3615.84</v>
+        <v>37470.6</v>
       </c>
     </row>
     <row r="20">
@@ -23387,7 +23387,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>21000</v>
+        <v>10500</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -23399,7 +23399,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>736.5599999999999</v>
+        <v>7632.9</v>
       </c>
     </row>
     <row r="21">
@@ -23440,7 +23440,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>52500</v>
+        <v>105000</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -23452,7 +23452,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4218.48</v>
+        <v>43715.7</v>
       </c>
     </row>
     <row r="22">
@@ -23816,7 +23816,7 @@
         <v>72270</v>
       </c>
       <c r="H4" t="n">
-        <v>20160</v>
+        <v>19230</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -23828,22 +23828,22 @@
         <v>75</v>
       </c>
       <c r="L4" t="n">
-        <v>208830</v>
+        <v>192570</v>
       </c>
       <c r="M4" t="n">
-        <v>30480</v>
+        <v>42150</v>
       </c>
       <c r="N4" t="n">
-        <v>19080</v>
+        <v>20520</v>
       </c>
       <c r="O4" t="n">
-        <v>15870</v>
+        <v>15300</v>
       </c>
       <c r="P4" t="n">
-        <v>3900</v>
+        <v>1290</v>
       </c>
       <c r="Q4" t="n">
-        <v>18845.16</v>
+        <v>184756.5</v>
       </c>
     </row>
     <row r="5">
@@ -23869,7 +23869,7 @@
         <v>93240</v>
       </c>
       <c r="H5" t="n">
-        <v>17790</v>
+        <v>21060</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -23881,22 +23881,22 @@
         <v>64</v>
       </c>
       <c r="L5" t="n">
-        <v>268770</v>
+        <v>274020</v>
       </c>
       <c r="M5" t="n">
-        <v>10080</v>
+        <v>24240</v>
       </c>
       <c r="N5" t="n">
-        <v>6360</v>
+        <v>10980</v>
       </c>
       <c r="O5" t="n">
-        <v>25110</v>
+        <v>26160</v>
       </c>
       <c r="P5" t="n">
-        <v>5280</v>
+        <v>3480</v>
       </c>
       <c r="Q5" t="n">
-        <v>30391.77</v>
+        <v>297958.5</v>
       </c>
     </row>
     <row r="6">
@@ -23922,7 +23922,7 @@
         <v>100620</v>
       </c>
       <c r="H6" t="n">
-        <v>2490</v>
+        <v>3000</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -23934,22 +23934,22 @@
         <v>59</v>
       </c>
       <c r="L6" t="n">
-        <v>260220</v>
+        <v>270810</v>
       </c>
       <c r="M6" t="n">
-        <v>4800</v>
+        <v>15360</v>
       </c>
       <c r="N6" t="n">
-        <v>990</v>
+        <v>2100</v>
       </c>
       <c r="O6" t="n">
-        <v>22230</v>
+        <v>25740</v>
       </c>
       <c r="P6" t="n">
-        <v>6900</v>
+        <v>5700</v>
       </c>
       <c r="Q6" t="n">
-        <v>31020.87</v>
+        <v>304126.2</v>
       </c>
     </row>
     <row r="7">
@@ -23975,7 +23975,7 @@
         <v>81630</v>
       </c>
       <c r="H7" t="n">
-        <v>720</v>
+        <v>930</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -23987,22 +23987,22 @@
         <v>55</v>
       </c>
       <c r="L7" t="n">
-        <v>191640</v>
+        <v>210840</v>
       </c>
       <c r="M7" t="n">
-        <v>4320</v>
+        <v>12390</v>
       </c>
       <c r="N7" t="n">
-        <v>180</v>
+        <v>390</v>
       </c>
       <c r="O7" t="n">
-        <v>22980</v>
+        <v>22080</v>
       </c>
       <c r="P7" t="n">
-        <v>9990</v>
+        <v>6210</v>
       </c>
       <c r="Q7" t="n">
-        <v>31787.22</v>
+        <v>311639.4</v>
       </c>
     </row>
     <row r="8">
@@ -24028,7 +24028,7 @@
         <v>70200</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -24040,22 +24040,22 @@
         <v>32</v>
       </c>
       <c r="L8" t="n">
-        <v>122730</v>
+        <v>138810</v>
       </c>
       <c r="M8" t="n">
-        <v>3540</v>
+        <v>9750</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>16170</v>
+        <v>24780</v>
       </c>
       <c r="P8" t="n">
-        <v>14700</v>
+        <v>7380</v>
       </c>
       <c r="Q8" t="n">
-        <v>25611.1</v>
+        <v>251089.2</v>
       </c>
     </row>
     <row r="9">
@@ -24081,7 +24081,7 @@
         <v>34170</v>
       </c>
       <c r="H9" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -24093,22 +24093,22 @@
         <v>22</v>
       </c>
       <c r="L9" t="n">
-        <v>83580</v>
+        <v>98400</v>
       </c>
       <c r="M9" t="n">
-        <v>2910</v>
+        <v>6000</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>7230</v>
+        <v>14490</v>
       </c>
       <c r="P9" t="n">
-        <v>14520</v>
+        <v>12390</v>
       </c>
       <c r="Q9" t="n">
-        <v>17569.23</v>
+        <v>172247.4</v>
       </c>
     </row>
     <row r="10">
@@ -24146,22 +24146,22 @@
         <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>41400</v>
+        <v>54150</v>
       </c>
       <c r="M10" t="n">
-        <v>2370</v>
+        <v>5430</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3420</v>
+        <v>9960</v>
       </c>
       <c r="P10" t="n">
-        <v>14370</v>
+        <v>13710</v>
       </c>
       <c r="Q10" t="n">
-        <v>10471.17</v>
+        <v>102658.5</v>
       </c>
     </row>
     <row r="11">
@@ -24199,22 +24199,22 @@
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>17250</v>
+        <v>24840</v>
       </c>
       <c r="M11" t="n">
-        <v>1950</v>
+        <v>4800</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3540</v>
+        <v>4320</v>
       </c>
       <c r="P11" t="n">
-        <v>13260</v>
+        <v>12450</v>
       </c>
       <c r="Q11" t="n">
-        <v>6656.69</v>
+        <v>65261.7</v>
       </c>
     </row>
     <row r="12">
@@ -24252,22 +24252,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3750</v>
+        <v>9840</v>
       </c>
       <c r="M12" t="n">
+        <v>3210</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
         <v>780</v>
       </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>360</v>
-      </c>
       <c r="P12" t="n">
-        <v>15630</v>
+        <v>19050</v>
       </c>
       <c r="Q12" t="n">
-        <v>2764.56</v>
+        <v>27103.5</v>
       </c>
     </row>
     <row r="13">
@@ -24305,22 +24305,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1440</v>
+        <v>5070</v>
       </c>
       <c r="M13" t="n">
-        <v>90</v>
+        <v>1110</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="P13" t="n">
-        <v>12030</v>
+        <v>11250</v>
       </c>
       <c r="Q13" t="n">
-        <v>768.37</v>
+        <v>7533</v>
       </c>
     </row>
     <row r="14">
@@ -24358,10 +24358,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>510</v>
+        <v>3660</v>
       </c>
       <c r="M14" t="n">
-        <v>60</v>
+        <v>540</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -24370,10 +24370,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>24030</v>
+        <v>26610</v>
       </c>
       <c r="Q14" t="n">
-        <v>345.17</v>
+        <v>3384</v>
       </c>
     </row>
     <row r="15">
@@ -24411,7 +24411,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>300</v>
+        <v>1560</v>
       </c>
       <c r="M15" t="n">
         <v>60</v>
@@ -24420,13 +24420,13 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P15" t="n">
-        <v>14580</v>
+        <v>21240</v>
       </c>
       <c r="Q15" t="n">
-        <v>158.81</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="16">
@@ -24464,10 +24464,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>60</v>
+        <v>1020</v>
       </c>
       <c r="M16" t="n">
-        <v>600</v>
+        <v>660</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -24476,10 +24476,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>15240</v>
+        <v>15720</v>
       </c>
       <c r="Q16" t="n">
-        <v>131.09</v>
+        <v>1285.2</v>
       </c>
     </row>
     <row r="17">
@@ -24517,22 +24517,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>90</v>
+        <v>1710</v>
       </c>
       <c r="M17" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P17" t="n">
-        <v>18510</v>
+        <v>33810</v>
       </c>
       <c r="Q17" t="n">
-        <v>102.36</v>
+        <v>1003.5</v>
       </c>
     </row>
     <row r="18">
@@ -24573,7 +24573,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -24582,10 +24582,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>210</v>
+        <v>960</v>
       </c>
       <c r="Q18" t="n">
-        <v>12.85</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19">
@@ -24626,7 +24626,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -24638,7 +24638,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.5</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="20">
@@ -24679,7 +24679,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -24691,7 +24691,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.01</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="21">
@@ -24732,7 +24732,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -24744,7 +24744,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.78</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="22">
@@ -25161,7 +25161,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6404.4</v>
+        <v>7581.6</v>
       </c>
       <c r="I5" t="n">
         <v>0.33</v>
@@ -25173,22 +25173,22 @@
         <v>21.18</v>
       </c>
       <c r="L5" t="n">
-        <v>56441.7</v>
+        <v>57544.2</v>
       </c>
       <c r="M5" t="n">
-        <v>201.6</v>
+        <v>484.8</v>
       </c>
       <c r="N5" t="n">
-        <v>63.6</v>
+        <v>109.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1255.5</v>
+        <v>1308</v>
       </c>
       <c r="P5" t="n">
-        <v>105.6</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>1519.59</v>
+        <v>14897.92</v>
       </c>
     </row>
     <row r="6">
@@ -25214,7 +25214,7 @@
         <v>5031</v>
       </c>
       <c r="H6" t="n">
-        <v>1419.3</v>
+        <v>1710</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -25226,22 +25226,22 @@
         <v>29.91</v>
       </c>
       <c r="L6" t="n">
-        <v>96281.39999999999</v>
+        <v>100199.7</v>
       </c>
       <c r="M6" t="n">
-        <v>384</v>
+        <v>1228.8</v>
       </c>
       <c r="N6" t="n">
-        <v>49.5</v>
+        <v>105</v>
       </c>
       <c r="O6" t="n">
-        <v>5557.5</v>
+        <v>6435</v>
       </c>
       <c r="P6" t="n">
-        <v>1035</v>
+        <v>855</v>
       </c>
       <c r="Q6" t="n">
-        <v>23265.65</v>
+        <v>228094.65</v>
       </c>
     </row>
     <row r="7">
@@ -25267,7 +25267,7 @@
         <v>12244.5</v>
       </c>
       <c r="H7" t="n">
-        <v>525.6</v>
+        <v>678.9</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -25279,22 +25279,22 @@
         <v>35.09</v>
       </c>
       <c r="L7" t="n">
-        <v>114984</v>
+        <v>126504</v>
       </c>
       <c r="M7" t="n">
-        <v>1512</v>
+        <v>4336.5</v>
       </c>
       <c r="N7" t="n">
-        <v>12.6</v>
+        <v>27.3</v>
       </c>
       <c r="O7" t="n">
-        <v>8043</v>
+        <v>7728</v>
       </c>
       <c r="P7" t="n">
-        <v>2497.5</v>
+        <v>1552.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>25429.78</v>
+        <v>249311.52</v>
       </c>
     </row>
     <row r="8">
@@ -25320,7 +25320,7 @@
         <v>45630</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>76.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -25332,22 +25332,22 @@
         <v>23.55</v>
       </c>
       <c r="L8" t="n">
-        <v>87138.3</v>
+        <v>98555.10000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>1947</v>
+        <v>5362.5</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>7276.5</v>
+        <v>11151</v>
       </c>
       <c r="P8" t="n">
-        <v>5586</v>
+        <v>2804.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>24330.54</v>
+        <v>238534.74</v>
       </c>
     </row>
     <row r="9">
@@ -25373,7 +25373,7 @@
         <v>29044.5</v>
       </c>
       <c r="H9" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -25385,22 +25385,22 @@
         <v>17.67</v>
       </c>
       <c r="L9" t="n">
-        <v>67699.8</v>
+        <v>79704</v>
       </c>
       <c r="M9" t="n">
-        <v>2037</v>
+        <v>4200</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3976.5</v>
+        <v>7969.5</v>
       </c>
       <c r="P9" t="n">
-        <v>7260</v>
+        <v>6195</v>
       </c>
       <c r="Q9" t="n">
-        <v>17042.16</v>
+        <v>167079.98</v>
       </c>
     </row>
     <row r="10">
@@ -25438,22 +25438,22 @@
         <v>3.48</v>
       </c>
       <c r="L10" t="n">
-        <v>36846</v>
+        <v>48193.5</v>
       </c>
       <c r="M10" t="n">
-        <v>2014.5</v>
+        <v>4615.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2394</v>
+        <v>6972</v>
       </c>
       <c r="P10" t="n">
-        <v>12214.5</v>
+        <v>11653.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>10471.17</v>
+        <v>102658.5</v>
       </c>
     </row>
     <row r="11">
@@ -25491,22 +25491,22 @@
         <v>0.9</v>
       </c>
       <c r="L11" t="n">
-        <v>17250</v>
+        <v>24840</v>
       </c>
       <c r="M11" t="n">
-        <v>1755</v>
+        <v>4320</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3009</v>
+        <v>3672</v>
       </c>
       <c r="P11" t="n">
-        <v>11934</v>
+        <v>11205</v>
       </c>
       <c r="Q11" t="n">
-        <v>6656.69</v>
+        <v>65261.7</v>
       </c>
     </row>
     <row r="12">
@@ -25544,22 +25544,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3750</v>
+        <v>9840</v>
       </c>
       <c r="M12" t="n">
-        <v>741</v>
+        <v>3049.5</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>360</v>
+        <v>780</v>
       </c>
       <c r="P12" t="n">
-        <v>15630</v>
+        <v>19050</v>
       </c>
       <c r="Q12" t="n">
-        <v>2764.56</v>
+        <v>27103.5</v>
       </c>
     </row>
     <row r="13">
@@ -25597,22 +25597,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1440</v>
+        <v>5070</v>
       </c>
       <c r="M13" t="n">
-        <v>90</v>
+        <v>1110</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="P13" t="n">
-        <v>12030</v>
+        <v>11250</v>
       </c>
       <c r="Q13" t="n">
-        <v>768.37</v>
+        <v>7533</v>
       </c>
     </row>
     <row r="14">
@@ -25650,10 +25650,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>510</v>
+        <v>3660</v>
       </c>
       <c r="M14" t="n">
-        <v>60</v>
+        <v>540</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -25662,10 +25662,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>24030</v>
+        <v>26610</v>
       </c>
       <c r="Q14" t="n">
-        <v>345.17</v>
+        <v>3384</v>
       </c>
     </row>
     <row r="15">
@@ -25703,7 +25703,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>300</v>
+        <v>1560</v>
       </c>
       <c r="M15" t="n">
         <v>60</v>
@@ -25712,13 +25712,13 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P15" t="n">
-        <v>14580</v>
+        <v>21240</v>
       </c>
       <c r="Q15" t="n">
-        <v>158.81</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="16">
@@ -25756,10 +25756,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>60</v>
+        <v>1020</v>
       </c>
       <c r="M16" t="n">
-        <v>600</v>
+        <v>660</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -25768,10 +25768,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>15240</v>
+        <v>15720</v>
       </c>
       <c r="Q16" t="n">
-        <v>131.09</v>
+        <v>1285.2</v>
       </c>
     </row>
     <row r="17">
@@ -25809,22 +25809,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>90</v>
+        <v>1710</v>
       </c>
       <c r="M17" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P17" t="n">
-        <v>18510</v>
+        <v>33810</v>
       </c>
       <c r="Q17" t="n">
-        <v>102.36</v>
+        <v>1003.5</v>
       </c>
     </row>
     <row r="18">
@@ -25865,7 +25865,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -25874,10 +25874,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>210</v>
+        <v>960</v>
       </c>
       <c r="Q18" t="n">
-        <v>12.85</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19">
@@ -25918,7 +25918,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -25930,7 +25930,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.5</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="20">
@@ -25971,7 +25971,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -25983,7 +25983,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.01</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="21">
@@ -26024,7 +26024,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -26036,7 +26036,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.78</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="22">
@@ -26453,7 +26453,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>36505080</v>
+        <v>43215120</v>
       </c>
       <c r="I5" t="n">
         <v>64288.14</v>
@@ -26465,22 +26465,22 @@
         <v>1028610.3</v>
       </c>
       <c r="L5" t="n">
-        <v>10159506</v>
+        <v>10357956</v>
       </c>
       <c r="M5" t="n">
-        <v>70560</v>
+        <v>169680</v>
       </c>
       <c r="N5" t="n">
-        <v>10812</v>
+        <v>18666</v>
       </c>
       <c r="O5" t="n">
-        <v>213435</v>
+        <v>222360</v>
       </c>
       <c r="P5" t="n">
-        <v>6864</v>
+        <v>4524</v>
       </c>
       <c r="Q5" t="n">
-        <v>911753.01</v>
+        <v>8938755</v>
       </c>
     </row>
     <row r="6">
@@ -26506,7 +26506,7 @@
         <v>271674</v>
       </c>
       <c r="H6" t="n">
-        <v>8090010</v>
+        <v>9747000</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -26518,22 +26518,22 @@
         <v>1452455.63</v>
       </c>
       <c r="L6" t="n">
-        <v>17330652</v>
+        <v>18035946</v>
       </c>
       <c r="M6" t="n">
-        <v>134400</v>
+        <v>430080</v>
       </c>
       <c r="N6" t="n">
-        <v>8415</v>
+        <v>17850</v>
       </c>
       <c r="O6" t="n">
-        <v>944775</v>
+        <v>1093950</v>
       </c>
       <c r="P6" t="n">
-        <v>67275</v>
+        <v>55575</v>
       </c>
       <c r="Q6" t="n">
-        <v>13959392.58</v>
+        <v>136856790</v>
       </c>
     </row>
     <row r="7">
@@ -26559,7 +26559,7 @@
         <v>661203</v>
       </c>
       <c r="H7" t="n">
-        <v>2995920</v>
+        <v>3869730</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -26571,22 +26571,22 @@
         <v>1703830.04</v>
       </c>
       <c r="L7" t="n">
-        <v>20697120</v>
+        <v>22770720</v>
       </c>
       <c r="M7" t="n">
-        <v>529200</v>
+        <v>1517775</v>
       </c>
       <c r="N7" t="n">
-        <v>2142</v>
+        <v>4641</v>
       </c>
       <c r="O7" t="n">
-        <v>1367310</v>
+        <v>1313760</v>
       </c>
       <c r="P7" t="n">
-        <v>162337.5</v>
+        <v>100912.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>15257865.02</v>
+        <v>149586912</v>
       </c>
     </row>
     <row r="8">
@@ -26612,7 +26612,7 @@
         <v>2464020</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>436050</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -26624,22 +26624,22 @@
         <v>1143590.91</v>
       </c>
       <c r="L8" t="n">
-        <v>15684894</v>
+        <v>17739918</v>
       </c>
       <c r="M8" t="n">
-        <v>681450</v>
+        <v>1876875</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1237005</v>
+        <v>1895670</v>
       </c>
       <c r="P8" t="n">
-        <v>363090</v>
+        <v>182286</v>
       </c>
       <c r="Q8" t="n">
-        <v>14598326.09</v>
+        <v>143120844</v>
       </c>
     </row>
     <row r="9">
@@ -26665,7 +26665,7 @@
         <v>1568403</v>
       </c>
       <c r="H9" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -26677,22 +26677,22 @@
         <v>857790.3</v>
       </c>
       <c r="L9" t="n">
-        <v>12185964</v>
+        <v>14346720</v>
       </c>
       <c r="M9" t="n">
-        <v>712950</v>
+        <v>1470000</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>676005</v>
+        <v>1354815</v>
       </c>
       <c r="P9" t="n">
-        <v>471900</v>
+        <v>402675</v>
       </c>
       <c r="Q9" t="n">
-        <v>10225294.65</v>
+        <v>100247986.8</v>
       </c>
     </row>
     <row r="10">
@@ -26730,22 +26730,22 @@
         <v>168974.88</v>
       </c>
       <c r="L10" t="n">
-        <v>6632280</v>
+        <v>8674830</v>
       </c>
       <c r="M10" t="n">
-        <v>705075</v>
+        <v>1615425</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>406980</v>
+        <v>1185240</v>
       </c>
       <c r="P10" t="n">
-        <v>793942.5</v>
+        <v>757477.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>6282700.2</v>
+        <v>61595100</v>
       </c>
     </row>
     <row r="11">
@@ -26783,22 +26783,22 @@
         <v>43627.57</v>
       </c>
       <c r="L11" t="n">
-        <v>3105000</v>
+        <v>4471200</v>
       </c>
       <c r="M11" t="n">
-        <v>614250</v>
+        <v>1512000</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>511530</v>
+        <v>624240</v>
       </c>
       <c r="P11" t="n">
-        <v>775710</v>
+        <v>728325</v>
       </c>
       <c r="Q11" t="n">
-        <v>3994016.04</v>
+        <v>39157020</v>
       </c>
     </row>
     <row r="12">
@@ -26836,22 +26836,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>675000</v>
+        <v>1771200</v>
       </c>
       <c r="M12" t="n">
-        <v>259350</v>
+        <v>1067325</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>61200</v>
+        <v>132600</v>
       </c>
       <c r="P12" t="n">
-        <v>1015950</v>
+        <v>1238250</v>
       </c>
       <c r="Q12" t="n">
-        <v>1658734.2</v>
+        <v>16262100</v>
       </c>
     </row>
     <row r="13">
@@ -26889,22 +26889,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>259200</v>
+        <v>912600</v>
       </c>
       <c r="M13" t="n">
-        <v>31500</v>
+        <v>388500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>10200</v>
+        <v>40800</v>
       </c>
       <c r="P13" t="n">
-        <v>781950</v>
+        <v>731250</v>
       </c>
       <c r="Q13" t="n">
-        <v>461019.6</v>
+        <v>4519800</v>
       </c>
     </row>
     <row r="14">
@@ -26942,10 +26942,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>91800</v>
+        <v>658800</v>
       </c>
       <c r="M14" t="n">
-        <v>21000</v>
+        <v>189000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -26954,10 +26954,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1561950</v>
+        <v>1729650</v>
       </c>
       <c r="Q14" t="n">
-        <v>207100.8</v>
+        <v>2030400</v>
       </c>
     </row>
     <row r="15">
@@ -26995,7 +26995,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>54000</v>
+        <v>280800</v>
       </c>
       <c r="M15" t="n">
         <v>21000</v>
@@ -27004,13 +27004,13 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>10200</v>
+        <v>20400</v>
       </c>
       <c r="P15" t="n">
-        <v>947700</v>
+        <v>1380600</v>
       </c>
       <c r="Q15" t="n">
-        <v>95288.39999999999</v>
+        <v>934200</v>
       </c>
     </row>
     <row r="16">
@@ -27048,10 +27048,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>10800</v>
+        <v>183600</v>
       </c>
       <c r="M16" t="n">
-        <v>210000</v>
+        <v>231000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -27060,10 +27060,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>990600</v>
+        <v>1021800</v>
       </c>
       <c r="Q16" t="n">
-        <v>78654.24000000001</v>
+        <v>771120</v>
       </c>
     </row>
     <row r="17">
@@ -27101,22 +27101,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>16200</v>
+        <v>307800</v>
       </c>
       <c r="M17" t="n">
-        <v>31500</v>
+        <v>10500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>10200</v>
+        <v>25500</v>
       </c>
       <c r="P17" t="n">
-        <v>1203150</v>
+        <v>2197650</v>
       </c>
       <c r="Q17" t="n">
-        <v>61414.2</v>
+        <v>602100</v>
       </c>
     </row>
     <row r="18">
@@ -27157,7 +27157,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>10500</v>
+        <v>42000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -27166,10 +27166,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>13650</v>
+        <v>62400</v>
       </c>
       <c r="Q18" t="n">
-        <v>7711.2</v>
+        <v>75600</v>
       </c>
     </row>
     <row r="19">
@@ -27210,7 +27210,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -27222,7 +27222,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2698.92</v>
+        <v>26460</v>
       </c>
     </row>
     <row r="20">
@@ -27263,7 +27263,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>21000</v>
+        <v>10500</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -27275,7 +27275,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>605.88</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="21">
@@ -27316,7 +27316,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>52500</v>
+        <v>105000</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -27328,7 +27328,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3470.04</v>
+        <v>34020</v>
       </c>
     </row>
     <row r="22">
@@ -27692,7 +27692,7 @@
         <v>129990</v>
       </c>
       <c r="H4" t="n">
-        <v>27960</v>
+        <v>29580</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -27704,7 +27704,7 @@
         <v>72</v>
       </c>
       <c r="L4" t="n">
-        <v>357180</v>
+        <v>406950</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27713,13 +27713,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>77400</v>
+        <v>79950</v>
       </c>
       <c r="P4" t="n">
-        <v>630</v>
+        <v>60</v>
       </c>
       <c r="Q4" t="n">
-        <v>38074.05</v>
+        <v>530145</v>
       </c>
     </row>
     <row r="5">
@@ -27745,7 +27745,7 @@
         <v>75420</v>
       </c>
       <c r="H5" t="n">
-        <v>25680</v>
+        <v>26220</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -27757,7 +27757,7 @@
         <v>37</v>
       </c>
       <c r="L5" t="n">
-        <v>166440</v>
+        <v>179730</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -27766,13 +27766,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>47670</v>
+        <v>51030</v>
       </c>
       <c r="P5" t="n">
-        <v>2340</v>
+        <v>30</v>
       </c>
       <c r="Q5" t="n">
-        <v>15117.71</v>
+        <v>210499.74</v>
       </c>
     </row>
     <row r="6">
@@ -27798,7 +27798,7 @@
         <v>28050</v>
       </c>
       <c r="H6" t="n">
-        <v>4320</v>
+        <v>5100</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -27810,7 +27810,7 @@
         <v>7</v>
       </c>
       <c r="L6" t="n">
-        <v>61380</v>
+        <v>69270</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -27819,13 +27819,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>22890</v>
+        <v>28890</v>
       </c>
       <c r="P6" t="n">
-        <v>2580</v>
+        <v>150</v>
       </c>
       <c r="Q6" t="n">
-        <v>5737.7</v>
+        <v>79892.00999999999</v>
       </c>
     </row>
     <row r="7">
@@ -27851,7 +27851,7 @@
         <v>900</v>
       </c>
       <c r="H7" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -27863,7 +27863,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>8640</v>
+        <v>11190</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -27872,13 +27872,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>8010</v>
+        <v>11640</v>
       </c>
       <c r="P7" t="n">
-        <v>4500</v>
+        <v>510</v>
       </c>
       <c r="Q7" t="n">
-        <v>346.97</v>
+        <v>4831.2</v>
       </c>
     </row>
     <row r="8">
@@ -27904,7 +27904,7 @@
         <v>300</v>
       </c>
       <c r="H8" t="n">
-        <v>270</v>
+        <v>330</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -27916,7 +27916,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2850</v>
+        <v>4500</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -27925,13 +27925,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3030</v>
+        <v>9360</v>
       </c>
       <c r="P8" t="n">
-        <v>5250</v>
+        <v>2430</v>
       </c>
       <c r="Q8" t="n">
-        <v>60.65</v>
+        <v>844.47</v>
       </c>
     </row>
     <row r="9">
@@ -27969,7 +27969,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>630</v>
+        <v>2280</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -27978,13 +27978,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>690</v>
+        <v>3780</v>
       </c>
       <c r="P9" t="n">
-        <v>6300</v>
+        <v>8640</v>
       </c>
       <c r="Q9" t="n">
-        <v>21.9</v>
+        <v>304.92</v>
       </c>
     </row>
     <row r="10">
@@ -28010,7 +28010,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -28022,22 +28022,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
+        <v>1830</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
         <v>270</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
       <c r="P10" t="n">
-        <v>3090</v>
+        <v>7620</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.76</v>
+        <v>80.19</v>
       </c>
     </row>
     <row r="11">
@@ -28063,7 +28063,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -28075,7 +28075,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>1230</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -28087,10 +28087,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2070</v>
+        <v>6150</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.92</v>
+        <v>12.87</v>
       </c>
     </row>
     <row r="12">
@@ -28128,7 +28128,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -28140,10 +28140,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>540</v>
+        <v>2160</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.21</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="13">
@@ -28181,7 +28181,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -28193,7 +28193,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>60</v>
+        <v>420</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -29037,7 +29037,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>9244.799999999999</v>
+        <v>9439.200000000001</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -29049,7 +29049,7 @@
         <v>12.25</v>
       </c>
       <c r="L5" t="n">
-        <v>34952.4</v>
+        <v>37743.3</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -29058,13 +29058,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2383.5</v>
+        <v>2551.5</v>
       </c>
       <c r="P5" t="n">
-        <v>46.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>755.89</v>
+        <v>10524.99</v>
       </c>
     </row>
     <row r="6">
@@ -29090,7 +29090,7 @@
         <v>1402.5</v>
       </c>
       <c r="H6" t="n">
-        <v>2462.4</v>
+        <v>2907</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -29102,7 +29102,7 @@
         <v>3.55</v>
       </c>
       <c r="L6" t="n">
-        <v>22710.6</v>
+        <v>25629.9</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -29111,13 +29111,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>5722.5</v>
+        <v>7222.5</v>
       </c>
       <c r="P6" t="n">
-        <v>387</v>
+        <v>22.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>4303.27</v>
+        <v>59919.01</v>
       </c>
     </row>
     <row r="7">
@@ -29143,7 +29143,7 @@
         <v>135</v>
       </c>
       <c r="H7" t="n">
-        <v>438</v>
+        <v>657</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -29155,7 +29155,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>5184</v>
+        <v>6714</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -29164,13 +29164,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2803.5</v>
+        <v>4074</v>
       </c>
       <c r="P7" t="n">
-        <v>1125</v>
+        <v>127.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>277.57</v>
+        <v>3864.96</v>
       </c>
     </row>
     <row r="8">
@@ -29196,7 +29196,7 @@
         <v>195</v>
       </c>
       <c r="H8" t="n">
-        <v>229.5</v>
+        <v>280.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -29208,7 +29208,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2023.5</v>
+        <v>3195</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -29217,13 +29217,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1363.5</v>
+        <v>4212</v>
       </c>
       <c r="P8" t="n">
-        <v>1995</v>
+        <v>923.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>57.62</v>
+        <v>802.25</v>
       </c>
     </row>
     <row r="9">
@@ -29261,7 +29261,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>510.3</v>
+        <v>1846.8</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -29270,13 +29270,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>379.5</v>
+        <v>2079</v>
       </c>
       <c r="P9" t="n">
-        <v>3150</v>
+        <v>4320</v>
       </c>
       <c r="Q9" t="n">
-        <v>21.24</v>
+        <v>295.77</v>
       </c>
     </row>
     <row r="10">
@@ -29302,7 +29302,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -29314,7 +29314,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>240.3</v>
+        <v>1628.7</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -29323,13 +29323,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="P10" t="n">
-        <v>2626.5</v>
+        <v>6477</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.76</v>
+        <v>80.19</v>
       </c>
     </row>
     <row r="11">
@@ -29355,7 +29355,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -29367,7 +29367,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>1230</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -29379,10 +29379,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1863</v>
+        <v>5535</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.92</v>
+        <v>12.87</v>
       </c>
     </row>
     <row r="12">
@@ -29420,7 +29420,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -29432,10 +29432,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>540</v>
+        <v>2160</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.21</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="13">
@@ -29473,7 +29473,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -29485,7 +29485,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>60</v>
+        <v>420</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -30329,7 +30329,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>52695360</v>
+        <v>53803440</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -30341,7 +30341,7 @@
         <v>594665.33</v>
       </c>
       <c r="L5" t="n">
-        <v>6291432</v>
+        <v>6793794</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -30350,13 +30350,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>405195</v>
+        <v>433755</v>
       </c>
       <c r="P5" t="n">
-        <v>3042</v>
+        <v>39</v>
       </c>
       <c r="Q5" t="n">
-        <v>453531.26</v>
+        <v>6314992.2</v>
       </c>
     </row>
     <row r="6">
@@ -30382,7 +30382,7 @@
         <v>75735</v>
       </c>
       <c r="H6" t="n">
-        <v>14035680</v>
+        <v>16569900</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -30394,7 +30394,7 @@
         <v>172325.24</v>
       </c>
       <c r="L6" t="n">
-        <v>4087908</v>
+        <v>4613382</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -30403,13 +30403,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>972825</v>
+        <v>1227825</v>
       </c>
       <c r="P6" t="n">
-        <v>25155</v>
+        <v>1462.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>2581964.51</v>
+        <v>35951404.5</v>
       </c>
     </row>
     <row r="7">
@@ -30435,7 +30435,7 @@
         <v>7290</v>
       </c>
       <c r="H7" t="n">
-        <v>2496600</v>
+        <v>3744900</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -30447,7 +30447,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>933120</v>
+        <v>1208520</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -30456,13 +30456,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>476595</v>
+        <v>692580</v>
       </c>
       <c r="P7" t="n">
-        <v>73125</v>
+        <v>8287.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>166544.64</v>
+        <v>2318976</v>
       </c>
     </row>
     <row r="8">
@@ -30488,7 +30488,7 @@
         <v>10530</v>
       </c>
       <c r="H8" t="n">
-        <v>1308150</v>
+        <v>1598850</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>364230</v>
+        <v>575100</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -30509,13 +30509,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>231795</v>
+        <v>716040</v>
       </c>
       <c r="P8" t="n">
-        <v>129675</v>
+        <v>60021</v>
       </c>
       <c r="Q8" t="n">
-        <v>34569.53</v>
+        <v>481347.9</v>
       </c>
     </row>
     <row r="9">
@@ -30553,7 +30553,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>91854</v>
+        <v>332424</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -30562,13 +30562,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>64515</v>
+        <v>353430</v>
       </c>
       <c r="P9" t="n">
-        <v>204750</v>
+        <v>280800</v>
       </c>
       <c r="Q9" t="n">
-        <v>12745.1</v>
+        <v>177463.44</v>
       </c>
     </row>
     <row r="10">
@@ -30594,7 +30594,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1710000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -30606,7 +30606,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>43254</v>
+        <v>293166</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -30615,13 +30615,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>32130</v>
       </c>
       <c r="P10" t="n">
-        <v>170722.5</v>
+        <v>421005</v>
       </c>
       <c r="Q10" t="n">
-        <v>3455.46</v>
+        <v>48114</v>
       </c>
     </row>
     <row r="11">
@@ -30647,7 +30647,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>171000</v>
+        <v>855000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -30659,7 +30659,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>5400</v>
+        <v>221400</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -30671,10 +30671,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>121095</v>
+        <v>359775</v>
       </c>
       <c r="Q11" t="n">
-        <v>554.58</v>
+        <v>7722</v>
       </c>
     </row>
     <row r="12">
@@ -30712,7 +30712,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>97200</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -30724,10 +30724,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>35100</v>
+        <v>140400</v>
       </c>
       <c r="Q12" t="n">
-        <v>127.98</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="13">
@@ -30765,7 +30765,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -30777,7 +30777,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3900</v>
+        <v>27300</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
